--- a/SALTA 1167/Noviembre/SALTA1167-Noviembre.xlsx
+++ b/SALTA 1167/Noviembre/SALTA1167-Noviembre.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\SALTA 1167\Octubre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\SALTA 1167\Noviembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70428E96-6D0F-4E8A-8721-AFE750E41A40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F424B4EB-DF08-4CA5-8223-1874EAECCDF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -20,14 +20,14 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="2">EDESUR!$B$3:$J$35</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$O$42</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$93</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$94</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="139">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -117,12 +117,6 @@
   </si>
   <si>
     <t>Honorarios administracion</t>
-  </si>
-  <si>
-    <t>VTO 14/11</t>
-  </si>
-  <si>
-    <t>PERÍODO: OCTUBRE</t>
   </si>
   <si>
     <t>1  A</t>
@@ -295,22 +289,10 @@
     <t xml:space="preserve">LIMPIEZA </t>
   </si>
   <si>
-    <t>Full Clean - Servicio de limpieza - Esperando definicion de traspaso</t>
-  </si>
-  <si>
     <t>Servicio de interet Claro</t>
   </si>
   <si>
-    <t>Ascensores Guillemi - Mantenimiento de ascesores - No se abona aguardando traspaso</t>
-  </si>
-  <si>
     <t xml:space="preserve">Sr cossentino - Traspaso administracion </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Si.Pro.Da </t>
-  </si>
-  <si>
-    <t>Fotocopias septiembre (Gestion de administracion saliente)</t>
   </si>
   <si>
     <t>Gastos bancarios - Mes de septiembre Administracion anterior</t>
@@ -439,6 +421,33 @@
   </si>
   <si>
     <t>CAJA B</t>
+  </si>
+  <si>
+    <t>VTO 15/12</t>
+  </si>
+  <si>
+    <t>PERÍODO: NOVIEMBRE</t>
+  </si>
+  <si>
+    <t>Service de blindez or cierre defectuoso - Cerrajeria CITTA</t>
+  </si>
+  <si>
+    <t>Transf 18/11</t>
+  </si>
+  <si>
+    <t>GF elevadores - Mantenimiento de ascensores</t>
+  </si>
+  <si>
+    <t>Transf 13/11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full Clean </t>
+  </si>
+  <si>
+    <t>Full Clean - Servicio de limpieza</t>
+  </si>
+  <si>
+    <t>Full Clean - Servicio de limpieza - Mes anterior</t>
   </si>
 </sst>
 </file>
@@ -1083,7 +1092,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="198">
+  <cellXfs count="201">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1329,7 +1338,6 @@
     <xf numFmtId="164" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="8" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1370,84 +1378,84 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1459,6 +1467,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="8" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1824,31 +1838,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M97"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M98"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.5703125" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" customWidth="1"/>
+    <col min="1" max="1" width="37.5546875" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
+    <col min="5" max="5" width="14.6640625" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.28515625" customWidth="1"/>
+    <col min="12" max="12" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="14"/>
       <c r="B1" s="53" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C1" s="53"/>
       <c r="D1" s="53"/>
       <c r="E1" s="54"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="15"/>
       <c r="B2" s="55" t="s">
         <v>14</v>
@@ -1857,16 +1871,16 @@
       <c r="D2" s="55"/>
       <c r="E2" s="56"/>
     </row>
-    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="15"/>
-      <c r="B3" s="172" t="s">
-        <v>86</v>
-      </c>
-      <c r="C3" s="172"/>
-      <c r="D3" s="172"/>
-      <c r="E3" s="173"/>
-    </row>
-    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="167" t="s">
+        <v>84</v>
+      </c>
+      <c r="C3" s="167"/>
+      <c r="D3" s="167"/>
+      <c r="E3" s="168"/>
+    </row>
+    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="18" t="s">
         <v>0</v>
       </c>
@@ -1877,12 +1891,12 @@
       <c r="D4" s="19"/>
       <c r="E4" s="20"/>
     </row>
-    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="15" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>31</v>
+        <v>131</v>
       </c>
       <c r="C5" s="16"/>
       <c r="D5" s="55" t="s">
@@ -1890,7 +1904,7 @@
       </c>
       <c r="E5" s="17"/>
     </row>
-    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="18" t="s">
         <v>26</v>
       </c>
@@ -1901,732 +1915,753 @@
       </c>
       <c r="E6" s="20"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="175" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" s="175"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="175"/>
-      <c r="C9" s="175"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="175"/>
-      <c r="C10" s="175"/>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="174" t="s">
-        <v>122</v>
-      </c>
-      <c r="B13" s="174"/>
-      <c r="C13" s="174"/>
-      <c r="D13" s="174"/>
-      <c r="E13" s="174"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="174"/>
-      <c r="B14" s="174"/>
-      <c r="C14" s="174"/>
-      <c r="D14" s="174"/>
-      <c r="E14" s="174"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="174"/>
-      <c r="B15" s="174"/>
-      <c r="C15" s="174"/>
-      <c r="D15" s="174"/>
-      <c r="E15" s="174"/>
-    </row>
-    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="174"/>
-      <c r="B16" s="174"/>
-      <c r="C16" s="174"/>
-      <c r="D16" s="174"/>
-      <c r="E16" s="174"/>
-    </row>
-    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="172" t="s">
+        <v>130</v>
+      </c>
+      <c r="C8" s="172"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B9" s="172"/>
+      <c r="C9" s="172"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="172"/>
+      <c r="C10" s="172"/>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="171" t="s">
+        <v>116</v>
+      </c>
+      <c r="B13" s="171"/>
+      <c r="C13" s="171"/>
+      <c r="D13" s="171"/>
+      <c r="E13" s="171"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="171"/>
+      <c r="B14" s="171"/>
+      <c r="C14" s="171"/>
+      <c r="D14" s="171"/>
+      <c r="E14" s="171"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="171"/>
+      <c r="B15" s="171"/>
+      <c r="C15" s="171"/>
+      <c r="D15" s="171"/>
+      <c r="E15" s="171"/>
+    </row>
+    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="171"/>
+      <c r="B16" s="171"/>
+      <c r="C16" s="171"/>
+      <c r="D16" s="171"/>
+      <c r="E16" s="171"/>
+    </row>
+    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="10" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="12"/>
       <c r="D20" s="8"/>
       <c r="E20" s="13"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="26" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B21" s="26"/>
       <c r="C21" s="26"/>
       <c r="D21" s="123"/>
       <c r="E21" s="108"/>
     </row>
-    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="166" t="s">
-        <v>88</v>
-      </c>
-      <c r="B22" s="167"/>
+    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="165" t="s">
+        <v>137</v>
+      </c>
+      <c r="B22" s="166"/>
       <c r="C22" s="40"/>
-      <c r="D22" s="124"/>
+      <c r="D22" s="200">
+        <v>431286.18</v>
+      </c>
       <c r="E22" s="137"/>
       <c r="H22" s="97"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="22" t="s">
+    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="165" t="s">
+        <v>138</v>
+      </c>
+      <c r="B23" s="166"/>
+      <c r="C23" s="40"/>
+      <c r="D23" s="200">
+        <v>431286.18</v>
+      </c>
+      <c r="E23" s="137"/>
+      <c r="H23" s="97"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24" s="22" t="s">
         <v>9</v>
-      </c>
-      <c r="B23" s="22"/>
-      <c r="C23" s="22"/>
-      <c r="D23" s="125"/>
-      <c r="E23" s="139">
-        <f>SUM(D22:D22)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="26" t="s">
-        <v>18</v>
       </c>
       <c r="B24" s="22"/>
       <c r="C24" s="22"/>
-      <c r="D24" s="126"/>
-      <c r="E24" s="138"/>
-    </row>
-    <row r="25" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="170" t="s">
-        <v>85</v>
-      </c>
-      <c r="B25" s="171"/>
-      <c r="C25" s="42"/>
-      <c r="D25" s="153">
-        <v>65518</v>
-      </c>
-      <c r="E25" s="110" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="22" t="s">
+      <c r="D24" s="125"/>
+      <c r="E24" s="139">
+        <f>SUM(D22:D22)</f>
+        <v>431286.18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="B25" s="22"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="126"/>
+      <c r="E25" s="138"/>
+    </row>
+    <row r="26" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="169" t="s">
+        <v>83</v>
+      </c>
+      <c r="B26" s="170"/>
+      <c r="C26" s="42"/>
+      <c r="D26" s="199">
+        <v>66146</v>
+      </c>
+      <c r="E26" s="110" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="B26" s="22"/>
-      <c r="C26" s="22"/>
-      <c r="D26" s="125"/>
-      <c r="E26" s="109">
-        <f>SUM(D25:D25)</f>
-        <v>65518</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="26" t="s">
+      <c r="B27" s="22"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="125"/>
+      <c r="E27" s="109">
+        <f>SUM(D26:D26)</f>
+        <v>66146</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="B27" s="112"/>
-      <c r="C27" s="112"/>
-      <c r="D27" s="127"/>
-      <c r="E27" s="113"/>
-    </row>
-    <row r="28" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B28" s="5"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="118">
-        <v>0</v>
-      </c>
-      <c r="E28" s="117"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="112"/>
+      <c r="C28" s="112"/>
+      <c r="D28" s="127"/>
+      <c r="E28" s="113"/>
+    </row>
+    <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
       <c r="D29" s="118">
-        <v>8128.13</v>
-      </c>
-      <c r="E29" s="117" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="E29" s="117"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B30" s="5"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="198">
+        <v>5457.15</v>
+      </c>
+      <c r="E30" s="117" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B31" s="134"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="198">
+        <v>321318.45</v>
+      </c>
+      <c r="E31" s="117" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32" s="169" t="s">
         <v>72</v>
       </c>
-      <c r="B30" s="134"/>
-      <c r="C30" s="5"/>
-      <c r="D30" s="118">
-        <v>374755.03</v>
-      </c>
-      <c r="E30" s="117" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="170" t="s">
-        <v>74</v>
-      </c>
-      <c r="B31" s="171"/>
-      <c r="C31" s="5"/>
-      <c r="D31" s="118">
-        <v>242436.29</v>
-      </c>
-      <c r="E31" s="117" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="120" t="s">
-        <v>89</v>
-      </c>
-      <c r="B32" s="116"/>
+      <c r="B32" s="170"/>
       <c r="C32" s="5"/>
-      <c r="D32" s="118">
+      <c r="D32" s="198">
+        <v>242436.28</v>
+      </c>
+      <c r="E32" s="117" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A33" s="120" t="s">
+        <v>86</v>
+      </c>
+      <c r="B33" s="116"/>
+      <c r="C33" s="5"/>
+      <c r="D33" s="118">
         <v>20332.080000000002</v>
       </c>
-      <c r="E32" s="110" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="22" t="s">
+      <c r="E33" s="110" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="B33" s="22"/>
-      <c r="C33" s="22"/>
-      <c r="D33" s="128"/>
-      <c r="E33" s="111">
-        <f>SUM(D28:D32)</f>
-        <v>645651.53</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="26"/>
       <c r="B34" s="22"/>
       <c r="C34" s="22"/>
-      <c r="D34" s="125"/>
-      <c r="E34" s="114"/>
-    </row>
-    <row r="35" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="120" t="s">
-        <v>71</v>
-      </c>
-      <c r="B35" s="116"/>
-      <c r="C35" s="5"/>
-      <c r="D35" s="118">
+      <c r="D34" s="128"/>
+      <c r="E34" s="111">
+        <f>SUM(D29:D33)</f>
+        <v>589543.96</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="26"/>
+      <c r="B35" s="22"/>
+      <c r="C35" s="22"/>
+      <c r="D35" s="125"/>
+      <c r="E35" s="114"/>
+    </row>
+    <row r="36" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="120" t="s">
+        <v>69</v>
+      </c>
+      <c r="B36" s="116"/>
+      <c r="C36" s="5"/>
+      <c r="D36" s="118">
         <v>3320</v>
       </c>
-      <c r="E35" s="119"/>
-    </row>
-    <row r="36" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="166" t="s">
-        <v>90</v>
-      </c>
-      <c r="B36" s="167"/>
-      <c r="C36" s="5"/>
-      <c r="D36" s="118"/>
       <c r="E36" s="119"/>
     </row>
-    <row r="37" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="166" t="s">
-        <v>93</v>
-      </c>
-      <c r="B37" s="167"/>
+    <row r="37" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="165" t="s">
+        <v>134</v>
+      </c>
+      <c r="B37" s="166"/>
       <c r="C37" s="5"/>
-      <c r="D37" s="82">
-        <v>3960</v>
-      </c>
-      <c r="E37" s="119"/>
-    </row>
-    <row r="38" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="170" t="s">
-        <v>92</v>
-      </c>
-      <c r="B38" s="171"/>
+      <c r="D37" s="198">
+        <v>75000</v>
+      </c>
+      <c r="E37" s="119" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="165" t="s">
+        <v>132</v>
+      </c>
+      <c r="B38" s="166"/>
       <c r="C38" s="5"/>
-      <c r="D38" s="82">
+      <c r="D38" s="197">
+        <v>90000</v>
+      </c>
+      <c r="E38" s="119" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="169" t="s">
+        <v>136</v>
+      </c>
+      <c r="B39" s="170"/>
+      <c r="C39" s="5"/>
+      <c r="D39" s="82">
         <v>35000</v>
       </c>
-      <c r="E38" s="119"/>
-      <c r="I38" s="170"/>
-      <c r="J38" s="171"/>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" s="22" t="s">
+      <c r="E39" s="119"/>
+      <c r="I39" s="169"/>
+      <c r="J39" s="170"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A40" s="22" t="s">
         <v>6</v>
-      </c>
-      <c r="B39" s="26"/>
-      <c r="C39" s="26"/>
-      <c r="D39" s="25"/>
-      <c r="E39" s="109">
-        <f>SUM(D35:D38)</f>
-        <v>42280</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A40" s="26" t="s">
-        <v>11</v>
       </c>
       <c r="B40" s="26"/>
       <c r="C40" s="26"/>
-      <c r="D40" s="123"/>
-      <c r="E40" s="108"/>
-    </row>
-    <row r="41" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="166" t="s">
+      <c r="D40" s="25"/>
+      <c r="E40" s="109">
+        <f>SUM(D36:D39)</f>
+        <v>203320</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A41" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="B41" s="26"/>
+      <c r="C41" s="26"/>
+      <c r="D41" s="123"/>
+      <c r="E41" s="108"/>
+    </row>
+    <row r="42" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="165" t="s">
         <v>29</v>
       </c>
-      <c r="B41" s="167"/>
-      <c r="C41" s="40"/>
-      <c r="D41" s="124">
+      <c r="B42" s="166"/>
+      <c r="C42" s="40"/>
+      <c r="D42" s="124">
         <v>140000</v>
       </c>
-      <c r="E41" s="142"/>
-    </row>
-    <row r="42" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="135" t="s">
-        <v>91</v>
-      </c>
-      <c r="B42" s="136"/>
-      <c r="C42" s="40"/>
-      <c r="D42" s="154">
+      <c r="E42" s="142"/>
+    </row>
+    <row r="43" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="135" t="s">
+        <v>87</v>
+      </c>
+      <c r="B43" s="136"/>
+      <c r="C43" s="40"/>
+      <c r="D43" s="153">
         <v>202000</v>
       </c>
-      <c r="E42" s="142"/>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A43" s="22" t="s">
+      <c r="E43" s="142"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A44" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="B43" s="22"/>
-      <c r="C43" s="22"/>
-      <c r="D43" s="125"/>
-      <c r="E43" s="139">
-        <f>SUM(D41:D42)</f>
+      <c r="B44" s="22"/>
+      <c r="C44" s="22"/>
+      <c r="D44" s="125"/>
+      <c r="E44" s="139">
+        <f>SUM(D42:D43)</f>
         <v>342000</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A44" s="26" t="s">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A45" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="B44" s="51"/>
-      <c r="C44" s="22"/>
-      <c r="D44" s="122"/>
-      <c r="E44" s="109"/>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A45" s="5" t="s">
+      <c r="B45" s="51"/>
+      <c r="C45" s="22"/>
+      <c r="D45" s="122"/>
+      <c r="E45" s="109"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A46" s="5" t="s">
         <v>28</v>
-      </c>
-      <c r="B45" s="5"/>
-      <c r="C45" s="5"/>
-      <c r="D45" s="118"/>
-      <c r="E45" s="115"/>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A46" s="5" t="s">
-        <v>94</v>
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5"/>
-      <c r="D46" s="118">
+      <c r="D46" s="118"/>
+      <c r="E46" s="115"/>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A47" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B47" s="5"/>
+      <c r="C47" s="5"/>
+      <c r="D47" s="118">
         <v>84679.61</v>
       </c>
-      <c r="E46" s="30"/>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A47" s="39" t="s">
+      <c r="E47" s="30"/>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A48" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="B47" s="39"/>
-      <c r="C47" s="39"/>
-      <c r="D47" s="84"/>
-      <c r="E47" s="140">
-        <f>SUM(D45:D46)</f>
+      <c r="B48" s="39"/>
+      <c r="C48" s="39"/>
+      <c r="D48" s="84"/>
+      <c r="E48" s="140">
+        <f>SUM(D46:D47)</f>
         <v>84679.61</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A48" s="5"/>
-      <c r="B48" s="5"/>
-      <c r="C48" s="5"/>
-      <c r="D48" s="79"/>
-      <c r="E48" s="85"/>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="23" t="s">
-        <v>121</v>
-      </c>
-      <c r="B49" s="23"/>
-      <c r="C49" s="23"/>
-      <c r="D49" s="86"/>
-      <c r="E49" s="141">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A49" s="5"/>
+      <c r="B49" s="5"/>
+      <c r="C49" s="5"/>
+      <c r="D49" s="79"/>
+      <c r="E49" s="85"/>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A50" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="B50" s="23"/>
+      <c r="C50" s="23"/>
+      <c r="D50" s="86"/>
+      <c r="E50" s="141">
         <f>2000000-1180129.14</f>
         <v>819870.8600000001</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="1"/>
-      <c r="D50" s="87"/>
-      <c r="E50" s="88"/>
-      <c r="F50" s="32"/>
-    </row>
-    <row r="51" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="B51" s="9"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="89"/>
-      <c r="E51" s="90">
-        <f>(SUM(E21:E49))</f>
-        <v>2000000.0000000002</v>
-      </c>
-      <c r="F51" s="107"/>
-      <c r="G51" s="32"/>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D52" s="87"/>
-      <c r="E52" s="87"/>
-    </row>
-    <row r="53" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="1"/>
+      <c r="D51" s="87"/>
+      <c r="E51" s="88"/>
+      <c r="F51" s="32"/>
+    </row>
+    <row r="52" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B52" s="9"/>
+      <c r="C52" s="4"/>
+      <c r="D52" s="89"/>
+      <c r="E52" s="90">
+        <f>(SUM(E21:E50))</f>
+        <v>2536846.6100000003</v>
+      </c>
+      <c r="F52" s="107"/>
+      <c r="G52" s="32"/>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="D53" s="87"/>
       <c r="E53" s="87"/>
-      <c r="H53" s="129"/>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="B54" s="11"/>
-      <c r="C54" s="12"/>
-      <c r="D54" s="91"/>
-      <c r="E54" s="92"/>
-    </row>
-    <row r="55" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="170" t="s">
-        <v>81</v>
-      </c>
-      <c r="B55" s="171"/>
-      <c r="C55" s="5"/>
-      <c r="D55" s="82">
-        <v>37000</v>
-      </c>
-      <c r="E55" s="80"/>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="170" t="s">
-        <v>82</v>
-      </c>
-      <c r="B56" s="171"/>
+    </row>
+    <row r="54" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D54" s="87"/>
+      <c r="E54" s="87"/>
+      <c r="H54" s="129"/>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A55" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="B55" s="11"/>
+      <c r="C55" s="12"/>
+      <c r="D55" s="91"/>
+      <c r="E55" s="92"/>
+    </row>
+    <row r="56" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="169" t="s">
+        <v>79</v>
+      </c>
+      <c r="B56" s="170"/>
       <c r="C56" s="5"/>
       <c r="D56" s="82">
+        <v>37000</v>
+      </c>
+      <c r="E56" s="80"/>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A57" s="169" t="s">
+        <v>80</v>
+      </c>
+      <c r="B57" s="170"/>
+      <c r="C57" s="5"/>
+      <c r="D57" s="82">
         <v>120000</v>
       </c>
-      <c r="E56" s="80" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="166"/>
-      <c r="B57" s="167"/>
-      <c r="C57" s="5"/>
-      <c r="D57" s="82"/>
-      <c r="E57" s="80"/>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="81"/>
-      <c r="B58" s="83"/>
+      <c r="E57" s="80" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="165"/>
+      <c r="B58" s="166"/>
       <c r="C58" s="5"/>
       <c r="D58" s="82"/>
       <c r="E58" s="80"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="37"/>
-      <c r="B59" s="36"/>
-      <c r="C59" s="36"/>
-      <c r="D59" s="44"/>
-      <c r="E59" s="44">
-        <f>SUM(D55:D58)</f>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A59" s="81"/>
+      <c r="B59" s="83"/>
+      <c r="C59" s="5"/>
+      <c r="D59" s="82"/>
+      <c r="E59" s="80"/>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A60" s="37"/>
+      <c r="B60" s="36"/>
+      <c r="C60" s="36"/>
+      <c r="D60" s="44"/>
+      <c r="E60" s="44">
+        <f>SUM(D56:D59)</f>
         <v>157000</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="62" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="23" t="s">
+    <row r="61" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="62" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="63" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="B63" s="23"/>
+      <c r="C63" s="23"/>
+      <c r="D63" s="24"/>
+      <c r="E63" s="78"/>
+    </row>
+    <row r="64" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="65" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B65" s="9"/>
+      <c r="C65" s="4"/>
+      <c r="D65" s="4"/>
+      <c r="E65" s="52">
+        <f>E60+E63</f>
+        <v>157000</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="67" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="76" t="s">
         <v>120</v>
       </c>
-      <c r="B62" s="23"/>
-      <c r="C62" s="23"/>
-      <c r="D62" s="24"/>
-      <c r="E62" s="78"/>
-    </row>
-    <row r="63" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="64" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="B64" s="9"/>
-      <c r="C64" s="4"/>
-      <c r="D64" s="4"/>
-      <c r="E64" s="52">
-        <f>E59+E62</f>
+      <c r="B67" s="77">
+        <f>E52</f>
+        <v>2536846.6100000003</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="76" t="s">
+        <v>121</v>
+      </c>
+      <c r="B68" s="77">
+        <f>E52-E50</f>
+        <v>1716975.7500000002</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="76" t="s">
+        <v>122</v>
+      </c>
+      <c r="B69" s="77">
+        <f>E65-E63</f>
         <v>157000</v>
       </c>
     </row>
-    <row r="65" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="66" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="76" t="s">
+    <row r="70" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="76" t="s">
+        <v>123</v>
+      </c>
+      <c r="B70" s="77">
+        <f>E65</f>
+        <v>157000</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" s="29" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A72"/>
+      <c r="B72" s="31"/>
+      <c r="C72" s="28"/>
+    </row>
+    <row r="73" spans="1:5" s="29" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="99" t="s">
+        <v>124</v>
+      </c>
+      <c r="B73" s="164">
+        <v>-120596.37</v>
+      </c>
+      <c r="C73" s="28"/>
+      <c r="D73" s="35"/>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A74" s="42" t="s">
+        <v>117</v>
+      </c>
+      <c r="B74" s="104">
+        <f>-B68</f>
+        <v>-1716975.7500000002</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A75" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="B75" s="104">
+        <f>B93</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A76" s="42" t="s">
         <v>126</v>
       </c>
-      <c r="B66" s="77">
-        <f>E51</f>
-        <v>2000000.0000000002</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="76" t="s">
+      <c r="B76" s="105">
+        <f>PRORRATEO!G34-B83</f>
+        <v>1910977.6400000001</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A77" s="106" t="s">
+        <v>25</v>
+      </c>
+      <c r="B77" s="130"/>
+    </row>
+    <row r="78" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A78" s="102" t="s">
+        <v>128</v>
+      </c>
+      <c r="B78" s="103">
+        <f>SUM(B73:C77)</f>
+        <v>73405.520000000019</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A79" s="100"/>
+      <c r="B79" s="100"/>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A80" s="99" t="s">
+        <v>125</v>
+      </c>
+      <c r="B80" s="164">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A81" s="42" t="s">
+        <v>118</v>
+      </c>
+      <c r="B81" s="104">
+        <f>-B69</f>
+        <v>-157000</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A82" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="B82" s="104">
+        <f>B101</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A83" s="42" t="s">
         <v>127</v>
       </c>
-      <c r="B67" s="77">
-        <f>E51-E49</f>
-        <v>1180129.1400000001</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="76" t="s">
-        <v>128</v>
-      </c>
-      <c r="B68" s="77">
-        <f>E64-E62</f>
-        <v>157000</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="76" t="s">
-        <v>129</v>
-      </c>
-      <c r="B69" s="77">
-        <f>E64</f>
-        <v>157000</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" s="29" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A71"/>
-      <c r="B71" s="31"/>
-      <c r="C71" s="28"/>
-    </row>
-    <row r="72" spans="1:4" s="29" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="99" t="s">
-        <v>130</v>
-      </c>
-      <c r="B72" s="165">
-        <v>-120596.37</v>
-      </c>
-      <c r="C72" s="28"/>
-      <c r="D72" s="35"/>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A73" s="42" t="s">
-        <v>123</v>
-      </c>
-      <c r="B73" s="104">
-        <f>-B67</f>
-        <v>-1180129.1400000001</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A74" s="42" t="s">
-        <v>27</v>
-      </c>
-      <c r="B74" s="104">
-        <f>B92</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A75" s="42" t="s">
-        <v>132</v>
-      </c>
-      <c r="B75" s="105">
-        <f>PRORRATEO!G34-B82</f>
-        <v>1910977.6400000001</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A76" s="106" t="s">
-        <v>25</v>
-      </c>
-      <c r="B76" s="130"/>
-    </row>
-    <row r="77" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="102" t="s">
-        <v>134</v>
-      </c>
-      <c r="B77" s="103">
-        <f>SUM(B72:C76)</f>
-        <v>610252.12999999989</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A78" s="100"/>
-      <c r="B78" s="100"/>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A79" s="99" t="s">
-        <v>131</v>
-      </c>
-      <c r="B79" s="165">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A80" s="42" t="s">
-        <v>124</v>
-      </c>
-      <c r="B80" s="104">
-        <f>-B68</f>
-        <v>-157000</v>
-      </c>
-    </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A81" s="42" t="s">
-        <v>27</v>
-      </c>
-      <c r="B81" s="104">
-        <f>B100</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A82" s="42" t="s">
-        <v>133</v>
-      </c>
-      <c r="B82" s="105">
+      <c r="B83" s="105">
         <f>2157000</f>
         <v>2157000</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A83" s="106" t="s">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A84" s="106" t="s">
         <v>25</v>
       </c>
-      <c r="B83" s="130"/>
-    </row>
-    <row r="84" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="102" t="s">
-        <v>135</v>
-      </c>
-      <c r="B84" s="103">
-        <f>SUM(B79:C83)</f>
+      <c r="B84" s="130"/>
+    </row>
+    <row r="85" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A85" s="102" t="s">
+        <v>129</v>
+      </c>
+      <c r="B85" s="103">
+        <f>SUM(B80:C84)</f>
         <v>2000000</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A85" s="100"/>
-      <c r="B85" s="100"/>
-    </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A86" s="100"/>
       <c r="B86" s="100"/>
     </row>
-    <row r="87" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A88" s="169" t="s">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A87" s="100"/>
+      <c r="B87" s="100"/>
+    </row>
+    <row r="88" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A89" s="174" t="s">
         <v>19</v>
       </c>
-      <c r="B88" s="169"/>
-      <c r="C88" s="169"/>
-    </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A89" s="169"/>
-      <c r="B89" s="169"/>
-      <c r="C89" s="169"/>
-    </row>
-    <row r="90" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="94"/>
-      <c r="B90" s="27"/>
-      <c r="C90" s="27">
+      <c r="B89" s="174"/>
+      <c r="C89" s="174"/>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A90" s="174"/>
+      <c r="B90" s="174"/>
+      <c r="C90" s="174"/>
+    </row>
+    <row r="91" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="94"/>
+      <c r="B91" s="27"/>
+      <c r="C91" s="27">
         <v>40000</v>
       </c>
-      <c r="E90" s="107"/>
-    </row>
-    <row r="91" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="94"/>
-      <c r="B91" s="96"/>
-      <c r="C91" s="93"/>
-      <c r="D91" s="107"/>
-    </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A92" s="33" t="s">
+      <c r="E91" s="107"/>
+    </row>
+    <row r="92" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="94"/>
+      <c r="B92" s="96"/>
+      <c r="C92" s="93"/>
+      <c r="D92" s="107"/>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A93" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="B92" s="95">
-        <f>SUM(B90:B91)</f>
-        <v>0</v>
-      </c>
-      <c r="C92" s="34"/>
-    </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="M93" s="7"/>
-    </row>
-    <row r="94" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="168"/>
-      <c r="B94" s="168"/>
-      <c r="C94" s="168"/>
-      <c r="D94" s="168"/>
-      <c r="E94" s="168"/>
-    </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A95" s="168"/>
-      <c r="B95" s="168"/>
-      <c r="C95" s="168"/>
-      <c r="D95" s="168"/>
-      <c r="E95" s="168"/>
-    </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A96" s="168"/>
-      <c r="B96" s="168"/>
-      <c r="C96" s="168"/>
-      <c r="D96" s="168"/>
-      <c r="E96" s="168"/>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A97" s="168"/>
-      <c r="B97" s="168"/>
-      <c r="C97" s="168"/>
-      <c r="D97" s="168"/>
-      <c r="E97" s="168"/>
+      <c r="B93" s="95">
+        <f>SUM(B91:B92)</f>
+        <v>0</v>
+      </c>
+      <c r="C93" s="34"/>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M94" s="7"/>
+    </row>
+    <row r="95" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="173"/>
+      <c r="B95" s="173"/>
+      <c r="C95" s="173"/>
+      <c r="D95" s="173"/>
+      <c r="E95" s="173"/>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A96" s="173"/>
+      <c r="B96" s="173"/>
+      <c r="C96" s="173"/>
+      <c r="D96" s="173"/>
+      <c r="E96" s="173"/>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A97" s="173"/>
+      <c r="B97" s="173"/>
+      <c r="C97" s="173"/>
+      <c r="D97" s="173"/>
+      <c r="E97" s="173"/>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A98" s="173"/>
+      <c r="B98" s="173"/>
+      <c r="C98" s="173"/>
+      <c r="D98" s="173"/>
+      <c r="E98" s="173"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="17">
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A95:E98"/>
+    <mergeCell ref="A89:C90"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A58:B58"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="B3:E3"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A39:B39"/>
     <mergeCell ref="A13:E16"/>
     <mergeCell ref="B8:C10"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A94:E97"/>
-    <mergeCell ref="A88:C89"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A55:B55"/>
-    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A23:B23"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2637,253 +2672,253 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Q42"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="4.28515625" customWidth="1"/>
-    <col min="3" max="3" width="18.5703125" customWidth="1"/>
+    <col min="1" max="2" width="4.33203125" customWidth="1"/>
+    <col min="3" max="3" width="18.5546875" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="8.42578125" customWidth="1"/>
-    <col min="6" max="6" width="14.140625" customWidth="1"/>
-    <col min="7" max="7" width="12.28515625" customWidth="1"/>
-    <col min="8" max="8" width="10.5703125" customWidth="1"/>
-    <col min="9" max="9" width="9.5703125" customWidth="1"/>
-    <col min="10" max="10" width="12.28515625" customWidth="1"/>
-    <col min="11" max="11" width="12.42578125" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" customWidth="1"/>
+    <col min="5" max="5" width="8.44140625" customWidth="1"/>
+    <col min="6" max="6" width="14.109375" customWidth="1"/>
+    <col min="7" max="7" width="12.33203125" customWidth="1"/>
+    <col min="8" max="8" width="10.5546875" customWidth="1"/>
+    <col min="9" max="9" width="9.5546875" customWidth="1"/>
+    <col min="10" max="10" width="12.33203125" customWidth="1"/>
+    <col min="11" max="11" width="12.44140625" customWidth="1"/>
+    <col min="12" max="12" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.6640625" customWidth="1"/>
     <col min="14" max="14" width="12" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" customWidth="1"/>
-    <col min="16" max="16" width="0.140625" customWidth="1"/>
+    <col min="15" max="15" width="14.33203125" customWidth="1"/>
+    <col min="16" max="16" width="0.109375" customWidth="1"/>
     <col min="17" max="17" width="12" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
-      <c r="C1" s="155"/>
-      <c r="D1" s="155"/>
-      <c r="E1" s="179"/>
-      <c r="F1" s="179"/>
-      <c r="G1" s="179"/>
-      <c r="H1" s="179"/>
-      <c r="I1" s="179"/>
-      <c r="J1" s="179"/>
-      <c r="K1" s="179"/>
-      <c r="L1" s="179"/>
-      <c r="M1" s="179"/>
+      <c r="C1" s="154"/>
+      <c r="D1" s="154"/>
+      <c r="E1" s="175"/>
+      <c r="F1" s="175"/>
+      <c r="G1" s="175"/>
+      <c r="H1" s="175"/>
+      <c r="I1" s="175"/>
+      <c r="J1" s="175"/>
+      <c r="K1" s="175"/>
+      <c r="L1" s="175"/>
+      <c r="M1" s="175"/>
       <c r="N1" s="6"/>
       <c r="O1" s="6"/>
     </row>
-    <row r="2" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
-      <c r="C2" s="155"/>
-      <c r="D2" s="156"/>
-      <c r="E2" s="156" t="s">
-        <v>116</v>
-      </c>
-      <c r="F2" s="156"/>
-      <c r="G2" s="157">
-        <v>0</v>
-      </c>
-      <c r="H2" s="156"/>
-      <c r="I2" s="156"/>
-      <c r="J2" s="158"/>
-      <c r="K2" s="156" t="s">
-        <v>115</v>
-      </c>
-      <c r="L2" s="159">
+      <c r="C2" s="154"/>
+      <c r="D2" s="155"/>
+      <c r="E2" s="155" t="s">
+        <v>110</v>
+      </c>
+      <c r="F2" s="155"/>
+      <c r="G2" s="156">
+        <v>0</v>
+      </c>
+      <c r="H2" s="155"/>
+      <c r="I2" s="155"/>
+      <c r="J2" s="157"/>
+      <c r="K2" s="155" t="s">
+        <v>109</v>
+      </c>
+      <c r="L2" s="158">
         <v>2000000</v>
       </c>
-      <c r="M2" s="160"/>
+      <c r="M2" s="159"/>
       <c r="N2" s="43"/>
       <c r="O2" s="43"/>
       <c r="P2" s="21"/>
     </row>
-    <row r="3" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
-      <c r="C3" s="155"/>
-      <c r="D3" s="155"/>
-      <c r="E3" s="155"/>
-      <c r="F3" s="155"/>
-      <c r="G3" s="161"/>
-      <c r="H3" s="155"/>
-      <c r="I3" s="155"/>
-      <c r="J3" s="162"/>
-      <c r="K3" s="155"/>
-      <c r="L3" s="155"/>
-      <c r="M3" s="160"/>
+      <c r="C3" s="154"/>
+      <c r="D3" s="154"/>
+      <c r="E3" s="154"/>
+      <c r="F3" s="154"/>
+      <c r="G3" s="160"/>
+      <c r="H3" s="154"/>
+      <c r="I3" s="154"/>
+      <c r="J3" s="161"/>
+      <c r="K3" s="154"/>
+      <c r="L3" s="154"/>
+      <c r="M3" s="159"/>
       <c r="N3" s="43"/>
       <c r="O3" s="43"/>
       <c r="P3" s="21"/>
     </row>
-    <row r="4" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="189" t="s">
-        <v>114</v>
-      </c>
-      <c r="B4" s="190"/>
-      <c r="C4" s="190"/>
-      <c r="D4" s="190"/>
-      <c r="E4" s="190"/>
-      <c r="F4" s="190"/>
-      <c r="G4" s="190"/>
-      <c r="H4" s="190"/>
-      <c r="I4" s="190"/>
-      <c r="J4" s="190"/>
-      <c r="K4" s="190"/>
-      <c r="L4" s="190"/>
-      <c r="M4" s="190"/>
-      <c r="N4" s="190"/>
-      <c r="O4" s="190"/>
+    <row r="4" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="187" t="s">
+        <v>108</v>
+      </c>
+      <c r="B4" s="188"/>
+      <c r="C4" s="188"/>
+      <c r="D4" s="188"/>
+      <c r="E4" s="188"/>
+      <c r="F4" s="188"/>
+      <c r="G4" s="188"/>
+      <c r="H4" s="188"/>
+      <c r="I4" s="188"/>
+      <c r="J4" s="188"/>
+      <c r="K4" s="188"/>
+      <c r="L4" s="188"/>
+      <c r="M4" s="188"/>
+      <c r="N4" s="188"/>
+      <c r="O4" s="188"/>
       <c r="P4" s="21"/>
     </row>
-    <row r="5" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="190"/>
-      <c r="B5" s="190"/>
-      <c r="C5" s="190"/>
-      <c r="D5" s="190"/>
-      <c r="E5" s="190"/>
-      <c r="F5" s="190"/>
-      <c r="G5" s="190"/>
-      <c r="H5" s="190"/>
-      <c r="I5" s="190"/>
-      <c r="J5" s="190"/>
-      <c r="K5" s="190"/>
-      <c r="L5" s="190"/>
-      <c r="M5" s="190"/>
-      <c r="N5" s="190"/>
-      <c r="O5" s="190"/>
+    <row r="5" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="188"/>
+      <c r="B5" s="188"/>
+      <c r="C5" s="188"/>
+      <c r="D5" s="188"/>
+      <c r="E5" s="188"/>
+      <c r="F5" s="188"/>
+      <c r="G5" s="188"/>
+      <c r="H5" s="188"/>
+      <c r="I5" s="188"/>
+      <c r="J5" s="188"/>
+      <c r="K5" s="188"/>
+      <c r="L5" s="188"/>
+      <c r="M5" s="188"/>
+      <c r="N5" s="188"/>
+      <c r="O5" s="188"/>
       <c r="P5" s="21"/>
     </row>
-    <row r="6" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="190"/>
-      <c r="B6" s="190"/>
-      <c r="C6" s="190"/>
-      <c r="D6" s="190"/>
-      <c r="E6" s="190"/>
-      <c r="F6" s="190"/>
-      <c r="G6" s="190"/>
-      <c r="H6" s="190"/>
-      <c r="I6" s="190"/>
-      <c r="J6" s="190"/>
-      <c r="K6" s="190"/>
-      <c r="L6" s="190"/>
-      <c r="M6" s="190"/>
-      <c r="N6" s="190"/>
-      <c r="O6" s="190"/>
+    <row r="6" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="188"/>
+      <c r="B6" s="188"/>
+      <c r="C6" s="188"/>
+      <c r="D6" s="188"/>
+      <c r="E6" s="188"/>
+      <c r="F6" s="188"/>
+      <c r="G6" s="188"/>
+      <c r="H6" s="188"/>
+      <c r="I6" s="188"/>
+      <c r="J6" s="188"/>
+      <c r="K6" s="188"/>
+      <c r="L6" s="188"/>
+      <c r="M6" s="188"/>
+      <c r="N6" s="188"/>
+      <c r="O6" s="188"/>
       <c r="P6" s="21"/>
     </row>
-    <row r="7" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="190"/>
-      <c r="B7" s="190"/>
-      <c r="C7" s="190"/>
-      <c r="D7" s="190"/>
-      <c r="E7" s="190"/>
-      <c r="F7" s="190"/>
-      <c r="G7" s="190"/>
-      <c r="H7" s="190"/>
-      <c r="I7" s="190"/>
-      <c r="J7" s="190"/>
-      <c r="K7" s="190"/>
-      <c r="L7" s="190"/>
-      <c r="M7" s="190"/>
-      <c r="N7" s="190"/>
-      <c r="O7" s="190"/>
+    <row r="7" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="188"/>
+      <c r="B7" s="188"/>
+      <c r="C7" s="188"/>
+      <c r="D7" s="188"/>
+      <c r="E7" s="188"/>
+      <c r="F7" s="188"/>
+      <c r="G7" s="188"/>
+      <c r="H7" s="188"/>
+      <c r="I7" s="188"/>
+      <c r="J7" s="188"/>
+      <c r="K7" s="188"/>
+      <c r="L7" s="188"/>
+      <c r="M7" s="188"/>
+      <c r="N7" s="188"/>
+      <c r="O7" s="188"/>
       <c r="P7" s="21"/>
     </row>
-    <row r="8" spans="1:16" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="191"/>
-      <c r="B8" s="191"/>
-      <c r="C8" s="191"/>
-      <c r="D8" s="191"/>
-      <c r="E8" s="191"/>
-      <c r="F8" s="191"/>
-      <c r="G8" s="191"/>
-      <c r="H8" s="191"/>
-      <c r="I8" s="191"/>
-      <c r="J8" s="191"/>
-      <c r="K8" s="191"/>
-      <c r="L8" s="191"/>
-      <c r="M8" s="191"/>
-      <c r="N8" s="191"/>
-      <c r="O8" s="191"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" s="176" t="s">
+    <row r="8" spans="1:16" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="189"/>
+      <c r="B8" s="189"/>
+      <c r="C8" s="189"/>
+      <c r="D8" s="189"/>
+      <c r="E8" s="189"/>
+      <c r="F8" s="189"/>
+      <c r="G8" s="189"/>
+      <c r="H8" s="189"/>
+      <c r="I8" s="189"/>
+      <c r="J8" s="189"/>
+      <c r="K8" s="189"/>
+      <c r="L8" s="189"/>
+      <c r="M8" s="189"/>
+      <c r="N8" s="189"/>
+      <c r="O8" s="189"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A9" s="180" t="s">
         <v>3</v>
       </c>
       <c r="B9" s="131"/>
-      <c r="C9" s="176" t="s">
+      <c r="C9" s="180" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="176" t="s">
+      <c r="D9" s="180" t="s">
         <v>13</v>
       </c>
-      <c r="E9" s="176" t="s">
+      <c r="E9" s="180" t="s">
         <v>7</v>
       </c>
-      <c r="F9" s="180" t="s">
+      <c r="F9" s="176" t="s">
         <v>24</v>
       </c>
-      <c r="G9" s="176" t="s">
+      <c r="G9" s="180" t="s">
         <v>5</v>
       </c>
-      <c r="H9" s="184" t="s">
+      <c r="H9" s="182" t="s">
         <v>17</v>
       </c>
-      <c r="I9" s="180" t="s">
+      <c r="I9" s="176" t="s">
         <v>23</v>
       </c>
-      <c r="J9" s="180" t="s">
-        <v>95</v>
-      </c>
-      <c r="K9" s="180" t="s">
-        <v>115</v>
-      </c>
-      <c r="L9" s="187" t="s">
-        <v>116</v>
+      <c r="J9" s="176" t="s">
+        <v>89</v>
+      </c>
+      <c r="K9" s="176" t="s">
+        <v>109</v>
+      </c>
+      <c r="L9" s="185" t="s">
+        <v>110</v>
       </c>
       <c r="M9" s="47" t="s">
         <v>21</v>
       </c>
-      <c r="N9" s="182" t="s">
+      <c r="N9" s="178" t="s">
         <v>12</v>
       </c>
-      <c r="O9" s="192" t="s">
+      <c r="O9" s="190" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="178"/>
+    <row r="10" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="181"/>
       <c r="B10" s="132"/>
-      <c r="C10" s="178"/>
-      <c r="D10" s="177"/>
-      <c r="E10" s="178"/>
-      <c r="F10" s="181"/>
-      <c r="G10" s="178"/>
-      <c r="H10" s="185"/>
-      <c r="I10" s="181"/>
-      <c r="J10" s="186"/>
-      <c r="K10" s="181"/>
-      <c r="L10" s="188"/>
+      <c r="C10" s="181"/>
+      <c r="D10" s="192"/>
+      <c r="E10" s="181"/>
+      <c r="F10" s="177"/>
+      <c r="G10" s="181"/>
+      <c r="H10" s="183"/>
+      <c r="I10" s="177"/>
+      <c r="J10" s="184"/>
+      <c r="K10" s="177"/>
+      <c r="L10" s="186"/>
       <c r="M10" s="45" t="str">
         <f>RESUMEN!B8</f>
-        <v>VTO 14/11</v>
-      </c>
-      <c r="N10" s="183"/>
-      <c r="O10" s="193"/>
-    </row>
-    <row r="11" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>VTO 15/12</v>
+      </c>
+      <c r="N10" s="179"/>
+      <c r="O10" s="191"/>
+    </row>
+    <row r="11" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="48">
         <v>1</v>
       </c>
       <c r="B11" s="48" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C11" s="48" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D11" s="48"/>
       <c r="E11" s="57">
@@ -2932,15 +2967,15 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="48">
         <v>2</v>
       </c>
       <c r="B12" s="48" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C12" s="48" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D12" s="49"/>
       <c r="E12" s="57">
@@ -2990,18 +3025,18 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="48">
         <v>3</v>
       </c>
       <c r="B13" s="48" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D13" s="49" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E13" s="57">
         <v>5.4</v>
@@ -3050,18 +3085,18 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="48">
         <v>4</v>
       </c>
       <c r="B14" s="48" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C14" s="48" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D14" s="49" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E14" s="57">
         <v>6.6</v>
@@ -3110,18 +3145,18 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="48">
         <v>5</v>
       </c>
       <c r="B15" s="48" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C15" s="48" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D15" s="48" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="E15" s="57">
         <v>6.6</v>
@@ -3170,18 +3205,18 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="48">
         <v>6</v>
       </c>
       <c r="B16" s="48" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D16" s="48" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="E16" s="57">
         <v>5.4</v>
@@ -3230,18 +3265,18 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="48">
         <v>7</v>
       </c>
       <c r="B17" s="48" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C17" s="48" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D17" s="48" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="E17" s="57">
         <v>5.4</v>
@@ -3290,18 +3325,18 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="48">
         <v>8</v>
       </c>
       <c r="B18" s="48" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D18" s="49" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E18" s="57">
         <v>6.6</v>
@@ -3350,18 +3385,18 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="48">
         <v>9</v>
       </c>
       <c r="B19" s="48" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C19" s="48" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D19" s="49" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E19" s="57">
         <v>6.6</v>
@@ -3410,18 +3445,18 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="48">
         <v>10</v>
       </c>
       <c r="B20" s="48" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C20" s="48" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D20" s="49" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E20" s="57">
         <v>5.4</v>
@@ -3470,15 +3505,15 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="48">
         <v>11</v>
       </c>
       <c r="B21" s="48" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C21" s="48" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D21" s="49"/>
       <c r="E21" s="57">
@@ -3528,21 +3563,21 @@
         <v>0.10999999999999999</v>
       </c>
       <c r="Q21" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="48">
         <v>12</v>
       </c>
       <c r="B22" s="48" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D22" s="49" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E22" s="57">
         <v>6.6</v>
@@ -3591,18 +3626,18 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="48">
         <v>13</v>
       </c>
       <c r="B23" s="48" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C23" s="48" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D23" s="49" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="E23" s="57">
         <v>6.6</v>
@@ -3651,15 +3686,15 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="48">
         <v>14</v>
       </c>
       <c r="B24" s="48" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C24" s="48" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D24" s="49"/>
       <c r="E24" s="57">
@@ -3709,15 +3744,15 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="48">
         <v>15</v>
       </c>
       <c r="B25" s="48" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C25" s="48" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D25" s="49"/>
       <c r="E25" s="57">
@@ -3767,18 +3802,18 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="48">
         <v>16</v>
       </c>
       <c r="B26" s="48" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C26" s="48" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D26" s="48" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="E26" s="57">
         <v>0.7</v>
@@ -3827,15 +3862,15 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="48">
         <v>17</v>
       </c>
       <c r="B27" s="48" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C27" s="48" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D27" s="49"/>
       <c r="E27" s="57">
@@ -3885,15 +3920,15 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="28" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="48">
         <v>18</v>
       </c>
       <c r="B28" s="48" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C28" s="48" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D28" s="98"/>
       <c r="E28" s="57">
@@ -3943,15 +3978,15 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" s="48">
         <v>19</v>
       </c>
       <c r="B29" s="48" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C29" s="48" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D29" s="49"/>
       <c r="E29" s="57">
@@ -3998,18 +4033,18 @@
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" s="66">
         <v>20</v>
       </c>
       <c r="B30" s="66" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C30" s="48" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D30" s="49" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E30" s="57">
         <v>0.6</v>
@@ -4052,18 +4087,18 @@
       </c>
       <c r="P30" s="32"/>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" s="66">
         <v>21</v>
       </c>
       <c r="B31" s="66" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C31" s="50" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D31" s="49" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E31" s="57">
         <v>0.3</v>
@@ -4106,15 +4141,15 @@
       </c>
       <c r="P31" s="32"/>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32" s="67">
         <v>22</v>
       </c>
       <c r="B32" s="67" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C32" s="48" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D32" s="49"/>
       <c r="E32" s="57">
@@ -4158,18 +4193,18 @@
       </c>
       <c r="P32" s="32"/>
     </row>
-    <row r="33" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="48">
         <v>23</v>
       </c>
       <c r="B33" s="70" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C33" s="70" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D33" s="49" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E33" s="57">
         <v>0.3</v>
@@ -4212,7 +4247,7 @@
       </c>
       <c r="P33" s="32"/>
     </row>
-    <row r="34" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="72"/>
       <c r="B34" s="72"/>
       <c r="C34" s="73"/>
@@ -4262,94 +4297,99 @@
         <v>2056519.9000000001</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C35" s="38"/>
       <c r="D35" s="38"/>
     </row>
-    <row r="36" spans="1:16" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="1:16" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C37" s="168" t="str">
+    <row r="36" spans="1:16" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="37" spans="1:16" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C37" s="173" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. PORFAVOR RESPETAR LOS CENTAVOS AL ABONAR.</v>
       </c>
-      <c r="D37" s="168"/>
-      <c r="E37" s="168"/>
-      <c r="F37" s="168"/>
-      <c r="G37" s="168"/>
-      <c r="H37" s="168"/>
-      <c r="I37" s="168"/>
-      <c r="J37" s="168"/>
-      <c r="K37" s="168"/>
-      <c r="L37" s="168"/>
-      <c r="M37" s="168"/>
-    </row>
-    <row r="38" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C38" s="168"/>
-      <c r="D38" s="168"/>
-      <c r="E38" s="168"/>
-      <c r="F38" s="168"/>
-      <c r="G38" s="168"/>
-      <c r="H38" s="168"/>
-      <c r="I38" s="168"/>
-      <c r="J38" s="168"/>
-      <c r="K38" s="168"/>
-      <c r="L38" s="168"/>
-      <c r="M38" s="168"/>
-    </row>
-    <row r="39" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C39" s="168"/>
-      <c r="D39" s="168"/>
-      <c r="E39" s="168"/>
-      <c r="F39" s="168"/>
-      <c r="G39" s="168"/>
-      <c r="H39" s="168"/>
-      <c r="I39" s="168"/>
-      <c r="J39" s="168"/>
-      <c r="K39" s="168"/>
-      <c r="L39" s="168"/>
-      <c r="M39" s="168"/>
-    </row>
-    <row r="40" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C40" s="168"/>
-      <c r="D40" s="168"/>
-      <c r="E40" s="168"/>
-      <c r="F40" s="168"/>
-      <c r="G40" s="168"/>
-      <c r="H40" s="168"/>
-      <c r="I40" s="168"/>
-      <c r="J40" s="168"/>
-      <c r="K40" s="168"/>
-      <c r="L40" s="168"/>
-      <c r="M40" s="168"/>
-    </row>
-    <row r="41" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C41" s="168"/>
-      <c r="D41" s="168"/>
-      <c r="E41" s="168"/>
-      <c r="F41" s="168"/>
-      <c r="G41" s="168"/>
-      <c r="H41" s="168"/>
-      <c r="I41" s="168"/>
-      <c r="J41" s="168"/>
-      <c r="K41" s="168"/>
-      <c r="L41" s="168"/>
-      <c r="M41" s="168"/>
-    </row>
-    <row r="42" spans="1:16" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C42" s="168"/>
-      <c r="D42" s="168"/>
-      <c r="E42" s="168"/>
-      <c r="F42" s="168"/>
-      <c r="G42" s="168"/>
-      <c r="H42" s="168"/>
-      <c r="I42" s="168"/>
-      <c r="J42" s="168"/>
-      <c r="K42" s="168"/>
-      <c r="L42" s="168"/>
-      <c r="M42" s="168"/>
+      <c r="D37" s="173"/>
+      <c r="E37" s="173"/>
+      <c r="F37" s="173"/>
+      <c r="G37" s="173"/>
+      <c r="H37" s="173"/>
+      <c r="I37" s="173"/>
+      <c r="J37" s="173"/>
+      <c r="K37" s="173"/>
+      <c r="L37" s="173"/>
+      <c r="M37" s="173"/>
+    </row>
+    <row r="38" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C38" s="173"/>
+      <c r="D38" s="173"/>
+      <c r="E38" s="173"/>
+      <c r="F38" s="173"/>
+      <c r="G38" s="173"/>
+      <c r="H38" s="173"/>
+      <c r="I38" s="173"/>
+      <c r="J38" s="173"/>
+      <c r="K38" s="173"/>
+      <c r="L38" s="173"/>
+      <c r="M38" s="173"/>
+    </row>
+    <row r="39" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C39" s="173"/>
+      <c r="D39" s="173"/>
+      <c r="E39" s="173"/>
+      <c r="F39" s="173"/>
+      <c r="G39" s="173"/>
+      <c r="H39" s="173"/>
+      <c r="I39" s="173"/>
+      <c r="J39" s="173"/>
+      <c r="K39" s="173"/>
+      <c r="L39" s="173"/>
+      <c r="M39" s="173"/>
+    </row>
+    <row r="40" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C40" s="173"/>
+      <c r="D40" s="173"/>
+      <c r="E40" s="173"/>
+      <c r="F40" s="173"/>
+      <c r="G40" s="173"/>
+      <c r="H40" s="173"/>
+      <c r="I40" s="173"/>
+      <c r="J40" s="173"/>
+      <c r="K40" s="173"/>
+      <c r="L40" s="173"/>
+      <c r="M40" s="173"/>
+    </row>
+    <row r="41" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C41" s="173"/>
+      <c r="D41" s="173"/>
+      <c r="E41" s="173"/>
+      <c r="F41" s="173"/>
+      <c r="G41" s="173"/>
+      <c r="H41" s="173"/>
+      <c r="I41" s="173"/>
+      <c r="J41" s="173"/>
+      <c r="K41" s="173"/>
+      <c r="L41" s="173"/>
+      <c r="M41" s="173"/>
+    </row>
+    <row r="42" spans="1:16" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C42" s="173"/>
+      <c r="D42" s="173"/>
+      <c r="E42" s="173"/>
+      <c r="F42" s="173"/>
+      <c r="G42" s="173"/>
+      <c r="H42" s="173"/>
+      <c r="I42" s="173"/>
+      <c r="J42" s="173"/>
+      <c r="K42" s="173"/>
+      <c r="L42" s="173"/>
+      <c r="M42" s="173"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="C37:M42"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="E9:E10"/>
     <mergeCell ref="E1:M1"/>
     <mergeCell ref="I9:I10"/>
     <mergeCell ref="F9:F10"/>
@@ -4361,11 +4401,6 @@
     <mergeCell ref="L9:L10"/>
     <mergeCell ref="A4:O8"/>
     <mergeCell ref="O9:O10"/>
-    <mergeCell ref="C37:M42"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="E9:E10"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
@@ -4375,48 +4410,48 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D7123E2-E76E-40B2-9631-974509386176}">
   <dimension ref="B3:J33"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="4" customWidth="1"/>
-    <col min="5" max="5" width="21.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.5703125" customWidth="1"/>
-    <col min="7" max="7" width="24.42578125" customWidth="1"/>
+    <col min="5" max="5" width="21.6640625" customWidth="1"/>
+    <col min="6" max="6" width="4.5546875" customWidth="1"/>
+    <col min="7" max="7" width="24.44140625" customWidth="1"/>
     <col min="8" max="8" width="5" customWidth="1"/>
-    <col min="10" max="10" width="19.5703125" customWidth="1"/>
+    <col min="10" max="10" width="19.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="143" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="C3" s="143" t="s">
+        <v>91</v>
+      </c>
+      <c r="E3" s="145" t="s">
         <v>97</v>
       </c>
-      <c r="E3" s="145" t="s">
-        <v>103</v>
-      </c>
       <c r="G3" s="146" t="s">
-        <v>104</v>
-      </c>
-      <c r="I3" s="196" t="s">
-        <v>105</v>
-      </c>
-      <c r="J3" s="197"/>
-    </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="I3" s="195" t="s">
+        <v>99</v>
+      </c>
+      <c r="J3" s="196"/>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B4" s="143"/>
       <c r="C4" s="143"/>
       <c r="E4" s="143"/>
       <c r="G4" s="147"/>
-      <c r="I4" s="196"/>
-      <c r="J4" s="197"/>
-    </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I4" s="195"/>
+      <c r="J4" s="196"/>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B5" s="143">
         <v>1</v>
       </c>
       <c r="C5" s="143" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="E5" s="148">
         <v>61353.383534261804</v>
@@ -4425,18 +4460,18 @@
       <c r="G5" s="149">
         <v>61353.383534261804</v>
       </c>
-      <c r="I5" s="194">
+      <c r="I5" s="193">
         <f>E5-G5</f>
         <v>0</v>
       </c>
-      <c r="J5" s="195"/>
-    </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J5" s="194"/>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B6" s="143">
         <v>1</v>
       </c>
       <c r="C6" s="143" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="E6" s="148">
         <v>34428.700834302756</v>
@@ -4445,18 +4480,18 @@
       <c r="G6" s="149">
         <v>34428.700834302756</v>
       </c>
-      <c r="I6" s="194">
+      <c r="I6" s="193">
         <f t="shared" ref="I6:I21" si="0">E6-G6</f>
         <v>0</v>
       </c>
-      <c r="J6" s="195"/>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J6" s="194"/>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B7" s="143">
         <v>1</v>
       </c>
       <c r="C7" s="143" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E7" s="148">
         <v>14356.010802482968</v>
@@ -4465,18 +4500,18 @@
       <c r="G7" s="149">
         <v>14356.010802482968</v>
       </c>
-      <c r="I7" s="194">
+      <c r="I7" s="193">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J7" s="195"/>
-    </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J7" s="194"/>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B8" s="143">
         <v>2</v>
       </c>
       <c r="C8" s="143" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="E8" s="148">
         <v>12061.218355435631</v>
@@ -4485,18 +4520,18 @@
       <c r="G8" s="149">
         <v>12061.218355435631</v>
       </c>
-      <c r="I8" s="194">
+      <c r="I8" s="193">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J8" s="195"/>
-    </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J8" s="194"/>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B9" s="144">
         <v>2</v>
       </c>
       <c r="C9" s="144" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="E9" s="148">
         <v>53068.035404197428</v>
@@ -4505,18 +4540,18 @@
       <c r="G9" s="149">
         <v>53068.035404197428</v>
       </c>
-      <c r="I9" s="194">
+      <c r="I9" s="193">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J9" s="195"/>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J9" s="194"/>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B10" s="144">
         <v>2</v>
       </c>
       <c r="C10" s="144" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="E10" s="148">
         <v>9841.6389016527519</v>
@@ -4525,18 +4560,18 @@
       <c r="G10" s="149">
         <v>9841.6389016527519</v>
       </c>
-      <c r="I10" s="194">
+      <c r="I10" s="193">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J10" s="195"/>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J10" s="194"/>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B11" s="144">
         <v>2</v>
       </c>
       <c r="C11" s="144" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E11" s="148">
         <v>9327.3712310195588</v>
@@ -4545,18 +4580,18 @@
       <c r="G11" s="149">
         <v>9327.3712310195588</v>
       </c>
-      <c r="I11" s="194">
+      <c r="I11" s="193">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J11" s="195"/>
-    </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J11" s="194"/>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B12" s="144">
         <v>3</v>
       </c>
       <c r="C12" s="144" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="E12" s="148">
         <v>9216.1440460861631</v>
@@ -4565,18 +4600,18 @@
       <c r="G12" s="149">
         <v>9216.1440460861631</v>
       </c>
-      <c r="I12" s="194">
+      <c r="I12" s="193">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J12" s="195"/>
-    </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J12" s="194"/>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B13" s="143">
         <v>3</v>
       </c>
       <c r="C13" s="143" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="E13" s="148">
         <v>23200.609218392572</v>
@@ -4585,18 +4620,18 @@
       <c r="G13" s="149">
         <v>23200.609218392572</v>
       </c>
-      <c r="I13" s="194">
+      <c r="I13" s="193">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J13" s="195"/>
-    </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J13" s="194"/>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B14" s="144">
         <v>3</v>
       </c>
       <c r="C14" s="144" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="E14" s="148">
         <v>7781.0089492021225</v>
@@ -4605,18 +4640,18 @@
       <c r="G14" s="149">
         <v>7781.0089492021225</v>
       </c>
-      <c r="I14" s="194">
+      <c r="I14" s="193">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J14" s="195"/>
-    </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J14" s="194"/>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B15" s="144">
         <v>3</v>
       </c>
       <c r="C15" s="144" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E15" s="148">
         <v>10351.832144880002</v>
@@ -4625,18 +4660,18 @@
       <c r="G15" s="149">
         <v>10351.832144880002</v>
       </c>
-      <c r="I15" s="194">
+      <c r="I15" s="193">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J15" s="195"/>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J15" s="194"/>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B16" s="143">
         <v>4</v>
       </c>
       <c r="C16" s="143" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="E16" s="148">
         <v>49509.655303807594</v>
@@ -4645,18 +4680,18 @@
       <c r="G16" s="149">
         <v>49509.655303807594</v>
       </c>
-      <c r="I16" s="194">
+      <c r="I16" s="193">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J16" s="195"/>
-    </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J16" s="194"/>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B17" s="144">
         <v>4</v>
       </c>
       <c r="C17" s="144" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="E17" s="148">
         <v>16866.513739552778</v>
@@ -4665,18 +4700,18 @@
       <c r="G17" s="149">
         <v>16866.513739552778</v>
       </c>
-      <c r="I17" s="194">
+      <c r="I17" s="193">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J17" s="195"/>
-    </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J17" s="194"/>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B18" s="143">
         <v>4</v>
       </c>
       <c r="C18" s="143" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="E18" s="148">
         <v>24968.536052597399</v>
@@ -4685,18 +4720,18 @@
       <c r="G18" s="149">
         <v>24968.536052597399</v>
       </c>
-      <c r="I18" s="194">
+      <c r="I18" s="193">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J18" s="195"/>
-    </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J18" s="194"/>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B19" s="144">
         <v>4</v>
       </c>
       <c r="C19" s="144" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E19" s="148">
         <v>10779.178697518902</v>
@@ -4705,21 +4740,21 @@
       <c r="G19" s="149">
         <v>10779.178697518902</v>
       </c>
-      <c r="I19" s="194">
+      <c r="I19" s="193">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J19" s="195"/>
-    </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J19" s="194"/>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B20" s="143"/>
       <c r="C20" s="143"/>
       <c r="E20" s="143"/>
       <c r="G20" s="147"/>
-      <c r="I20" s="194"/>
-      <c r="J20" s="195"/>
-    </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I20" s="193"/>
+      <c r="J20" s="194"/>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B21" s="143"/>
       <c r="C21" s="143"/>
       <c r="E21" s="152">
@@ -4730,165 +4765,165 @@
         <f>SUM(G5:G20)</f>
         <v>347109.83721539041</v>
       </c>
-      <c r="I21" s="194">
+      <c r="I21" s="193">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J21" s="195"/>
-    </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J21" s="194"/>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B22" s="143" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C22" s="143">
         <v>1</v>
       </c>
-      <c r="E22" s="163">
+      <c r="E22" s="162">
         <v>723.43331893167124</v>
       </c>
-      <c r="G22" s="164">
+      <c r="G22" s="163">
         <v>723.43331893167124</v>
       </c>
-      <c r="I22" s="194">
+      <c r="I22" s="193">
         <f t="shared" ref="I22" si="1">E22-G22</f>
         <v>0</v>
       </c>
-      <c r="J22" s="195"/>
-    </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J22" s="194"/>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B23" s="143" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C23" s="143">
         <v>2</v>
       </c>
-      <c r="E23" s="163">
+      <c r="E23" s="162">
         <v>620.08570194143249</v>
       </c>
-      <c r="G23" s="164">
+      <c r="G23" s="163">
         <v>620.08570194143249</v>
       </c>
-      <c r="I23" s="194">
+      <c r="I23" s="193">
         <f t="shared" ref="I23:I31" si="2">E23-G23</f>
         <v>0</v>
       </c>
-      <c r="J23" s="195"/>
-    </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J23" s="194"/>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B24" s="143" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C24" s="143">
         <v>3</v>
       </c>
-      <c r="E24" s="163">
+      <c r="E24" s="162">
         <v>620.08570194143249</v>
       </c>
-      <c r="G24" s="164">
+      <c r="G24" s="163">
         <v>620.08570194143249</v>
       </c>
-      <c r="I24" s="194">
+      <c r="I24" s="193">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J24" s="195"/>
-    </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J24" s="194"/>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B25" s="143" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C25" s="143">
         <v>4</v>
       </c>
-      <c r="E25" s="163">
+      <c r="E25" s="162">
         <v>620.08570194143249</v>
       </c>
-      <c r="G25" s="164">
+      <c r="G25" s="163">
         <v>620.08570194143249</v>
       </c>
-      <c r="I25" s="194">
+      <c r="I25" s="193">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J25" s="195"/>
-    </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J25" s="194"/>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B26" s="143" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C26" s="143">
         <v>5</v>
       </c>
-      <c r="E26" s="163">
+      <c r="E26" s="162">
         <v>620.08570194143249</v>
       </c>
-      <c r="G26" s="164">
+      <c r="G26" s="163">
         <v>620.08570194143249</v>
       </c>
-      <c r="I26" s="194">
+      <c r="I26" s="193">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J26" s="195"/>
-    </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J26" s="194"/>
+    </row>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B27" s="143" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C27" s="143">
         <v>6</v>
       </c>
-      <c r="E27" s="163">
+      <c r="E27" s="162">
         <v>310.04285097071624</v>
       </c>
-      <c r="G27" s="164">
+      <c r="G27" s="163">
         <v>310.04285097071624</v>
       </c>
-      <c r="I27" s="194">
+      <c r="I27" s="193">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J27" s="195"/>
-    </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J27" s="194"/>
+    </row>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B28" s="143" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C28" s="143">
         <v>7</v>
       </c>
-      <c r="E28" s="163">
+      <c r="E28" s="162">
         <v>310.04285097071624</v>
       </c>
-      <c r="G28" s="164">
+      <c r="G28" s="163">
         <v>310.04285097071624</v>
       </c>
-      <c r="I28" s="194">
+      <c r="I28" s="193">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J28" s="195"/>
-    </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J28" s="194"/>
+    </row>
+    <row r="29" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B29" s="143" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C29" s="143">
         <v>8</v>
       </c>
-      <c r="E29" s="163">
+      <c r="E29" s="162">
         <v>310.04285097071624</v>
       </c>
-      <c r="G29" s="164">
+      <c r="G29" s="163">
         <v>310.04285097071624</v>
       </c>
-      <c r="I29" s="194">
+      <c r="I29" s="193">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J29" s="195"/>
-    </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J29" s="194"/>
+    </row>
+    <row r="30" spans="2:10" x14ac:dyDescent="0.3">
       <c r="E30" s="152">
         <f>SUM(E22:E29)</f>
         <v>4133.9046796095499</v>
@@ -4897,28 +4932,28 @@
         <f>SUM(G22:G29)</f>
         <v>4133.9046796095499</v>
       </c>
-      <c r="I30" s="194">
+      <c r="I30" s="193">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J30" s="195"/>
-    </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J30" s="194"/>
+    </row>
+    <row r="31" spans="2:10" x14ac:dyDescent="0.3">
       <c r="E31" s="152"/>
       <c r="G31" s="149"/>
-      <c r="I31" s="194">
+      <c r="I31" s="193">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J31" s="195"/>
-    </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="J31" s="194"/>
+    </row>
+    <row r="32" spans="2:10" x14ac:dyDescent="0.3">
       <c r="E32" s="150"/>
       <c r="G32" s="151"/>
-      <c r="I32" s="194"/>
-      <c r="J32" s="195"/>
-    </row>
-    <row r="33" spans="5:10" x14ac:dyDescent="0.25">
+      <c r="I32" s="193"/>
+      <c r="J32" s="194"/>
+    </row>
+    <row r="33" spans="5:10" x14ac:dyDescent="0.3">
       <c r="E33" s="152">
         <f>E30+E21</f>
         <v>351243.74189499998</v>
@@ -4927,14 +4962,29 @@
         <f>G21+G30</f>
         <v>351243.74189499998</v>
       </c>
-      <c r="I33" s="194">
+      <c r="I33" s="193">
         <f>E33-G33</f>
         <v>0</v>
       </c>
-      <c r="J33" s="195"/>
+      <c r="J33" s="194"/>
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="I17:J17"/>
     <mergeCell ref="I31:J31"/>
     <mergeCell ref="I32:J32"/>
     <mergeCell ref="I33:J33"/>
@@ -4951,21 +5001,6 @@
     <mergeCell ref="I22:J22"/>
     <mergeCell ref="I23:J23"/>
     <mergeCell ref="I24:J24"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="I17:J17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="portrait" r:id="rId1"/>

--- a/SALTA 1167/Noviembre/SALTA1167-Noviembre.xlsx
+++ b/SALTA 1167/Noviembre/SALTA1167-Noviembre.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\SALTA 1167\Noviembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\SALTA 1167\Noviembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F424B4EB-DF08-4CA5-8223-1874EAECCDF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B31B0D55-F426-4736-A94A-0C4199256F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -20,14 +20,14 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="2">EDESUR!$B$3:$J$35</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$O$42</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$94</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$97</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="142">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -236,9 +236,6 @@
     <t>REDONDO HECTOR</t>
   </si>
   <si>
-    <t>Pila energizer AAA - Madero Bytes SA</t>
-  </si>
-  <si>
     <t>Metrogas</t>
   </si>
   <si>
@@ -264,12 +261,6 @@
   </si>
   <si>
     <t>Gaston ibarra</t>
-  </si>
-  <si>
-    <t>Digitalizacion acta de desingnacion y rubrica del libro - Escribania Romanatti</t>
-  </si>
-  <si>
-    <t>Padron Gustavo - Contador - Gestion en ARCA - Inscripcion en ARCA</t>
   </si>
   <si>
     <t xml:space="preserve">MAIL: salta1167rc@gmail.com
@@ -292,12 +283,6 @@
     <t>Servicio de interet Claro</t>
   </si>
   <si>
-    <t xml:space="preserve">Sr cossentino - Traspaso administracion </t>
-  </si>
-  <si>
-    <t>Gastos bancarios - Mes de septiembre Administracion anterior</t>
-  </si>
-  <si>
     <t>EDESUR</t>
   </si>
   <si>
@@ -329,15 +314,6 @@
   </si>
   <si>
     <t>SALDO a PAGAR</t>
-  </si>
-  <si>
-    <t>Mp 03/10</t>
-  </si>
-  <si>
-    <t>Mp 06/10</t>
-  </si>
-  <si>
-    <t>Mp 28/10</t>
   </si>
   <si>
     <t>Daniel Leiva</t>
@@ -429,25 +405,58 @@
     <t>PERÍODO: NOVIEMBRE</t>
   </si>
   <si>
-    <t>Service de blindez or cierre defectuoso - Cerrajeria CITTA</t>
-  </si>
-  <si>
     <t>Transf 18/11</t>
   </si>
   <si>
-    <t>GF elevadores - Mantenimiento de ascensores</t>
-  </si>
-  <si>
     <t>Transf 13/11</t>
   </si>
   <si>
-    <t xml:space="preserve">Full Clean </t>
-  </si>
-  <si>
     <t>Full Clean - Servicio de limpieza</t>
   </si>
   <si>
     <t>Full Clean - Servicio de limpieza - Mes anterior</t>
+  </si>
+  <si>
+    <t>Transf 07/11</t>
+  </si>
+  <si>
+    <t>Service de blindez por cierre defectuoso - Cerrajeria CITTA</t>
+  </si>
+  <si>
+    <t>Transf 27/11</t>
+  </si>
+  <si>
+    <t>Transf 03/11</t>
+  </si>
+  <si>
+    <t>Indugar SRL - Compra de pinturas trabajo en medianera</t>
+  </si>
+  <si>
+    <t>Transf 28/11</t>
+  </si>
+  <si>
+    <t>Gastos bancarios</t>
+  </si>
+  <si>
+    <t>Bonificacion apertura de cuenta bancaria (pago de servicios)</t>
+  </si>
+  <si>
+    <t>Efectivo</t>
+  </si>
+  <si>
+    <t>GF elevadores - Mantenimiento de ascensores - Mes de septiembre</t>
+  </si>
+  <si>
+    <t>GF elevadores - Mantenimiento de ascensores - Mes de Octubre</t>
+  </si>
+  <si>
+    <t>GF elevadores - Mantenimiento de ascensores - Mes de Noviembre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cambios de porteros SUM </t>
+  </si>
+  <si>
+    <t>Transf 2/11</t>
   </si>
 </sst>
 </file>
@@ -1092,7 +1101,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="201">
+  <cellXfs count="197">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1173,7 +1182,6 @@
     </xf>
     <xf numFmtId="44" fontId="17" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="17" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="17" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="13" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="17" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1"/>
@@ -1182,7 +1190,6 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="17" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="17" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="17" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1372,34 +1379,45 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="8" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="17" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1417,12 +1435,6 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1453,9 +1465,6 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1467,12 +1476,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="8" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1838,31 +1841,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M98"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M101"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="14.6640625" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" customWidth="1"/>
+    <col min="12" max="12" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="14"/>
       <c r="B1" s="53" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C1" s="53"/>
       <c r="D1" s="53"/>
       <c r="E1" s="54"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="15"/>
       <c r="B2" s="55" t="s">
         <v>14</v>
@@ -1871,32 +1874,32 @@
       <c r="D2" s="55"/>
       <c r="E2" s="56"/>
     </row>
-    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="15"/>
-      <c r="B3" s="167" t="s">
-        <v>84</v>
-      </c>
-      <c r="C3" s="167"/>
-      <c r="D3" s="167"/>
-      <c r="E3" s="168"/>
-    </row>
-    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="169" t="s">
+        <v>81</v>
+      </c>
+      <c r="C3" s="169"/>
+      <c r="D3" s="169"/>
+      <c r="E3" s="170"/>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="75" t="s">
+      <c r="B4" s="73" t="s">
         <v>22</v>
       </c>
       <c r="C4" s="19"/>
       <c r="D4" s="19"/>
       <c r="E4" s="20"/>
     </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="C5" s="16"/>
       <c r="D5" s="55" t="s">
@@ -1904,7 +1907,7 @@
       </c>
       <c r="E5" s="17"/>
     </row>
-    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="18" t="s">
         <v>26</v>
       </c>
@@ -1915,753 +1918,776 @@
       </c>
       <c r="E6" s="20"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B8" s="172" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="C8" s="172"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B9" s="172"/>
       <c r="C9" s="172"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B10" s="172"/>
       <c r="C10" s="172"/>
     </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="171" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="B13" s="171"/>
       <c r="C13" s="171"/>
       <c r="D13" s="171"/>
       <c r="E13" s="171"/>
     </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="171"/>
       <c r="B14" s="171"/>
       <c r="C14" s="171"/>
       <c r="D14" s="171"/>
       <c r="E14" s="171"/>
     </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="171"/>
       <c r="B15" s="171"/>
       <c r="C15" s="171"/>
       <c r="D15" s="171"/>
       <c r="E15" s="171"/>
     </row>
-    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="171"/>
       <c r="B16" s="171"/>
       <c r="C16" s="171"/>
       <c r="D16" s="171"/>
       <c r="E16" s="171"/>
     </row>
-    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="12"/>
       <c r="D20" s="8"/>
       <c r="E20" s="13"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="26" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B21" s="26"/>
       <c r="C21" s="26"/>
-      <c r="D21" s="123"/>
-      <c r="E21" s="108"/>
-    </row>
-    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D21" s="121"/>
+      <c r="E21" s="106"/>
+    </row>
+    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="165" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="B22" s="166"/>
       <c r="C22" s="40"/>
-      <c r="D22" s="200">
+      <c r="D22" s="122">
         <v>431286.18</v>
       </c>
-      <c r="E22" s="137"/>
-      <c r="H22" s="97"/>
-    </row>
-    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E22" s="135" t="s">
+        <v>128</v>
+      </c>
+      <c r="H22" s="95"/>
+    </row>
+    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="165" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="B23" s="166"/>
       <c r="C23" s="40"/>
-      <c r="D23" s="200">
+      <c r="D23" s="122">
         <v>431286.18</v>
       </c>
-      <c r="E23" s="137"/>
-      <c r="H23" s="97"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E23" s="115" t="s">
+        <v>131</v>
+      </c>
+      <c r="H23" s="95"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="22" t="s">
         <v>9</v>
       </c>
       <c r="B24" s="22"/>
       <c r="C24" s="22"/>
-      <c r="D24" s="125"/>
-      <c r="E24" s="139">
-        <f>SUM(D22:D22)</f>
-        <v>431286.18</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D24" s="123"/>
+      <c r="E24" s="137">
+        <f>SUM(D22:D23)</f>
+        <v>862572.36</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="26" t="s">
         <v>18</v>
       </c>
       <c r="B25" s="22"/>
       <c r="C25" s="22"/>
-      <c r="D25" s="126"/>
-      <c r="E25" s="138"/>
-    </row>
-    <row r="26" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="169" t="s">
-        <v>83</v>
-      </c>
-      <c r="B26" s="170"/>
+      <c r="D25" s="124"/>
+      <c r="E25" s="136"/>
+    </row>
+    <row r="26" spans="1:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="173" t="s">
+        <v>80</v>
+      </c>
+      <c r="B26" s="174"/>
       <c r="C26" s="42"/>
-      <c r="D26" s="199">
+      <c r="D26" s="164">
         <v>66146</v>
       </c>
-      <c r="E26" s="110" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E26" s="108" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="22" t="s">
         <v>1</v>
       </c>
       <c r="B27" s="22"/>
       <c r="C27" s="22"/>
-      <c r="D27" s="125"/>
-      <c r="E27" s="109">
+      <c r="D27" s="123"/>
+      <c r="E27" s="107">
         <f>SUM(D26:D26)</f>
         <v>66146</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="B28" s="112"/>
-      <c r="C28" s="112"/>
-      <c r="D28" s="127"/>
-      <c r="E28" s="113"/>
-    </row>
-    <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="110"/>
+      <c r="C28" s="110"/>
+      <c r="D28" s="125"/>
+      <c r="E28" s="111"/>
+    </row>
+    <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
-      <c r="D29" s="118">
-        <v>0</v>
-      </c>
-      <c r="E29" s="117"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D29" s="116">
+        <v>0</v>
+      </c>
+      <c r="E29" s="115"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
-      <c r="D30" s="198">
+      <c r="D30" s="116">
         <v>5457.15</v>
       </c>
-      <c r="E30" s="117" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E30" s="115" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="B31" s="134"/>
+        <v>69</v>
+      </c>
+      <c r="B31" s="132"/>
       <c r="C31" s="5"/>
-      <c r="D31" s="198">
+      <c r="D31" s="116">
         <v>321318.45</v>
       </c>
-      <c r="E31" s="117" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="169" t="s">
-        <v>72</v>
-      </c>
-      <c r="B32" s="170"/>
+      <c r="E31" s="115" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="173" t="s">
+        <v>71</v>
+      </c>
+      <c r="B32" s="174"/>
       <c r="C32" s="5"/>
-      <c r="D32" s="198">
+      <c r="D32" s="116">
         <v>242436.28</v>
       </c>
-      <c r="E32" s="117" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A33" s="120" t="s">
-        <v>86</v>
-      </c>
-      <c r="B33" s="116"/>
+      <c r="E32" s="115" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="118" t="s">
+        <v>83</v>
+      </c>
+      <c r="B33" s="114"/>
       <c r="C33" s="5"/>
-      <c r="D33" s="118">
-        <v>20332.080000000002</v>
-      </c>
-      <c r="E33" s="110" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D33" s="116">
+        <v>20718.39</v>
+      </c>
+      <c r="E33" s="115" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="22" t="s">
         <v>2</v>
       </c>
       <c r="B34" s="22"/>
       <c r="C34" s="22"/>
-      <c r="D34" s="128"/>
-      <c r="E34" s="111">
+      <c r="D34" s="126"/>
+      <c r="E34" s="109">
         <f>SUM(D29:D33)</f>
-        <v>589543.96</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>589930.27</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="26"/>
       <c r="B35" s="22"/>
       <c r="C35" s="22"/>
-      <c r="D35" s="125"/>
-      <c r="E35" s="114"/>
-    </row>
-    <row r="36" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="120" t="s">
-        <v>69</v>
-      </c>
-      <c r="B36" s="116"/>
+      <c r="D35" s="123"/>
+      <c r="E35" s="112"/>
+    </row>
+    <row r="36" spans="1:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="165" t="s">
+        <v>137</v>
+      </c>
+      <c r="B36" s="166"/>
       <c r="C36" s="5"/>
-      <c r="D36" s="118">
-        <v>3320</v>
-      </c>
-      <c r="E36" s="119"/>
-    </row>
-    <row r="37" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D36" s="116">
+        <v>75000</v>
+      </c>
+      <c r="E36" s="117" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="165" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B37" s="166"/>
       <c r="C37" s="5"/>
-      <c r="D37" s="198">
+      <c r="D37" s="116">
         <v>75000</v>
       </c>
-      <c r="E37" s="119" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E37" s="117" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="165" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="B38" s="166"/>
       <c r="C38" s="5"/>
-      <c r="D38" s="197">
+      <c r="D38" s="116">
+        <v>75000</v>
+      </c>
+      <c r="E38" s="117" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="133" t="s">
+        <v>140</v>
+      </c>
+      <c r="B39" s="134"/>
+      <c r="C39" s="5"/>
+      <c r="D39" s="80">
+        <v>40000</v>
+      </c>
+      <c r="E39" s="117" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="165" t="s">
+        <v>132</v>
+      </c>
+      <c r="B40" s="166"/>
+      <c r="C40" s="5"/>
+      <c r="D40" s="80">
+        <v>779802</v>
+      </c>
+      <c r="E40" s="117" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="165" t="s">
+        <v>129</v>
+      </c>
+      <c r="B41" s="166"/>
+      <c r="C41" s="5"/>
+      <c r="D41" s="80">
         <v>90000</v>
       </c>
-      <c r="E38" s="119" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="169" t="s">
-        <v>136</v>
-      </c>
-      <c r="B39" s="170"/>
-      <c r="C39" s="5"/>
-      <c r="D39" s="82">
-        <v>35000</v>
-      </c>
-      <c r="E39" s="119"/>
-      <c r="I39" s="169"/>
-      <c r="J39" s="170"/>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A40" s="22" t="s">
+      <c r="E41" s="117" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="B40" s="26"/>
-      <c r="C40" s="26"/>
-      <c r="D40" s="25"/>
-      <c r="E40" s="109">
-        <f>SUM(D36:D39)</f>
-        <v>203320</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A41" s="26" t="s">
+      <c r="B42" s="26"/>
+      <c r="C42" s="26"/>
+      <c r="D42" s="25"/>
+      <c r="E42" s="107">
+        <f>SUM(D36:D41)</f>
+        <v>1134802</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="B41" s="26"/>
-      <c r="C41" s="26"/>
-      <c r="D41" s="123"/>
-      <c r="E41" s="108"/>
-    </row>
-    <row r="42" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="165" t="s">
+      <c r="B43" s="26"/>
+      <c r="C43" s="26"/>
+      <c r="D43" s="121"/>
+      <c r="E43" s="106"/>
+    </row>
+    <row r="44" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="165" t="s">
         <v>29</v>
       </c>
-      <c r="B42" s="166"/>
-      <c r="C42" s="40"/>
-      <c r="D42" s="124">
+      <c r="B44" s="166"/>
+      <c r="C44" s="40"/>
+      <c r="D44" s="122">
         <v>140000</v>
       </c>
-      <c r="E42" s="142"/>
-    </row>
-    <row r="43" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="135" t="s">
-        <v>87</v>
-      </c>
-      <c r="B43" s="136"/>
-      <c r="C43" s="40"/>
-      <c r="D43" s="153">
-        <v>202000</v>
-      </c>
-      <c r="E43" s="142"/>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A44" s="22" t="s">
+      <c r="E44" s="140"/>
+    </row>
+    <row r="45" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="133"/>
+      <c r="B45" s="134"/>
+      <c r="C45" s="40"/>
+      <c r="D45" s="151"/>
+      <c r="E45" s="140"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="B44" s="22"/>
-      <c r="C44" s="22"/>
-      <c r="D44" s="125"/>
-      <c r="E44" s="139">
-        <f>SUM(D42:D43)</f>
-        <v>342000</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A45" s="26" t="s">
+      <c r="B46" s="22"/>
+      <c r="C46" s="22"/>
+      <c r="D46" s="123"/>
+      <c r="E46" s="137">
+        <f>SUM(D44:D45)</f>
+        <v>140000</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="B45" s="51"/>
-      <c r="C45" s="22"/>
-      <c r="D45" s="122"/>
-      <c r="E45" s="109"/>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A46" s="5" t="s">
+      <c r="B47" s="51"/>
+      <c r="C47" s="22"/>
+      <c r="D47" s="120"/>
+      <c r="E47" s="107"/>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B46" s="5"/>
-      <c r="C46" s="5"/>
-      <c r="D46" s="118"/>
-      <c r="E46" s="115"/>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A47" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="B47" s="5"/>
-      <c r="C47" s="5"/>
-      <c r="D47" s="118">
-        <v>84679.61</v>
-      </c>
-      <c r="E47" s="30"/>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A48" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="B48" s="39"/>
-      <c r="C48" s="39"/>
-      <c r="D48" s="84"/>
-      <c r="E48" s="140">
-        <f>SUM(D46:D47)</f>
-        <v>84679.61</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A49" s="5"/>
+      <c r="B48" s="5"/>
+      <c r="C48" s="5"/>
+      <c r="D48" s="116"/>
+      <c r="E48" s="113"/>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" s="5" t="s">
+        <v>134</v>
+      </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
-      <c r="D49" s="79"/>
-      <c r="E49" s="85"/>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A50" s="23" t="s">
+      <c r="D49" s="116">
+        <f>35049.2-9-40</f>
+        <v>35000.199999999997</v>
+      </c>
+      <c r="E49" s="30"/>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="B50" s="39"/>
+      <c r="C50" s="39"/>
+      <c r="D50" s="82"/>
+      <c r="E50" s="138">
+        <f>SUM(D48:D49)</f>
+        <v>35000.199999999997</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="5"/>
+      <c r="B51" s="5"/>
+      <c r="C51" s="5"/>
+      <c r="D51" s="77"/>
+      <c r="E51" s="83"/>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="B52" s="23"/>
+      <c r="C52" s="23"/>
+      <c r="D52" s="84"/>
+      <c r="E52" s="139"/>
+    </row>
+    <row r="53" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="1"/>
+      <c r="D53" s="85"/>
+      <c r="E53" s="86"/>
+      <c r="F53" s="32"/>
+    </row>
+    <row r="54" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B54" s="9"/>
+      <c r="C54" s="4"/>
+      <c r="D54" s="87"/>
+      <c r="E54" s="88">
+        <f>(SUM(E21:E52))</f>
+        <v>2828450.83</v>
+      </c>
+      <c r="F54" s="105"/>
+      <c r="G54" s="32"/>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D55" s="85"/>
+      <c r="E55" s="85"/>
+    </row>
+    <row r="56" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D56" s="85"/>
+      <c r="E56" s="85"/>
+      <c r="H56" s="127"/>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="B57" s="11"/>
+      <c r="C57" s="12"/>
+      <c r="D57" s="89"/>
+      <c r="E57" s="90"/>
+    </row>
+    <row r="58" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="79"/>
+      <c r="B58" s="114"/>
+      <c r="C58" s="5"/>
+      <c r="D58" s="80"/>
+      <c r="E58" s="78"/>
+    </row>
+    <row r="59" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="165"/>
+      <c r="B59" s="166"/>
+      <c r="C59" s="5"/>
+      <c r="D59" s="80"/>
+      <c r="E59" s="78"/>
+    </row>
+    <row r="60" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" s="79"/>
+      <c r="B61" s="81"/>
+      <c r="C61" s="5"/>
+      <c r="D61" s="80"/>
+      <c r="E61" s="78"/>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" s="37"/>
+      <c r="B62" s="36"/>
+      <c r="C62" s="36"/>
+      <c r="D62" s="44"/>
+      <c r="E62" s="44">
+        <f>SUM(D58:D61)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="B65" s="23"/>
+      <c r="C65" s="23"/>
+      <c r="D65" s="24"/>
+      <c r="E65" s="76"/>
+    </row>
+    <row r="66" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="67" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B67" s="9"/>
+      <c r="C67" s="4"/>
+      <c r="D67" s="4"/>
+      <c r="E67" s="52">
+        <f>E62+E65</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="74" t="s">
+        <v>112</v>
+      </c>
+      <c r="B69" s="75">
+        <f>E54</f>
+        <v>2828450.83</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="74" t="s">
+        <v>113</v>
+      </c>
+      <c r="B70" s="75">
+        <f>E54-E52</f>
+        <v>2828450.83</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="74" t="s">
+        <v>114</v>
+      </c>
+      <c r="B71" s="75">
+        <f>E67-E65</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="74" t="s">
         <v>115</v>
       </c>
-      <c r="B50" s="23"/>
-      <c r="C50" s="23"/>
-      <c r="D50" s="86"/>
-      <c r="E50" s="141">
-        <f>2000000-1180129.14</f>
-        <v>819870.8600000001</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="1"/>
-      <c r="D51" s="87"/>
-      <c r="E51" s="88"/>
-      <c r="F51" s="32"/>
-    </row>
-    <row r="52" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="B52" s="9"/>
-      <c r="C52" s="4"/>
-      <c r="D52" s="89"/>
-      <c r="E52" s="90">
-        <f>(SUM(E21:E50))</f>
-        <v>2536846.6100000003</v>
-      </c>
-      <c r="F52" s="107"/>
-      <c r="G52" s="32"/>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D53" s="87"/>
-      <c r="E53" s="87"/>
-    </row>
-    <row r="54" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D54" s="87"/>
-      <c r="E54" s="87"/>
-      <c r="H54" s="129"/>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A55" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="B55" s="11"/>
-      <c r="C55" s="12"/>
-      <c r="D55" s="91"/>
-      <c r="E55" s="92"/>
-    </row>
-    <row r="56" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="169" t="s">
-        <v>79</v>
-      </c>
-      <c r="B56" s="170"/>
-      <c r="C56" s="5"/>
-      <c r="D56" s="82">
-        <v>37000</v>
-      </c>
-      <c r="E56" s="80"/>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A57" s="169" t="s">
-        <v>80</v>
-      </c>
-      <c r="B57" s="170"/>
-      <c r="C57" s="5"/>
-      <c r="D57" s="82">
-        <v>120000</v>
-      </c>
-      <c r="E57" s="80" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="165"/>
-      <c r="B58" s="166"/>
-      <c r="C58" s="5"/>
-      <c r="D58" s="82"/>
-      <c r="E58" s="80"/>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A59" s="81"/>
-      <c r="B59" s="83"/>
-      <c r="C59" s="5"/>
-      <c r="D59" s="82"/>
-      <c r="E59" s="80"/>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A60" s="37"/>
-      <c r="B60" s="36"/>
-      <c r="C60" s="36"/>
-      <c r="D60" s="44"/>
-      <c r="E60" s="44">
-        <f>SUM(D56:D59)</f>
-        <v>157000</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="62" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="63" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="23" t="s">
-        <v>114</v>
-      </c>
-      <c r="B63" s="23"/>
-      <c r="C63" s="23"/>
-      <c r="D63" s="24"/>
-      <c r="E63" s="78"/>
-    </row>
-    <row r="64" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="65" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="B65" s="9"/>
-      <c r="C65" s="4"/>
-      <c r="D65" s="4"/>
-      <c r="E65" s="52">
-        <f>E60+E63</f>
-        <v>157000</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="67" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="76" t="s">
+      <c r="B72" s="75">
+        <f>E67</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" s="29" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A74"/>
+      <c r="B74" s="31"/>
+      <c r="C74" s="28"/>
+    </row>
+    <row r="75" spans="1:5" s="29" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="97" t="s">
+        <v>116</v>
+      </c>
+      <c r="B75" s="162">
+        <v>610252.12999999989</v>
+      </c>
+      <c r="C75" s="28"/>
+      <c r="D75" s="35"/>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="42" t="s">
+        <v>109</v>
+      </c>
+      <c r="B76" s="102">
+        <f>-B70</f>
+        <v>-2828450.83</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="B77" s="102">
+        <f>B96</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="42" t="s">
+        <v>118</v>
+      </c>
+      <c r="B78" s="103">
+        <f>PRORRATEO!G34-B86</f>
+        <v>2038799.4999999998</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A79" s="42" t="s">
+        <v>135</v>
+      </c>
+      <c r="B79" s="103">
+        <f>2728.58+121218.14+160659.23+10359.2</f>
+        <v>294965.15000000002</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="104" t="s">
+        <v>25</v>
+      </c>
+      <c r="B80" s="128"/>
+    </row>
+    <row r="81" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="100" t="s">
         <v>120</v>
       </c>
-      <c r="B67" s="77">
-        <f>E52</f>
-        <v>2536846.6100000003</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="76" t="s">
+      <c r="B81" s="101">
+        <f>SUM(B75:C80)</f>
+        <v>115565.9499999996</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="98"/>
+      <c r="B82" s="98"/>
+      <c r="D82" s="32"/>
+      <c r="E82" s="31"/>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" s="97" t="s">
+        <v>117</v>
+      </c>
+      <c r="B83" s="162">
+        <v>2000000</v>
+      </c>
+      <c r="D83" s="31"/>
+      <c r="E83" s="32"/>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" s="42" t="s">
+        <v>110</v>
+      </c>
+      <c r="B84" s="102">
+        <f>-B71</f>
+        <v>0</v>
+      </c>
+      <c r="D84" s="32"/>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="B85" s="102">
+        <f>B104</f>
+        <v>0</v>
+      </c>
+      <c r="D85" s="32"/>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" s="42" t="s">
+        <v>119</v>
+      </c>
+      <c r="B86" s="103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" s="104" t="s">
+        <v>25</v>
+      </c>
+      <c r="B87" s="128"/>
+    </row>
+    <row r="88" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="100" t="s">
         <v>121</v>
       </c>
-      <c r="B68" s="77">
-        <f>E52-E50</f>
-        <v>1716975.7500000002</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="76" t="s">
-        <v>122</v>
-      </c>
-      <c r="B69" s="77">
-        <f>E65-E63</f>
-        <v>157000</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="76" t="s">
-        <v>123</v>
-      </c>
-      <c r="B70" s="77">
-        <f>E65</f>
-        <v>157000</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" s="29" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A72"/>
-      <c r="B72" s="31"/>
-      <c r="C72" s="28"/>
-    </row>
-    <row r="73" spans="1:5" s="29" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="99" t="s">
-        <v>124</v>
-      </c>
-      <c r="B73" s="164">
-        <v>-120596.37</v>
-      </c>
-      <c r="C73" s="28"/>
-      <c r="D73" s="35"/>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A74" s="42" t="s">
-        <v>117</v>
-      </c>
-      <c r="B74" s="104">
-        <f>-B68</f>
-        <v>-1716975.7500000002</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A75" s="42" t="s">
-        <v>27</v>
-      </c>
-      <c r="B75" s="104">
-        <f>B93</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A76" s="42" t="s">
-        <v>126</v>
-      </c>
-      <c r="B76" s="105">
-        <f>PRORRATEO!G34-B83</f>
-        <v>1910977.6400000001</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A77" s="106" t="s">
-        <v>25</v>
-      </c>
-      <c r="B77" s="130"/>
-    </row>
-    <row r="78" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="102" t="s">
-        <v>128</v>
-      </c>
-      <c r="B78" s="103">
-        <f>SUM(B73:C77)</f>
-        <v>73405.520000000019</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A79" s="100"/>
-      <c r="B79" s="100"/>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A80" s="99" t="s">
-        <v>125</v>
-      </c>
-      <c r="B80" s="164">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A81" s="42" t="s">
-        <v>118</v>
-      </c>
-      <c r="B81" s="104">
-        <f>-B69</f>
-        <v>-157000</v>
-      </c>
-    </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A82" s="42" t="s">
-        <v>27</v>
-      </c>
-      <c r="B82" s="104">
-        <f>B101</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A83" s="42" t="s">
-        <v>127</v>
-      </c>
-      <c r="B83" s="105">
-        <f>2157000</f>
-        <v>2157000</v>
-      </c>
-    </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A84" s="106" t="s">
-        <v>25</v>
-      </c>
-      <c r="B84" s="130"/>
-    </row>
-    <row r="85" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="102" t="s">
-        <v>129</v>
-      </c>
-      <c r="B85" s="103">
-        <f>SUM(B80:C84)</f>
+      <c r="B88" s="101">
+        <f>SUM(B83:C87)</f>
         <v>2000000</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A86" s="100"/>
-      <c r="B86" s="100"/>
-    </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A87" s="100"/>
-      <c r="B87" s="100"/>
-    </row>
-    <row r="88" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A89" s="174" t="s">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" s="98"/>
+      <c r="B89" s="98"/>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" s="98"/>
+      <c r="B90" s="98"/>
+    </row>
+    <row r="91" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" s="168" t="s">
         <v>19</v>
       </c>
-      <c r="B89" s="174"/>
-      <c r="C89" s="174"/>
-    </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A90" s="174"/>
-      <c r="B90" s="174"/>
-      <c r="C90" s="174"/>
-    </row>
-    <row r="91" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="94"/>
-      <c r="B91" s="27"/>
-      <c r="C91" s="27">
+      <c r="B92" s="168"/>
+      <c r="C92" s="168"/>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" s="168"/>
+      <c r="B93" s="168"/>
+      <c r="C93" s="168"/>
+    </row>
+    <row r="94" spans="1:5" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="92"/>
+      <c r="B94" s="27"/>
+      <c r="C94" s="27">
         <v>40000</v>
       </c>
-      <c r="E91" s="107"/>
-    </row>
-    <row r="92" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="94"/>
-      <c r="B92" s="96"/>
-      <c r="C92" s="93"/>
-      <c r="D92" s="107"/>
-    </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A93" s="33" t="s">
+      <c r="E94" s="105"/>
+    </row>
+    <row r="95" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="92"/>
+      <c r="B95" s="94"/>
+      <c r="C95" s="91"/>
+      <c r="D95" s="105"/>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="B93" s="95">
-        <f>SUM(B91:B92)</f>
-        <v>0</v>
-      </c>
-      <c r="C93" s="34"/>
-    </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="M94" s="7"/>
-    </row>
-    <row r="95" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="173"/>
-      <c r="B95" s="173"/>
-      <c r="C95" s="173"/>
-      <c r="D95" s="173"/>
-      <c r="E95" s="173"/>
-    </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A96" s="173"/>
-      <c r="B96" s="173"/>
-      <c r="C96" s="173"/>
-      <c r="D96" s="173"/>
-      <c r="E96" s="173"/>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A97" s="173"/>
-      <c r="B97" s="173"/>
-      <c r="C97" s="173"/>
-      <c r="D97" s="173"/>
-      <c r="E97" s="173"/>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A98" s="173"/>
-      <c r="B98" s="173"/>
-      <c r="C98" s="173"/>
-      <c r="D98" s="173"/>
-      <c r="E98" s="173"/>
+      <c r="B96" s="93">
+        <f>SUM(B94:B95)</f>
+        <v>0</v>
+      </c>
+      <c r="C96" s="34"/>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M97" s="7"/>
+    </row>
+    <row r="98" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="167"/>
+      <c r="B98" s="167"/>
+      <c r="C98" s="167"/>
+      <c r="D98" s="167"/>
+      <c r="E98" s="167"/>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A99" s="167"/>
+      <c r="B99" s="167"/>
+      <c r="C99" s="167"/>
+      <c r="D99" s="167"/>
+      <c r="E99" s="167"/>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A100" s="167"/>
+      <c r="B100" s="167"/>
+      <c r="C100" s="167"/>
+      <c r="D100" s="167"/>
+      <c r="E100" s="167"/>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A101" s="167"/>
+      <c r="B101" s="167"/>
+      <c r="C101" s="167"/>
+      <c r="D101" s="167"/>
+      <c r="E101" s="167"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="A42:B42"/>
+  <mergeCells count="16">
     <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A95:E98"/>
-    <mergeCell ref="A89:C90"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A37:B37"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="B3:E3"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A36:B36"/>
     <mergeCell ref="A13:E16"/>
     <mergeCell ref="B8:C10"/>
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="A32:B32"/>
     <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A98:E101"/>
+    <mergeCell ref="A92:C93"/>
+    <mergeCell ref="A59:B59"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2672,245 +2698,245 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Q42"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="4.33203125" customWidth="1"/>
-    <col min="3" max="3" width="18.5546875" customWidth="1"/>
+    <col min="1" max="2" width="4.28515625" customWidth="1"/>
+    <col min="3" max="3" width="18.5703125" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="8.44140625" customWidth="1"/>
-    <col min="6" max="6" width="14.109375" customWidth="1"/>
-    <col min="7" max="7" width="12.33203125" customWidth="1"/>
-    <col min="8" max="8" width="10.5546875" customWidth="1"/>
-    <col min="9" max="9" width="9.5546875" customWidth="1"/>
-    <col min="10" max="10" width="12.33203125" customWidth="1"/>
-    <col min="11" max="11" width="12.44140625" customWidth="1"/>
-    <col min="12" max="12" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.6640625" customWidth="1"/>
+    <col min="5" max="5" width="8.42578125" customWidth="1"/>
+    <col min="6" max="6" width="14.140625" customWidth="1"/>
+    <col min="7" max="7" width="12.28515625" customWidth="1"/>
+    <col min="8" max="8" width="10.5703125" customWidth="1"/>
+    <col min="9" max="9" width="9.5703125" customWidth="1"/>
+    <col min="10" max="10" width="12.28515625" customWidth="1"/>
+    <col min="11" max="11" width="12.42578125" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" customWidth="1"/>
     <col min="14" max="14" width="12" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="14.33203125" customWidth="1"/>
-    <col min="16" max="16" width="0.109375" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" customWidth="1"/>
+    <col min="16" max="16" width="0.140625" customWidth="1"/>
     <col min="17" max="17" width="12" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
-      <c r="C1" s="154"/>
-      <c r="D1" s="154"/>
-      <c r="E1" s="175"/>
-      <c r="F1" s="175"/>
-      <c r="G1" s="175"/>
-      <c r="H1" s="175"/>
-      <c r="I1" s="175"/>
-      <c r="J1" s="175"/>
-      <c r="K1" s="175"/>
-      <c r="L1" s="175"/>
-      <c r="M1" s="175"/>
+      <c r="C1" s="152"/>
+      <c r="D1" s="152"/>
+      <c r="E1" s="178"/>
+      <c r="F1" s="178"/>
+      <c r="G1" s="178"/>
+      <c r="H1" s="178"/>
+      <c r="I1" s="178"/>
+      <c r="J1" s="178"/>
+      <c r="K1" s="178"/>
+      <c r="L1" s="178"/>
+      <c r="M1" s="178"/>
       <c r="N1" s="6"/>
       <c r="O1" s="6"/>
     </row>
-    <row r="2" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
-      <c r="C2" s="154"/>
-      <c r="D2" s="155"/>
-      <c r="E2" s="155" t="s">
-        <v>110</v>
-      </c>
-      <c r="F2" s="155"/>
-      <c r="G2" s="156">
-        <v>0</v>
-      </c>
-      <c r="H2" s="155"/>
-      <c r="I2" s="155"/>
-      <c r="J2" s="157"/>
-      <c r="K2" s="155" t="s">
-        <v>109</v>
-      </c>
-      <c r="L2" s="158">
+      <c r="C2" s="152"/>
+      <c r="D2" s="153"/>
+      <c r="E2" s="153" t="s">
+        <v>102</v>
+      </c>
+      <c r="F2" s="153"/>
+      <c r="G2" s="154">
+        <v>0</v>
+      </c>
+      <c r="H2" s="153"/>
+      <c r="I2" s="153"/>
+      <c r="J2" s="155"/>
+      <c r="K2" s="153" t="s">
+        <v>101</v>
+      </c>
+      <c r="L2" s="156">
         <v>2000000</v>
       </c>
-      <c r="M2" s="159"/>
+      <c r="M2" s="157"/>
       <c r="N2" s="43"/>
       <c r="O2" s="43"/>
       <c r="P2" s="21"/>
     </row>
-    <row r="3" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
-      <c r="C3" s="154"/>
-      <c r="D3" s="154"/>
-      <c r="E3" s="154"/>
-      <c r="F3" s="154"/>
-      <c r="G3" s="160"/>
-      <c r="H3" s="154"/>
-      <c r="I3" s="154"/>
-      <c r="J3" s="161"/>
-      <c r="K3" s="154"/>
-      <c r="L3" s="154"/>
-      <c r="M3" s="159"/>
+      <c r="C3" s="152"/>
+      <c r="D3" s="152"/>
+      <c r="E3" s="152"/>
+      <c r="F3" s="152"/>
+      <c r="G3" s="158"/>
+      <c r="H3" s="152"/>
+      <c r="I3" s="152"/>
+      <c r="J3" s="159"/>
+      <c r="K3" s="152"/>
+      <c r="L3" s="152"/>
+      <c r="M3" s="157"/>
       <c r="N3" s="43"/>
       <c r="O3" s="43"/>
       <c r="P3" s="21"/>
     </row>
-    <row r="4" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="187" t="s">
-        <v>108</v>
-      </c>
-      <c r="B4" s="188"/>
-      <c r="C4" s="188"/>
-      <c r="D4" s="188"/>
-      <c r="E4" s="188"/>
-      <c r="F4" s="188"/>
-      <c r="G4" s="188"/>
-      <c r="H4" s="188"/>
-      <c r="I4" s="188"/>
-      <c r="J4" s="188"/>
-      <c r="K4" s="188"/>
-      <c r="L4" s="188"/>
-      <c r="M4" s="188"/>
-      <c r="N4" s="188"/>
-      <c r="O4" s="188"/>
+    <row r="4" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="188" t="s">
+        <v>100</v>
+      </c>
+      <c r="B4" s="189"/>
+      <c r="C4" s="189"/>
+      <c r="D4" s="189"/>
+      <c r="E4" s="189"/>
+      <c r="F4" s="189"/>
+      <c r="G4" s="189"/>
+      <c r="H4" s="189"/>
+      <c r="I4" s="189"/>
+      <c r="J4" s="189"/>
+      <c r="K4" s="189"/>
+      <c r="L4" s="189"/>
+      <c r="M4" s="189"/>
+      <c r="N4" s="189"/>
+      <c r="O4" s="189"/>
       <c r="P4" s="21"/>
     </row>
-    <row r="5" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="188"/>
-      <c r="B5" s="188"/>
-      <c r="C5" s="188"/>
-      <c r="D5" s="188"/>
-      <c r="E5" s="188"/>
-      <c r="F5" s="188"/>
-      <c r="G5" s="188"/>
-      <c r="H5" s="188"/>
-      <c r="I5" s="188"/>
-      <c r="J5" s="188"/>
-      <c r="K5" s="188"/>
-      <c r="L5" s="188"/>
-      <c r="M5" s="188"/>
-      <c r="N5" s="188"/>
-      <c r="O5" s="188"/>
+    <row r="5" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="189"/>
+      <c r="B5" s="189"/>
+      <c r="C5" s="189"/>
+      <c r="D5" s="189"/>
+      <c r="E5" s="189"/>
+      <c r="F5" s="189"/>
+      <c r="G5" s="189"/>
+      <c r="H5" s="189"/>
+      <c r="I5" s="189"/>
+      <c r="J5" s="189"/>
+      <c r="K5" s="189"/>
+      <c r="L5" s="189"/>
+      <c r="M5" s="189"/>
+      <c r="N5" s="189"/>
+      <c r="O5" s="189"/>
       <c r="P5" s="21"/>
     </row>
-    <row r="6" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="188"/>
-      <c r="B6" s="188"/>
-      <c r="C6" s="188"/>
-      <c r="D6" s="188"/>
-      <c r="E6" s="188"/>
-      <c r="F6" s="188"/>
-      <c r="G6" s="188"/>
-      <c r="H6" s="188"/>
-      <c r="I6" s="188"/>
-      <c r="J6" s="188"/>
-      <c r="K6" s="188"/>
-      <c r="L6" s="188"/>
-      <c r="M6" s="188"/>
-      <c r="N6" s="188"/>
-      <c r="O6" s="188"/>
+    <row r="6" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="189"/>
+      <c r="B6" s="189"/>
+      <c r="C6" s="189"/>
+      <c r="D6" s="189"/>
+      <c r="E6" s="189"/>
+      <c r="F6" s="189"/>
+      <c r="G6" s="189"/>
+      <c r="H6" s="189"/>
+      <c r="I6" s="189"/>
+      <c r="J6" s="189"/>
+      <c r="K6" s="189"/>
+      <c r="L6" s="189"/>
+      <c r="M6" s="189"/>
+      <c r="N6" s="189"/>
+      <c r="O6" s="189"/>
       <c r="P6" s="21"/>
     </row>
-    <row r="7" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="188"/>
-      <c r="B7" s="188"/>
-      <c r="C7" s="188"/>
-      <c r="D7" s="188"/>
-      <c r="E7" s="188"/>
-      <c r="F7" s="188"/>
-      <c r="G7" s="188"/>
-      <c r="H7" s="188"/>
-      <c r="I7" s="188"/>
-      <c r="J7" s="188"/>
-      <c r="K7" s="188"/>
-      <c r="L7" s="188"/>
-      <c r="M7" s="188"/>
-      <c r="N7" s="188"/>
-      <c r="O7" s="188"/>
+    <row r="7" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="189"/>
+      <c r="B7" s="189"/>
+      <c r="C7" s="189"/>
+      <c r="D7" s="189"/>
+      <c r="E7" s="189"/>
+      <c r="F7" s="189"/>
+      <c r="G7" s="189"/>
+      <c r="H7" s="189"/>
+      <c r="I7" s="189"/>
+      <c r="J7" s="189"/>
+      <c r="K7" s="189"/>
+      <c r="L7" s="189"/>
+      <c r="M7" s="189"/>
+      <c r="N7" s="189"/>
+      <c r="O7" s="189"/>
       <c r="P7" s="21"/>
     </row>
-    <row r="8" spans="1:16" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="189"/>
-      <c r="B8" s="189"/>
-      <c r="C8" s="189"/>
-      <c r="D8" s="189"/>
-      <c r="E8" s="189"/>
-      <c r="F8" s="189"/>
-      <c r="G8" s="189"/>
-      <c r="H8" s="189"/>
-      <c r="I8" s="189"/>
-      <c r="J8" s="189"/>
-      <c r="K8" s="189"/>
-      <c r="L8" s="189"/>
-      <c r="M8" s="189"/>
-      <c r="N8" s="189"/>
-      <c r="O8" s="189"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A9" s="180" t="s">
+    <row r="8" spans="1:16" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="190"/>
+      <c r="B8" s="190"/>
+      <c r="C8" s="190"/>
+      <c r="D8" s="190"/>
+      <c r="E8" s="190"/>
+      <c r="F8" s="190"/>
+      <c r="G8" s="190"/>
+      <c r="H8" s="190"/>
+      <c r="I8" s="190"/>
+      <c r="J8" s="190"/>
+      <c r="K8" s="190"/>
+      <c r="L8" s="190"/>
+      <c r="M8" s="190"/>
+      <c r="N8" s="190"/>
+      <c r="O8" s="190"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="175" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="131"/>
-      <c r="C9" s="180" t="s">
+      <c r="B9" s="129"/>
+      <c r="C9" s="175" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="180" t="s">
+      <c r="D9" s="175" t="s">
         <v>13</v>
       </c>
-      <c r="E9" s="180" t="s">
+      <c r="E9" s="175" t="s">
         <v>7</v>
       </c>
-      <c r="F9" s="176" t="s">
+      <c r="F9" s="179" t="s">
         <v>24</v>
       </c>
-      <c r="G9" s="180" t="s">
+      <c r="G9" s="175" t="s">
         <v>5</v>
       </c>
-      <c r="H9" s="182" t="s">
+      <c r="H9" s="183" t="s">
         <v>17</v>
       </c>
-      <c r="I9" s="176" t="s">
+      <c r="I9" s="179" t="s">
         <v>23</v>
       </c>
-      <c r="J9" s="176" t="s">
-        <v>89</v>
-      </c>
-      <c r="K9" s="176" t="s">
-        <v>109</v>
-      </c>
-      <c r="L9" s="185" t="s">
-        <v>110</v>
+      <c r="J9" s="179" t="s">
+        <v>84</v>
+      </c>
+      <c r="K9" s="179" t="s">
+        <v>101</v>
+      </c>
+      <c r="L9" s="186" t="s">
+        <v>102</v>
       </c>
       <c r="M9" s="47" t="s">
         <v>21</v>
       </c>
-      <c r="N9" s="178" t="s">
+      <c r="N9" s="181" t="s">
         <v>12</v>
       </c>
-      <c r="O9" s="190" t="s">
+      <c r="O9" s="191" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="181"/>
-      <c r="B10" s="132"/>
-      <c r="C10" s="181"/>
-      <c r="D10" s="192"/>
-      <c r="E10" s="181"/>
-      <c r="F10" s="177"/>
-      <c r="G10" s="181"/>
-      <c r="H10" s="183"/>
-      <c r="I10" s="177"/>
-      <c r="J10" s="184"/>
-      <c r="K10" s="177"/>
-      <c r="L10" s="186"/>
+    <row r="10" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="177"/>
+      <c r="B10" s="130"/>
+      <c r="C10" s="177"/>
+      <c r="D10" s="176"/>
+      <c r="E10" s="177"/>
+      <c r="F10" s="180"/>
+      <c r="G10" s="177"/>
+      <c r="H10" s="184"/>
+      <c r="I10" s="180"/>
+      <c r="J10" s="185"/>
+      <c r="K10" s="180"/>
+      <c r="L10" s="187"/>
       <c r="M10" s="45" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 15/12</v>
       </c>
-      <c r="N10" s="179"/>
-      <c r="O10" s="191"/>
-    </row>
-    <row r="11" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N10" s="182"/>
+      <c r="O10" s="192"/>
+    </row>
+    <row r="11" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="48">
         <v>1</v>
       </c>
@@ -2925,49 +2951,49 @@
         <v>12</v>
       </c>
       <c r="F11" s="58">
-        <v>495807</v>
-      </c>
-      <c r="G11" s="60">
-        <f>530667-G27-G28</f>
-        <v>495867</v>
-      </c>
-      <c r="H11" s="61">
+        <v>239940.01</v>
+      </c>
+      <c r="G11" s="59">
+        <f>271858-G27-G28</f>
+        <v>247857.65</v>
+      </c>
+      <c r="H11" s="60">
         <f t="shared" ref="H11:H33" si="0">F11-G11</f>
-        <v>-60</v>
-      </c>
-      <c r="I11" s="61">
+        <v>-7917.6399999999849</v>
+      </c>
+      <c r="I11" s="60">
         <f>IF(H11&gt;0,H11*3%,0)</f>
         <v>0</v>
       </c>
-      <c r="J11" s="62">
+      <c r="J11" s="61">
         <f>EDESUR!I5</f>
         <v>0</v>
       </c>
-      <c r="K11" s="121">
+      <c r="K11" s="119">
         <f>L$2*E11/100</f>
         <v>240000</v>
       </c>
-      <c r="L11" s="121">
+      <c r="L11" s="119">
         <f>G$2*E11/100</f>
         <v>0</v>
       </c>
-      <c r="M11" s="63">
+      <c r="M11" s="62">
         <f>ROUND(SUM(H11:L11),0) + P11</f>
-        <v>239940.01</v>
-      </c>
-      <c r="N11" s="64">
+        <v>232082.01</v>
+      </c>
+      <c r="N11" s="63">
         <f>ROUND(M11*6% + M11,0) + P11</f>
-        <v>254336.01</v>
-      </c>
-      <c r="O11" s="65">
+        <v>246007.01</v>
+      </c>
+      <c r="O11" s="64">
         <f>ROUND(M11*3%,0) + M11</f>
-        <v>247138.01</v>
+        <v>239044.01</v>
       </c>
       <c r="P11" s="32">
         <v>0.01</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="48">
         <v>2</v>
       </c>
@@ -2982,41 +3008,41 @@
         <v>6.6</v>
       </c>
       <c r="F12" s="58">
-        <v>230445</v>
-      </c>
-      <c r="G12" s="60">
+        <v>132000.01999999999</v>
+      </c>
+      <c r="G12" s="59">
         <f>F12</f>
-        <v>230445</v>
-      </c>
-      <c r="H12" s="61">
+        <v>132000.01999999999</v>
+      </c>
+      <c r="H12" s="60">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I12" s="61">
+      <c r="I12" s="60">
         <f t="shared" ref="I12:I33" si="1">IF(H12&gt;0,H12*3%,0)</f>
         <v>0</v>
       </c>
-      <c r="J12" s="62">
+      <c r="J12" s="61">
         <f>EDESUR!I6</f>
         <v>0</v>
       </c>
-      <c r="K12" s="121">
+      <c r="K12" s="119">
         <f t="shared" ref="K12:K33" si="2">L$2*E12/100</f>
         <v>132000</v>
       </c>
-      <c r="L12" s="121">
+      <c r="L12" s="119">
         <f t="shared" ref="L12:L33" si="3">G$2*E12/100</f>
         <v>0</v>
       </c>
-      <c r="M12" s="63">
+      <c r="M12" s="62">
         <f t="shared" ref="M12:M33" si="4">ROUND(SUM(H12:L12),0) + P12</f>
         <v>132000.01999999999</v>
       </c>
-      <c r="N12" s="64">
+      <c r="N12" s="63">
         <f t="shared" ref="N12:N28" si="5">ROUND(M12*6% + M12,0) + P12</f>
         <v>139920.01999999999</v>
       </c>
-      <c r="O12" s="65">
+      <c r="O12" s="64">
         <f t="shared" ref="O12:O33" si="6">ROUND(M12*3%,0) + M12</f>
         <v>135960.01999999999</v>
       </c>
@@ -3025,7 +3051,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="48">
         <v>3</v>
       </c>
@@ -3036,47 +3062,47 @@
         <v>35</v>
       </c>
       <c r="D13" s="49" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E13" s="57">
         <v>5.4</v>
       </c>
       <c r="F13" s="58">
-        <v>183797</v>
-      </c>
-      <c r="G13" s="60">
+        <v>108000.03</v>
+      </c>
+      <c r="G13" s="59">
         <f>F13</f>
-        <v>183797</v>
-      </c>
-      <c r="H13" s="61">
+        <v>108000.03</v>
+      </c>
+      <c r="H13" s="60">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I13" s="61">
+      <c r="I13" s="60">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J13" s="62">
+      <c r="J13" s="61">
         <f>EDESUR!I7</f>
         <v>0</v>
       </c>
-      <c r="K13" s="121">
+      <c r="K13" s="119">
         <f t="shared" si="2"/>
         <v>108000</v>
       </c>
-      <c r="L13" s="121">
+      <c r="L13" s="119">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M13" s="63">
+      <c r="M13" s="62">
         <f t="shared" si="4"/>
         <v>108000.03</v>
       </c>
-      <c r="N13" s="64">
+      <c r="N13" s="63">
         <f t="shared" si="5"/>
         <v>114480.03</v>
       </c>
-      <c r="O13" s="65">
+      <c r="O13" s="64">
         <f t="shared" si="6"/>
         <v>111240.03</v>
       </c>
@@ -3085,7 +3111,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="48">
         <v>4</v>
       </c>
@@ -3096,56 +3122,56 @@
         <v>37</v>
       </c>
       <c r="D14" s="49" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E14" s="57">
         <v>6.6</v>
       </c>
       <c r="F14" s="58">
-        <v>206119</v>
-      </c>
-      <c r="G14" s="60">
-        <f>322065.64-115947</f>
-        <v>206118.64</v>
-      </c>
-      <c r="H14" s="61">
+        <v>132000.04</v>
+      </c>
+      <c r="G14" s="59">
+        <f>134300</f>
+        <v>134300</v>
+      </c>
+      <c r="H14" s="60">
         <f t="shared" si="0"/>
-        <v>0.35999999998603016</v>
-      </c>
-      <c r="I14" s="61">
+        <v>-2299.9599999999919</v>
+      </c>
+      <c r="I14" s="60">
         <f t="shared" si="1"/>
-        <v>1.0799999999580905E-2</v>
-      </c>
-      <c r="J14" s="62">
+        <v>0</v>
+      </c>
+      <c r="J14" s="61">
         <f>EDESUR!I8</f>
         <v>0</v>
       </c>
-      <c r="K14" s="121">
+      <c r="K14" s="119">
         <f t="shared" si="2"/>
         <v>132000</v>
       </c>
-      <c r="L14" s="121">
+      <c r="L14" s="119">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M14" s="63">
+      <c r="M14" s="62">
         <f t="shared" si="4"/>
-        <v>132000.04</v>
-      </c>
-      <c r="N14" s="64">
+        <v>129700.04</v>
+      </c>
+      <c r="N14" s="63">
         <f t="shared" si="5"/>
-        <v>139920.04</v>
-      </c>
-      <c r="O14" s="65">
+        <v>137482.04</v>
+      </c>
+      <c r="O14" s="64">
         <f t="shared" si="6"/>
-        <v>135960.04</v>
+        <v>133591.03999999998</v>
       </c>
       <c r="P14" s="32">
         <f t="shared" si="7"/>
         <v>0.04</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="48">
         <v>5</v>
       </c>
@@ -3156,47 +3182,47 @@
         <v>39</v>
       </c>
       <c r="D15" s="48" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="E15" s="57">
         <v>6.6</v>
       </c>
       <c r="F15" s="58">
-        <v>301901</v>
-      </c>
-      <c r="G15" s="60">
-        <f>F15</f>
-        <v>301901</v>
-      </c>
-      <c r="H15" s="61">
+        <v>132000.04999999999</v>
+      </c>
+      <c r="G15" s="59">
+        <f t="shared" ref="G15:G19" si="8">F15</f>
+        <v>132000.04999999999</v>
+      </c>
+      <c r="H15" s="60">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I15" s="61">
+      <c r="I15" s="60">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J15" s="62">
+      <c r="J15" s="61">
         <f>EDESUR!I9</f>
         <v>0</v>
       </c>
-      <c r="K15" s="121">
+      <c r="K15" s="119">
         <f t="shared" si="2"/>
         <v>132000</v>
       </c>
-      <c r="L15" s="121">
+      <c r="L15" s="119">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M15" s="63">
+      <c r="M15" s="62">
         <f t="shared" si="4"/>
         <v>132000.04999999999</v>
       </c>
-      <c r="N15" s="64">
+      <c r="N15" s="63">
         <f t="shared" si="5"/>
         <v>139920.04999999999</v>
       </c>
-      <c r="O15" s="65">
+      <c r="O15" s="64">
         <f t="shared" si="6"/>
         <v>135960.04999999999</v>
       </c>
@@ -3205,7 +3231,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="48">
         <v>6</v>
       </c>
@@ -3216,47 +3242,47 @@
         <v>41</v>
       </c>
       <c r="D16" s="48" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="E16" s="57">
         <v>5.4</v>
       </c>
       <c r="F16" s="58">
-        <v>193307</v>
-      </c>
-      <c r="G16" s="60">
-        <f>F16</f>
-        <v>193307</v>
-      </c>
-      <c r="H16" s="61">
+        <v>108000.06</v>
+      </c>
+      <c r="G16" s="59">
+        <f t="shared" si="8"/>
+        <v>108000.06</v>
+      </c>
+      <c r="H16" s="60">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I16" s="61">
+      <c r="I16" s="60">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J16" s="62">
+      <c r="J16" s="61">
         <f>EDESUR!I10</f>
         <v>0</v>
       </c>
-      <c r="K16" s="121">
+      <c r="K16" s="119">
         <f t="shared" si="2"/>
         <v>108000</v>
       </c>
-      <c r="L16" s="121">
+      <c r="L16" s="119">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M16" s="63">
+      <c r="M16" s="62">
         <f t="shared" si="4"/>
         <v>108000.06</v>
       </c>
-      <c r="N16" s="64">
+      <c r="N16" s="63">
         <f t="shared" si="5"/>
         <v>114480.06</v>
       </c>
-      <c r="O16" s="65">
+      <c r="O16" s="64">
         <f t="shared" si="6"/>
         <v>111240.06</v>
       </c>
@@ -3265,7 +3291,7 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="48">
         <v>7</v>
       </c>
@@ -3276,47 +3302,47 @@
         <v>43</v>
       </c>
       <c r="D17" s="48" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="E17" s="57">
         <v>5.4</v>
       </c>
       <c r="F17" s="58">
-        <v>287266</v>
-      </c>
-      <c r="G17" s="60">
-        <f>171318+115948</f>
-        <v>287266</v>
-      </c>
-      <c r="H17" s="61">
+        <v>108000.07</v>
+      </c>
+      <c r="G17" s="59">
+        <f t="shared" si="8"/>
+        <v>108000.07</v>
+      </c>
+      <c r="H17" s="60">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I17" s="61">
+      <c r="I17" s="60">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J17" s="62">
+      <c r="J17" s="61">
         <f>EDESUR!I11</f>
         <v>0</v>
       </c>
-      <c r="K17" s="121">
+      <c r="K17" s="119">
         <f t="shared" si="2"/>
         <v>108000</v>
       </c>
-      <c r="L17" s="121">
+      <c r="L17" s="119">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M17" s="63">
+      <c r="M17" s="62">
         <f t="shared" si="4"/>
         <v>108000.07</v>
       </c>
-      <c r="N17" s="64">
+      <c r="N17" s="63">
         <f t="shared" si="5"/>
         <v>114480.07</v>
       </c>
-      <c r="O17" s="65">
+      <c r="O17" s="64">
         <f t="shared" si="6"/>
         <v>111240.07</v>
       </c>
@@ -3325,7 +3351,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="48">
         <v>8</v>
       </c>
@@ -3336,47 +3362,47 @@
         <v>45</v>
       </c>
       <c r="D18" s="49" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E18" s="57">
         <v>6.6</v>
       </c>
       <c r="F18" s="58">
-        <v>274735</v>
-      </c>
-      <c r="G18" s="60">
-        <f>F18</f>
-        <v>274735</v>
-      </c>
-      <c r="H18" s="61">
+        <v>132000.07999999999</v>
+      </c>
+      <c r="G18" s="59">
+        <f t="shared" si="8"/>
+        <v>132000.07999999999</v>
+      </c>
+      <c r="H18" s="60">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I18" s="61">
+      <c r="I18" s="60">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J18" s="62">
+      <c r="J18" s="61">
         <f>EDESUR!I12</f>
         <v>0</v>
       </c>
-      <c r="K18" s="121">
+      <c r="K18" s="119">
         <f t="shared" si="2"/>
         <v>132000</v>
       </c>
-      <c r="L18" s="121">
+      <c r="L18" s="119">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M18" s="63">
+      <c r="M18" s="62">
         <f t="shared" si="4"/>
         <v>132000.07999999999</v>
       </c>
-      <c r="N18" s="64">
+      <c r="N18" s="63">
         <f t="shared" si="5"/>
         <v>139920.07999999999</v>
       </c>
-      <c r="O18" s="65">
+      <c r="O18" s="64">
         <f t="shared" si="6"/>
         <v>135960.07999999999</v>
       </c>
@@ -3385,7 +3411,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="48">
         <v>9</v>
       </c>
@@ -3396,47 +3422,47 @@
         <v>47</v>
       </c>
       <c r="D19" s="49" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E19" s="57">
         <v>6.6</v>
       </c>
       <c r="F19" s="58">
-        <v>228179</v>
-      </c>
-      <c r="G19" s="60">
-        <f>219377+8802</f>
-        <v>228179</v>
-      </c>
-      <c r="H19" s="61">
+        <v>132000.09</v>
+      </c>
+      <c r="G19" s="59">
+        <f t="shared" si="8"/>
+        <v>132000.09</v>
+      </c>
+      <c r="H19" s="60">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I19" s="61">
+      <c r="I19" s="60">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J19" s="62">
+      <c r="J19" s="61">
         <f>EDESUR!I13</f>
         <v>0</v>
       </c>
-      <c r="K19" s="121">
+      <c r="K19" s="119">
         <f t="shared" si="2"/>
         <v>132000</v>
       </c>
-      <c r="L19" s="121">
+      <c r="L19" s="119">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M19" s="63">
+      <c r="M19" s="62">
         <f t="shared" si="4"/>
         <v>132000.09</v>
       </c>
-      <c r="N19" s="64">
+      <c r="N19" s="63">
         <f t="shared" si="5"/>
         <v>139920.09</v>
       </c>
-      <c r="O19" s="65">
+      <c r="O19" s="64">
         <f t="shared" si="6"/>
         <v>135960.09</v>
       </c>
@@ -3445,7 +3471,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="48">
         <v>10</v>
       </c>
@@ -3456,56 +3482,56 @@
         <v>49</v>
       </c>
       <c r="D20" s="49" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E20" s="57">
         <v>5.4</v>
       </c>
       <c r="F20" s="58">
-        <v>269046</v>
-      </c>
-      <c r="G20" s="60">
-        <f>286548-G31-8802+3320</f>
-        <v>272366</v>
-      </c>
-      <c r="H20" s="61">
+        <v>104680.1</v>
+      </c>
+      <c r="G20" s="59">
+        <f>F20+40000</f>
+        <v>144680.1</v>
+      </c>
+      <c r="H20" s="60">
         <f t="shared" si="0"/>
-        <v>-3320</v>
-      </c>
-      <c r="I20" s="61">
+        <v>-40000</v>
+      </c>
+      <c r="I20" s="60">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J20" s="62">
+      <c r="J20" s="61">
         <f>EDESUR!I14</f>
         <v>0</v>
       </c>
-      <c r="K20" s="121">
+      <c r="K20" s="119">
         <f t="shared" si="2"/>
         <v>108000</v>
       </c>
-      <c r="L20" s="121">
+      <c r="L20" s="119">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M20" s="63">
+      <c r="M20" s="62">
         <f t="shared" si="4"/>
-        <v>104680.1</v>
-      </c>
-      <c r="N20" s="64">
+        <v>68000.100000000006</v>
+      </c>
+      <c r="N20" s="63">
         <f t="shared" si="5"/>
-        <v>110961.1</v>
-      </c>
-      <c r="O20" s="65">
+        <v>72080.100000000006</v>
+      </c>
+      <c r="O20" s="64">
         <f t="shared" si="6"/>
-        <v>107820.1</v>
+        <v>70040.100000000006</v>
       </c>
       <c r="P20" s="32">
         <f t="shared" si="7"/>
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="48">
         <v>11</v>
       </c>
@@ -3520,41 +3546,41 @@
         <v>5.4</v>
       </c>
       <c r="F21" s="58">
-        <v>169635</v>
-      </c>
-      <c r="G21" s="60">
-        <f>178335-G32</f>
-        <v>169635</v>
-      </c>
-      <c r="H21" s="61">
+        <v>108000.11</v>
+      </c>
+      <c r="G21" s="59">
+        <f>114000.11-G32</f>
+        <v>108000.11</v>
+      </c>
+      <c r="H21" s="60">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I21" s="61">
+      <c r="I21" s="60">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J21" s="62">
+      <c r="J21" s="61">
         <f>EDESUR!I15</f>
         <v>0</v>
       </c>
-      <c r="K21" s="121">
+      <c r="K21" s="119">
         <f t="shared" si="2"/>
         <v>108000</v>
       </c>
-      <c r="L21" s="121">
+      <c r="L21" s="119">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M21" s="63">
+      <c r="M21" s="62">
         <f t="shared" si="4"/>
         <v>108000.11</v>
       </c>
-      <c r="N21" s="64">
+      <c r="N21" s="63">
         <f t="shared" si="5"/>
         <v>114480.11</v>
       </c>
-      <c r="O21" s="65">
+      <c r="O21" s="64">
         <f t="shared" si="6"/>
         <v>111240.11</v>
       </c>
@@ -3563,10 +3589,10 @@
         <v>0.10999999999999999</v>
       </c>
       <c r="Q21" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="48">
         <v>12</v>
       </c>
@@ -3577,47 +3603,47 @@
         <v>53</v>
       </c>
       <c r="D22" s="49" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E22" s="57">
         <v>6.6</v>
       </c>
       <c r="F22" s="58">
-        <v>226859</v>
-      </c>
-      <c r="G22" s="60">
+        <v>132000.12</v>
+      </c>
+      <c r="G22" s="59">
         <f>F22</f>
-        <v>226859</v>
-      </c>
-      <c r="H22" s="61">
+        <v>132000.12</v>
+      </c>
+      <c r="H22" s="60">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I22" s="61">
+      <c r="I22" s="60">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J22" s="62">
+      <c r="J22" s="61">
         <f>EDESUR!I16</f>
         <v>0</v>
       </c>
-      <c r="K22" s="121">
+      <c r="K22" s="119">
         <f t="shared" si="2"/>
         <v>132000</v>
       </c>
-      <c r="L22" s="121">
+      <c r="L22" s="119">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M22" s="63">
+      <c r="M22" s="62">
         <f t="shared" si="4"/>
         <v>132000.12</v>
       </c>
-      <c r="N22" s="64">
+      <c r="N22" s="63">
         <f t="shared" si="5"/>
         <v>139920.12</v>
       </c>
-      <c r="O22" s="65">
+      <c r="O22" s="64">
         <f t="shared" si="6"/>
         <v>135960.12</v>
       </c>
@@ -3626,7 +3652,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="48">
         <v>13</v>
       </c>
@@ -3637,56 +3663,56 @@
         <v>55</v>
       </c>
       <c r="D23" s="49" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="E23" s="57">
         <v>6.6</v>
       </c>
       <c r="F23" s="58">
-        <v>236320</v>
-      </c>
-      <c r="G23" s="60">
-        <f>F23</f>
-        <v>236320</v>
-      </c>
-      <c r="H23" s="61">
+        <v>132000.13</v>
+      </c>
+      <c r="G23" s="59">
+        <f>135960.13</f>
+        <v>135960.13</v>
+      </c>
+      <c r="H23" s="60">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I23" s="61">
+        <v>-3960</v>
+      </c>
+      <c r="I23" s="60">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J23" s="62">
+      <c r="J23" s="61">
         <f>EDESUR!I17</f>
         <v>0</v>
       </c>
-      <c r="K23" s="121">
+      <c r="K23" s="119">
         <f t="shared" si="2"/>
         <v>132000</v>
       </c>
-      <c r="L23" s="121">
+      <c r="L23" s="119">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M23" s="63">
+      <c r="M23" s="62">
         <f t="shared" si="4"/>
-        <v>132000.13</v>
-      </c>
-      <c r="N23" s="64">
+        <v>128040.13</v>
+      </c>
+      <c r="N23" s="63">
         <f t="shared" si="5"/>
-        <v>139920.13</v>
-      </c>
-      <c r="O23" s="65">
+        <v>135723.13</v>
+      </c>
+      <c r="O23" s="64">
         <f t="shared" si="6"/>
-        <v>135960.13</v>
+        <v>131881.13</v>
       </c>
       <c r="P23" s="32">
         <f t="shared" si="7"/>
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="48">
         <v>14</v>
       </c>
@@ -3701,41 +3727,41 @@
         <v>5.4</v>
       </c>
       <c r="F24" s="58">
-        <v>337128</v>
-      </c>
-      <c r="G24" s="60">
+        <v>108000.14</v>
+      </c>
+      <c r="G24" s="59">
         <f>F24</f>
-        <v>337128</v>
-      </c>
-      <c r="H24" s="61">
+        <v>108000.14</v>
+      </c>
+      <c r="H24" s="60">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I24" s="61">
+      <c r="I24" s="60">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J24" s="62">
+      <c r="J24" s="61">
         <f>EDESUR!I18</f>
         <v>0</v>
       </c>
-      <c r="K24" s="121">
+      <c r="K24" s="119">
         <f t="shared" si="2"/>
         <v>108000</v>
       </c>
-      <c r="L24" s="121">
+      <c r="L24" s="119">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M24" s="63">
+      <c r="M24" s="62">
         <f t="shared" si="4"/>
         <v>108000.14</v>
       </c>
-      <c r="N24" s="64">
+      <c r="N24" s="63">
         <f t="shared" si="5"/>
         <v>114480.14</v>
       </c>
-      <c r="O24" s="65">
+      <c r="O24" s="64">
         <f t="shared" si="6"/>
         <v>111240.14</v>
       </c>
@@ -3744,7 +3770,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="48">
         <v>15</v>
       </c>
@@ -3759,41 +3785,41 @@
         <v>5.4</v>
       </c>
       <c r="F25" s="58">
-        <v>308054</v>
-      </c>
-      <c r="G25" s="60">
+        <v>108000.15</v>
+      </c>
+      <c r="G25" s="59">
         <f>F25</f>
-        <v>308054</v>
-      </c>
-      <c r="H25" s="61">
+        <v>108000.15</v>
+      </c>
+      <c r="H25" s="60">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I25" s="61">
+      <c r="I25" s="60">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J25" s="62">
+      <c r="J25" s="61">
         <f>EDESUR!I19</f>
         <v>0</v>
       </c>
-      <c r="K25" s="121">
+      <c r="K25" s="119">
         <f t="shared" si="2"/>
         <v>108000</v>
       </c>
-      <c r="L25" s="121">
+      <c r="L25" s="119">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M25" s="63">
+      <c r="M25" s="62">
         <f t="shared" si="4"/>
         <v>108000.15</v>
       </c>
-      <c r="N25" s="64">
+      <c r="N25" s="63">
         <f t="shared" si="5"/>
         <v>114480.15</v>
       </c>
-      <c r="O25" s="65">
+      <c r="O25" s="64">
         <f t="shared" si="6"/>
         <v>111240.15</v>
       </c>
@@ -3802,7 +3828,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="48">
         <v>16</v>
       </c>
@@ -3813,47 +3839,47 @@
         <v>41</v>
       </c>
       <c r="D26" s="48" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="E26" s="57">
         <v>0.7</v>
       </c>
       <c r="F26" s="58">
-        <v>20300</v>
-      </c>
-      <c r="G26" s="60">
+        <v>14000.16</v>
+      </c>
+      <c r="G26" s="59">
         <f>F26</f>
-        <v>20300</v>
-      </c>
-      <c r="H26" s="61">
+        <v>14000.16</v>
+      </c>
+      <c r="H26" s="60">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I26" s="61">
+      <c r="I26" s="60">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J26" s="62">
+      <c r="J26" s="61">
         <f>EDESUR!I22</f>
         <v>0</v>
       </c>
-      <c r="K26" s="121">
+      <c r="K26" s="119">
         <f t="shared" si="2"/>
         <v>14000</v>
       </c>
-      <c r="L26" s="121">
+      <c r="L26" s="119">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M26" s="63">
+      <c r="M26" s="62">
         <f t="shared" si="4"/>
         <v>14000.16</v>
       </c>
-      <c r="N26" s="64">
+      <c r="N26" s="63">
         <f t="shared" si="5"/>
         <v>14840.16</v>
       </c>
-      <c r="O26" s="65">
+      <c r="O26" s="64">
         <f t="shared" si="6"/>
         <v>14420.16</v>
       </c>
@@ -3862,7 +3888,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="48">
         <v>17</v>
       </c>
@@ -3877,41 +3903,41 @@
         <v>0.6</v>
       </c>
       <c r="F27" s="59">
-        <v>17400</v>
-      </c>
-      <c r="G27" s="60">
-        <f t="shared" ref="G27:G30" si="8">F27</f>
-        <v>17400</v>
-      </c>
-      <c r="H27" s="61">
+        <v>12000.17</v>
+      </c>
+      <c r="G27" s="59">
+        <f t="shared" ref="G27:G29" si="9">F27</f>
+        <v>12000.17</v>
+      </c>
+      <c r="H27" s="60">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I27" s="61">
+      <c r="I27" s="60">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J27" s="62">
+      <c r="J27" s="61">
         <f>EDESUR!I21</f>
         <v>0</v>
       </c>
-      <c r="K27" s="121">
+      <c r="K27" s="119">
         <f t="shared" si="2"/>
         <v>12000</v>
       </c>
-      <c r="L27" s="121">
+      <c r="L27" s="119">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M27" s="63">
+      <c r="M27" s="62">
         <f t="shared" si="4"/>
         <v>12000.17</v>
       </c>
-      <c r="N27" s="64">
+      <c r="N27" s="63">
         <f t="shared" si="5"/>
         <v>12720.17</v>
       </c>
-      <c r="O27" s="65">
+      <c r="O27" s="64">
         <f t="shared" si="6"/>
         <v>12360.17</v>
       </c>
@@ -3920,7 +3946,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="28" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="48">
         <v>18</v>
       </c>
@@ -3930,46 +3956,46 @@
       <c r="C28" s="48" t="s">
         <v>31</v>
       </c>
-      <c r="D28" s="98"/>
+      <c r="D28" s="96"/>
       <c r="E28" s="57">
         <v>0.6</v>
       </c>
       <c r="F28" s="58">
-        <v>17400</v>
-      </c>
-      <c r="G28" s="60">
-        <f t="shared" si="8"/>
-        <v>17400</v>
-      </c>
-      <c r="H28" s="61">
+        <v>12000.18</v>
+      </c>
+      <c r="G28" s="59">
+        <f t="shared" si="9"/>
+        <v>12000.18</v>
+      </c>
+      <c r="H28" s="60">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I28" s="61">
+      <c r="I28" s="60">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J28" s="62">
+      <c r="J28" s="61">
         <f>EDESUR!I22</f>
         <v>0</v>
       </c>
-      <c r="K28" s="121">
+      <c r="K28" s="119">
         <f t="shared" si="2"/>
         <v>12000</v>
       </c>
-      <c r="L28" s="121">
+      <c r="L28" s="119">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M28" s="63">
+      <c r="M28" s="62">
         <f t="shared" si="4"/>
         <v>12000.18</v>
       </c>
-      <c r="N28" s="64">
+      <c r="N28" s="63">
         <f t="shared" si="5"/>
         <v>12720.18</v>
       </c>
-      <c r="O28" s="65">
+      <c r="O28" s="64">
         <f t="shared" si="6"/>
         <v>12360.18</v>
       </c>
@@ -3978,7 +4004,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="48">
         <v>19</v>
       </c>
@@ -3993,38 +4019,38 @@
         <v>0.6</v>
       </c>
       <c r="F29" s="58">
-        <v>17400</v>
-      </c>
-      <c r="G29" s="60">
-        <f t="shared" si="8"/>
-        <v>17400</v>
-      </c>
-      <c r="H29" s="61">
+        <v>12000.19</v>
+      </c>
+      <c r="G29" s="59">
+        <f t="shared" si="9"/>
+        <v>12000.19</v>
+      </c>
+      <c r="H29" s="60">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I29" s="61">
+      <c r="I29" s="60">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J29" s="62">
+      <c r="J29" s="61">
         <f>EDESUR!I23</f>
         <v>0</v>
       </c>
-      <c r="K29" s="121">
+      <c r="K29" s="119">
         <f t="shared" si="2"/>
         <v>12000</v>
       </c>
-      <c r="L29" s="121">
+      <c r="L29" s="119">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M29" s="63">
+      <c r="M29" s="62">
         <f t="shared" si="4"/>
         <v>12000.19</v>
       </c>
-      <c r="N29" s="64"/>
-      <c r="O29" s="65">
+      <c r="N29" s="63"/>
+      <c r="O29" s="64">
         <f t="shared" si="6"/>
         <v>12360.19</v>
       </c>
@@ -4033,119 +4059,116 @@
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A30" s="66">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A30" s="65">
         <v>20</v>
       </c>
-      <c r="B30" s="66" t="s">
+      <c r="B30" s="65" t="s">
         <v>64</v>
       </c>
       <c r="C30" s="48" t="s">
         <v>37</v>
       </c>
       <c r="D30" s="49" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E30" s="57">
         <v>0.6</v>
       </c>
-      <c r="F30" s="68">
-        <v>17400</v>
-      </c>
-      <c r="G30" s="60">
-        <f t="shared" si="8"/>
-        <v>17400</v>
-      </c>
-      <c r="H30" s="61">
+      <c r="F30" s="67">
+        <v>12000</v>
+      </c>
+      <c r="G30" s="59"/>
+      <c r="H30" s="60">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I30" s="61">
+        <v>12000</v>
+      </c>
+      <c r="I30" s="60">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J30" s="62">
+        <v>360</v>
+      </c>
+      <c r="J30" s="61">
         <f>EDESUR!I24</f>
         <v>0</v>
       </c>
-      <c r="K30" s="121">
+      <c r="K30" s="119">
         <f t="shared" si="2"/>
         <v>12000</v>
       </c>
-      <c r="L30" s="121">
+      <c r="L30" s="119">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M30" s="63">
+      <c r="M30" s="62">
         <f t="shared" si="4"/>
-        <v>12000</v>
-      </c>
-      <c r="N30" s="64"/>
-      <c r="O30" s="65">
+        <v>24360</v>
+      </c>
+      <c r="N30" s="63"/>
+      <c r="O30" s="64">
         <f t="shared" si="6"/>
-        <v>12360</v>
+        <v>25091</v>
       </c>
       <c r="P30" s="32"/>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A31" s="66">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A31" s="65">
         <v>21</v>
       </c>
-      <c r="B31" s="66" t="s">
+      <c r="B31" s="65" t="s">
         <v>65</v>
       </c>
       <c r="C31" s="50" t="s">
         <v>49</v>
       </c>
       <c r="D31" s="49" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E31" s="57">
         <v>0.3</v>
       </c>
-      <c r="F31" s="68">
-        <v>8700</v>
-      </c>
-      <c r="G31" s="69">
+      <c r="F31" s="67">
+        <v>6000</v>
+      </c>
+      <c r="G31" s="163">
         <f>F31</f>
-        <v>8700</v>
-      </c>
-      <c r="H31" s="61">
+        <v>6000</v>
+      </c>
+      <c r="H31" s="60">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I31" s="61">
+      <c r="I31" s="60">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J31" s="62">
+      <c r="J31" s="61">
         <f>EDESUR!I25</f>
         <v>0</v>
       </c>
-      <c r="K31" s="121">
+      <c r="K31" s="119">
         <f t="shared" si="2"/>
         <v>6000</v>
       </c>
-      <c r="L31" s="121">
+      <c r="L31" s="119">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M31" s="63">
+      <c r="M31" s="62">
         <f t="shared" si="4"/>
         <v>6000</v>
       </c>
-      <c r="N31" s="64"/>
-      <c r="O31" s="65">
+      <c r="N31" s="63"/>
+      <c r="O31" s="64">
         <f t="shared" si="6"/>
         <v>6180</v>
       </c>
       <c r="P31" s="32"/>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A32" s="67">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A32" s="66">
         <v>22</v>
       </c>
-      <c r="B32" s="67" t="s">
+      <c r="B32" s="66" t="s">
         <v>66</v>
       </c>
       <c r="C32" s="48" t="s">
@@ -4155,241 +4178,236 @@
       <c r="E32" s="57">
         <v>0.3</v>
       </c>
-      <c r="F32" s="68">
-        <v>8700</v>
-      </c>
-      <c r="G32" s="69">
+      <c r="F32" s="67">
+        <v>6000</v>
+      </c>
+      <c r="G32" s="163">
         <f>F32</f>
-        <v>8700</v>
-      </c>
-      <c r="H32" s="61">
+        <v>6000</v>
+      </c>
+      <c r="H32" s="60">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I32" s="61">
+      <c r="I32" s="60">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J32" s="62">
+      <c r="J32" s="61">
         <f>EDESUR!I26</f>
         <v>0</v>
       </c>
-      <c r="K32" s="121">
+      <c r="K32" s="119">
         <f t="shared" si="2"/>
         <v>6000</v>
       </c>
-      <c r="L32" s="121">
+      <c r="L32" s="119">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M32" s="63">
+      <c r="M32" s="62">
         <f t="shared" si="4"/>
         <v>6000</v>
       </c>
-      <c r="N32" s="64"/>
-      <c r="O32" s="65">
+      <c r="N32" s="63"/>
+      <c r="O32" s="64">
         <f t="shared" si="6"/>
         <v>6180</v>
       </c>
       <c r="P32" s="32"/>
     </row>
-    <row r="33" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="48">
         <v>23</v>
       </c>
-      <c r="B33" s="70" t="s">
+      <c r="B33" s="68" t="s">
         <v>67</v>
       </c>
-      <c r="C33" s="70" t="s">
+      <c r="C33" s="68" t="s">
         <v>68</v>
       </c>
       <c r="D33" s="49" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E33" s="57">
         <v>0.3</v>
       </c>
-      <c r="F33" s="68">
-        <v>8700</v>
-      </c>
-      <c r="G33" s="69">
+      <c r="F33" s="67">
+        <v>6000</v>
+      </c>
+      <c r="G33" s="163">
         <f>F33</f>
-        <v>8700</v>
-      </c>
-      <c r="H33" s="61">
+        <v>6000</v>
+      </c>
+      <c r="H33" s="60">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I33" s="61">
+      <c r="I33" s="60">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J33" s="62">
+      <c r="J33" s="61">
         <f>EDESUR!I27</f>
         <v>0</v>
       </c>
-      <c r="K33" s="121">
+      <c r="K33" s="119">
         <f t="shared" si="2"/>
         <v>6000</v>
       </c>
-      <c r="L33" s="121">
+      <c r="L33" s="119">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M33" s="63">
+      <c r="M33" s="62">
         <f t="shared" si="4"/>
         <v>6000</v>
       </c>
-      <c r="N33" s="71"/>
-      <c r="O33" s="65">
+      <c r="N33" s="69"/>
+      <c r="O33" s="64">
         <f t="shared" si="6"/>
         <v>6180</v>
       </c>
       <c r="P33" s="32"/>
     </row>
-    <row r="34" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="72"/>
-      <c r="B34" s="72"/>
-      <c r="C34" s="73"/>
-      <c r="D34" s="73"/>
-      <c r="E34" s="133">
+    <row r="34" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="70"/>
+      <c r="B34" s="70"/>
+      <c r="C34" s="71"/>
+      <c r="D34" s="71"/>
+      <c r="E34" s="131">
         <f>SUM(E11:E33)</f>
         <v>99.999999999999986</v>
       </c>
       <c r="F34" s="41">
         <f>SUM(F11:F33)</f>
-        <v>4064598</v>
+        <v>1996621.9000000001</v>
       </c>
       <c r="G34" s="46">
         <f>SUM(G11:G33)</f>
-        <v>4067977.64</v>
+        <v>2038799.4999999998</v>
       </c>
       <c r="H34" s="46">
         <f>SUM(H11:H33)</f>
-        <v>-3379.640000000014</v>
+        <v>-42177.599999999977</v>
       </c>
       <c r="I34" s="46">
-        <f t="shared" ref="I34:N34" si="9">SUM(I11:I33)</f>
-        <v>1.0799999999580905E-2</v>
+        <f t="shared" ref="I34:N34" si="10">SUM(I11:I33)</f>
+        <v>360</v>
       </c>
       <c r="J34" s="46">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="K34" s="101">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="K34" s="99">
+        <f t="shared" si="10"/>
         <v>2000000</v>
       </c>
       <c r="L34" s="46">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M34" s="74">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M34" s="72">
         <f>SUM(M11:M33)</f>
-        <v>1996621.9000000001</v>
-      </c>
-      <c r="N34" s="74">
-        <f t="shared" si="9"/>
-        <v>2071898.7100000002</v>
-      </c>
-      <c r="O34" s="74">
+        <v>1958183.9000000001</v>
+      </c>
+      <c r="N34" s="72">
+        <f t="shared" si="10"/>
+        <v>2018053.7100000002</v>
+      </c>
+      <c r="O34" s="72">
         <f>SUM(O11:O33)</f>
-        <v>2056519.9000000001</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>2016928.9000000001</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C35" s="38"/>
       <c r="D35" s="38"/>
     </row>
-    <row r="36" spans="1:16" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="37" spans="1:16" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C37" s="173" t="str">
+    <row r="36" spans="1:16" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="1:16" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C37" s="167" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. PORFAVOR RESPETAR LOS CENTAVOS AL ABONAR.</v>
       </c>
-      <c r="D37" s="173"/>
-      <c r="E37" s="173"/>
-      <c r="F37" s="173"/>
-      <c r="G37" s="173"/>
-      <c r="H37" s="173"/>
-      <c r="I37" s="173"/>
-      <c r="J37" s="173"/>
-      <c r="K37" s="173"/>
-      <c r="L37" s="173"/>
-      <c r="M37" s="173"/>
-    </row>
-    <row r="38" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C38" s="173"/>
-      <c r="D38" s="173"/>
-      <c r="E38" s="173"/>
-      <c r="F38" s="173"/>
-      <c r="G38" s="173"/>
-      <c r="H38" s="173"/>
-      <c r="I38" s="173"/>
-      <c r="J38" s="173"/>
-      <c r="K38" s="173"/>
-      <c r="L38" s="173"/>
-      <c r="M38" s="173"/>
-    </row>
-    <row r="39" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C39" s="173"/>
-      <c r="D39" s="173"/>
-      <c r="E39" s="173"/>
-      <c r="F39" s="173"/>
-      <c r="G39" s="173"/>
-      <c r="H39" s="173"/>
-      <c r="I39" s="173"/>
-      <c r="J39" s="173"/>
-      <c r="K39" s="173"/>
-      <c r="L39" s="173"/>
-      <c r="M39" s="173"/>
-    </row>
-    <row r="40" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C40" s="173"/>
-      <c r="D40" s="173"/>
-      <c r="E40" s="173"/>
-      <c r="F40" s="173"/>
-      <c r="G40" s="173"/>
-      <c r="H40" s="173"/>
-      <c r="I40" s="173"/>
-      <c r="J40" s="173"/>
-      <c r="K40" s="173"/>
-      <c r="L40" s="173"/>
-      <c r="M40" s="173"/>
-    </row>
-    <row r="41" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C41" s="173"/>
-      <c r="D41" s="173"/>
-      <c r="E41" s="173"/>
-      <c r="F41" s="173"/>
-      <c r="G41" s="173"/>
-      <c r="H41" s="173"/>
-      <c r="I41" s="173"/>
-      <c r="J41" s="173"/>
-      <c r="K41" s="173"/>
-      <c r="L41" s="173"/>
-      <c r="M41" s="173"/>
-    </row>
-    <row r="42" spans="1:16" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C42" s="173"/>
-      <c r="D42" s="173"/>
-      <c r="E42" s="173"/>
-      <c r="F42" s="173"/>
-      <c r="G42" s="173"/>
-      <c r="H42" s="173"/>
-      <c r="I42" s="173"/>
-      <c r="J42" s="173"/>
-      <c r="K42" s="173"/>
-      <c r="L42" s="173"/>
-      <c r="M42" s="173"/>
+      <c r="D37" s="167"/>
+      <c r="E37" s="167"/>
+      <c r="F37" s="167"/>
+      <c r="G37" s="167"/>
+      <c r="H37" s="167"/>
+      <c r="I37" s="167"/>
+      <c r="J37" s="167"/>
+      <c r="K37" s="167"/>
+      <c r="L37" s="167"/>
+      <c r="M37" s="167"/>
+    </row>
+    <row r="38" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C38" s="167"/>
+      <c r="D38" s="167"/>
+      <c r="E38" s="167"/>
+      <c r="F38" s="167"/>
+      <c r="G38" s="167"/>
+      <c r="H38" s="167"/>
+      <c r="I38" s="167"/>
+      <c r="J38" s="167"/>
+      <c r="K38" s="167"/>
+      <c r="L38" s="167"/>
+      <c r="M38" s="167"/>
+    </row>
+    <row r="39" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C39" s="167"/>
+      <c r="D39" s="167"/>
+      <c r="E39" s="167"/>
+      <c r="F39" s="167"/>
+      <c r="G39" s="167"/>
+      <c r="H39" s="167"/>
+      <c r="I39" s="167"/>
+      <c r="J39" s="167"/>
+      <c r="K39" s="167"/>
+      <c r="L39" s="167"/>
+      <c r="M39" s="167"/>
+    </row>
+    <row r="40" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C40" s="167"/>
+      <c r="D40" s="167"/>
+      <c r="E40" s="167"/>
+      <c r="F40" s="167"/>
+      <c r="G40" s="167"/>
+      <c r="H40" s="167"/>
+      <c r="I40" s="167"/>
+      <c r="J40" s="167"/>
+      <c r="K40" s="167"/>
+      <c r="L40" s="167"/>
+      <c r="M40" s="167"/>
+    </row>
+    <row r="41" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C41" s="167"/>
+      <c r="D41" s="167"/>
+      <c r="E41" s="167"/>
+      <c r="F41" s="167"/>
+      <c r="G41" s="167"/>
+      <c r="H41" s="167"/>
+      <c r="I41" s="167"/>
+      <c r="J41" s="167"/>
+      <c r="K41" s="167"/>
+      <c r="L41" s="167"/>
+      <c r="M41" s="167"/>
+    </row>
+    <row r="42" spans="1:16" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C42" s="167"/>
+      <c r="D42" s="167"/>
+      <c r="E42" s="167"/>
+      <c r="F42" s="167"/>
+      <c r="G42" s="167"/>
+      <c r="H42" s="167"/>
+      <c r="I42" s="167"/>
+      <c r="J42" s="167"/>
+      <c r="K42" s="167"/>
+      <c r="L42" s="167"/>
+      <c r="M42" s="167"/>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="C37:M42"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="E9:E10"/>
     <mergeCell ref="E1:M1"/>
     <mergeCell ref="I9:I10"/>
     <mergeCell ref="F9:F10"/>
@@ -4401,6 +4419,11 @@
     <mergeCell ref="L9:L10"/>
     <mergeCell ref="A4:O8"/>
     <mergeCell ref="O9:O10"/>
+    <mergeCell ref="C37:M42"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="E9:E10"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
@@ -4410,54 +4433,54 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D7123E2-E76E-40B2-9631-974509386176}">
   <dimension ref="B3:J33"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="4" customWidth="1"/>
-    <col min="5" max="5" width="21.6640625" customWidth="1"/>
-    <col min="6" max="6" width="4.5546875" customWidth="1"/>
-    <col min="7" max="7" width="24.44140625" customWidth="1"/>
+    <col min="5" max="5" width="21.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.5703125" customWidth="1"/>
+    <col min="7" max="7" width="24.42578125" customWidth="1"/>
     <col min="8" max="8" width="5" customWidth="1"/>
-    <col min="10" max="10" width="19.5546875" customWidth="1"/>
+    <col min="10" max="10" width="19.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B3" s="143" t="s">
-        <v>90</v>
-      </c>
-      <c r="C3" s="143" t="s">
-        <v>91</v>
-      </c>
-      <c r="E3" s="145" t="s">
-        <v>97</v>
-      </c>
-      <c r="G3" s="146" t="s">
-        <v>98</v>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B3" s="141" t="s">
+        <v>85</v>
+      </c>
+      <c r="C3" s="141" t="s">
+        <v>86</v>
+      </c>
+      <c r="E3" s="143" t="s">
+        <v>92</v>
+      </c>
+      <c r="G3" s="144" t="s">
+        <v>93</v>
       </c>
       <c r="I3" s="195" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="J3" s="196"/>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B4" s="143"/>
-      <c r="C4" s="143"/>
-      <c r="E4" s="143"/>
-      <c r="G4" s="147"/>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B4" s="141"/>
+      <c r="C4" s="141"/>
+      <c r="E4" s="141"/>
+      <c r="G4" s="145"/>
       <c r="I4" s="195"/>
       <c r="J4" s="196"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B5" s="143">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B5" s="141">
         <v>1</v>
       </c>
-      <c r="C5" s="143" t="s">
-        <v>92</v>
-      </c>
-      <c r="E5" s="148">
+      <c r="C5" s="141" t="s">
+        <v>87</v>
+      </c>
+      <c r="E5" s="146">
         <v>61353.383534261804</v>
       </c>
       <c r="F5" s="2"/>
-      <c r="G5" s="149">
+      <c r="G5" s="147">
         <v>61353.383534261804</v>
       </c>
       <c r="I5" s="193">
@@ -4466,18 +4489,18 @@
       </c>
       <c r="J5" s="194"/>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B6" s="143">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B6" s="141">
         <v>1</v>
       </c>
-      <c r="C6" s="143" t="s">
-        <v>93</v>
-      </c>
-      <c r="E6" s="148">
+      <c r="C6" s="141" t="s">
+        <v>88</v>
+      </c>
+      <c r="E6" s="146">
         <v>34428.700834302756</v>
       </c>
       <c r="F6" s="2"/>
-      <c r="G6" s="149">
+      <c r="G6" s="147">
         <v>34428.700834302756</v>
       </c>
       <c r="I6" s="193">
@@ -4486,18 +4509,18 @@
       </c>
       <c r="J6" s="194"/>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B7" s="143">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B7" s="141">
         <v>1</v>
       </c>
-      <c r="C7" s="143" t="s">
-        <v>94</v>
-      </c>
-      <c r="E7" s="148">
+      <c r="C7" s="141" t="s">
+        <v>89</v>
+      </c>
+      <c r="E7" s="146">
         <v>14356.010802482968</v>
       </c>
       <c r="F7" s="2"/>
-      <c r="G7" s="149">
+      <c r="G7" s="147">
         <v>14356.010802482968</v>
       </c>
       <c r="I7" s="193">
@@ -4506,18 +4529,18 @@
       </c>
       <c r="J7" s="194"/>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B8" s="143">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B8" s="141">
         <v>2</v>
       </c>
-      <c r="C8" s="143" t="s">
-        <v>92</v>
-      </c>
-      <c r="E8" s="148">
+      <c r="C8" s="141" t="s">
+        <v>87</v>
+      </c>
+      <c r="E8" s="146">
         <v>12061.218355435631</v>
       </c>
       <c r="F8" s="2"/>
-      <c r="G8" s="149">
+      <c r="G8" s="147">
         <v>12061.218355435631</v>
       </c>
       <c r="I8" s="193">
@@ -4526,18 +4549,18 @@
       </c>
       <c r="J8" s="194"/>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B9" s="144">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B9" s="142">
         <v>2</v>
       </c>
-      <c r="C9" s="144" t="s">
-        <v>95</v>
-      </c>
-      <c r="E9" s="148">
+      <c r="C9" s="142" t="s">
+        <v>90</v>
+      </c>
+      <c r="E9" s="146">
         <v>53068.035404197428</v>
       </c>
       <c r="F9" s="2"/>
-      <c r="G9" s="149">
+      <c r="G9" s="147">
         <v>53068.035404197428</v>
       </c>
       <c r="I9" s="193">
@@ -4546,18 +4569,18 @@
       </c>
       <c r="J9" s="194"/>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B10" s="144">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B10" s="142">
         <v>2</v>
       </c>
-      <c r="C10" s="144" t="s">
-        <v>93</v>
-      </c>
-      <c r="E10" s="148">
+      <c r="C10" s="142" t="s">
+        <v>88</v>
+      </c>
+      <c r="E10" s="146">
         <v>9841.6389016527519</v>
       </c>
       <c r="F10" s="2"/>
-      <c r="G10" s="149">
+      <c r="G10" s="147">
         <v>9841.6389016527519</v>
       </c>
       <c r="I10" s="193">
@@ -4566,18 +4589,18 @@
       </c>
       <c r="J10" s="194"/>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B11" s="144">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B11" s="142">
         <v>2</v>
       </c>
-      <c r="C11" s="144" t="s">
-        <v>94</v>
-      </c>
-      <c r="E11" s="148">
+      <c r="C11" s="142" t="s">
+        <v>89</v>
+      </c>
+      <c r="E11" s="146">
         <v>9327.3712310195588</v>
       </c>
       <c r="F11" s="2"/>
-      <c r="G11" s="149">
+      <c r="G11" s="147">
         <v>9327.3712310195588</v>
       </c>
       <c r="I11" s="193">
@@ -4586,18 +4609,18 @@
       </c>
       <c r="J11" s="194"/>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B12" s="144">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B12" s="142">
         <v>3</v>
       </c>
-      <c r="C12" s="144" t="s">
-        <v>92</v>
-      </c>
-      <c r="E12" s="148">
+      <c r="C12" s="142" t="s">
+        <v>87</v>
+      </c>
+      <c r="E12" s="146">
         <v>9216.1440460861631</v>
       </c>
       <c r="F12" s="2"/>
-      <c r="G12" s="149">
+      <c r="G12" s="147">
         <v>9216.1440460861631</v>
       </c>
       <c r="I12" s="193">
@@ -4606,18 +4629,18 @@
       </c>
       <c r="J12" s="194"/>
     </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B13" s="143">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B13" s="141">
         <v>3</v>
       </c>
-      <c r="C13" s="143" t="s">
-        <v>95</v>
-      </c>
-      <c r="E13" s="148">
+      <c r="C13" s="141" t="s">
+        <v>90</v>
+      </c>
+      <c r="E13" s="146">
         <v>23200.609218392572</v>
       </c>
       <c r="F13" s="2"/>
-      <c r="G13" s="149">
+      <c r="G13" s="147">
         <v>23200.609218392572</v>
       </c>
       <c r="I13" s="193">
@@ -4626,18 +4649,18 @@
       </c>
       <c r="J13" s="194"/>
     </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B14" s="144">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B14" s="142">
         <v>3</v>
       </c>
-      <c r="C14" s="144" t="s">
-        <v>93</v>
-      </c>
-      <c r="E14" s="148">
+      <c r="C14" s="142" t="s">
+        <v>88</v>
+      </c>
+      <c r="E14" s="146">
         <v>7781.0089492021225</v>
       </c>
       <c r="F14" s="2"/>
-      <c r="G14" s="149">
+      <c r="G14" s="147">
         <v>7781.0089492021225</v>
       </c>
       <c r="I14" s="193">
@@ -4646,18 +4669,18 @@
       </c>
       <c r="J14" s="194"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B15" s="144">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B15" s="142">
         <v>3</v>
       </c>
-      <c r="C15" s="144" t="s">
-        <v>94</v>
-      </c>
-      <c r="E15" s="148">
+      <c r="C15" s="142" t="s">
+        <v>89</v>
+      </c>
+      <c r="E15" s="146">
         <v>10351.832144880002</v>
       </c>
       <c r="F15" s="2"/>
-      <c r="G15" s="149">
+      <c r="G15" s="147">
         <v>10351.832144880002</v>
       </c>
       <c r="I15" s="193">
@@ -4666,18 +4689,18 @@
       </c>
       <c r="J15" s="194"/>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B16" s="143">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B16" s="141">
         <v>4</v>
       </c>
-      <c r="C16" s="143" t="s">
-        <v>92</v>
-      </c>
-      <c r="E16" s="148">
+      <c r="C16" s="141" t="s">
+        <v>87</v>
+      </c>
+      <c r="E16" s="146">
         <v>49509.655303807594</v>
       </c>
       <c r="F16" s="2"/>
-      <c r="G16" s="149">
+      <c r="G16" s="147">
         <v>49509.655303807594</v>
       </c>
       <c r="I16" s="193">
@@ -4686,18 +4709,18 @@
       </c>
       <c r="J16" s="194"/>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B17" s="144">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B17" s="142">
         <v>4</v>
       </c>
-      <c r="C17" s="144" t="s">
-        <v>95</v>
-      </c>
-      <c r="E17" s="148">
+      <c r="C17" s="142" t="s">
+        <v>90</v>
+      </c>
+      <c r="E17" s="146">
         <v>16866.513739552778</v>
       </c>
       <c r="F17" s="2"/>
-      <c r="G17" s="149">
+      <c r="G17" s="147">
         <v>16866.513739552778</v>
       </c>
       <c r="I17" s="193">
@@ -4706,18 +4729,18 @@
       </c>
       <c r="J17" s="194"/>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B18" s="143">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B18" s="141">
         <v>4</v>
       </c>
-      <c r="C18" s="143" t="s">
-        <v>93</v>
-      </c>
-      <c r="E18" s="148">
+      <c r="C18" s="141" t="s">
+        <v>88</v>
+      </c>
+      <c r="E18" s="146">
         <v>24968.536052597399</v>
       </c>
       <c r="F18" s="2"/>
-      <c r="G18" s="149">
+      <c r="G18" s="147">
         <v>24968.536052597399</v>
       </c>
       <c r="I18" s="193">
@@ -4726,18 +4749,18 @@
       </c>
       <c r="J18" s="194"/>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B19" s="144">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B19" s="142">
         <v>4</v>
       </c>
-      <c r="C19" s="144" t="s">
-        <v>94</v>
-      </c>
-      <c r="E19" s="148">
+      <c r="C19" s="142" t="s">
+        <v>89</v>
+      </c>
+      <c r="E19" s="146">
         <v>10779.178697518902</v>
       </c>
       <c r="F19" s="2"/>
-      <c r="G19" s="149">
+      <c r="G19" s="147">
         <v>10779.178697518902</v>
       </c>
       <c r="I19" s="193">
@@ -4746,22 +4769,22 @@
       </c>
       <c r="J19" s="194"/>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B20" s="143"/>
-      <c r="C20" s="143"/>
-      <c r="E20" s="143"/>
-      <c r="G20" s="147"/>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B20" s="141"/>
+      <c r="C20" s="141"/>
+      <c r="E20" s="141"/>
+      <c r="G20" s="145"/>
       <c r="I20" s="193"/>
       <c r="J20" s="194"/>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B21" s="143"/>
-      <c r="C21" s="143"/>
-      <c r="E21" s="152">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B21" s="141"/>
+      <c r="C21" s="141"/>
+      <c r="E21" s="150">
         <f>SUM(E5:E20)</f>
         <v>347109.83721539041</v>
       </c>
-      <c r="G21" s="149">
+      <c r="G21" s="147">
         <f>SUM(G5:G20)</f>
         <v>347109.83721539041</v>
       </c>
@@ -4771,17 +4794,17 @@
       </c>
       <c r="J21" s="194"/>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B22" s="143" t="s">
-        <v>96</v>
-      </c>
-      <c r="C22" s="143">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B22" s="141" t="s">
+        <v>91</v>
+      </c>
+      <c r="C22" s="141">
         <v>1</v>
       </c>
-      <c r="E22" s="162">
+      <c r="E22" s="160">
         <v>723.43331893167124</v>
       </c>
-      <c r="G22" s="163">
+      <c r="G22" s="161">
         <v>723.43331893167124</v>
       </c>
       <c r="I22" s="193">
@@ -4790,17 +4813,17 @@
       </c>
       <c r="J22" s="194"/>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B23" s="143" t="s">
-        <v>96</v>
-      </c>
-      <c r="C23" s="143">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B23" s="141" t="s">
+        <v>91</v>
+      </c>
+      <c r="C23" s="141">
         <v>2</v>
       </c>
-      <c r="E23" s="162">
+      <c r="E23" s="160">
         <v>620.08570194143249</v>
       </c>
-      <c r="G23" s="163">
+      <c r="G23" s="161">
         <v>620.08570194143249</v>
       </c>
       <c r="I23" s="193">
@@ -4809,17 +4832,17 @@
       </c>
       <c r="J23" s="194"/>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B24" s="143" t="s">
-        <v>96</v>
-      </c>
-      <c r="C24" s="143">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B24" s="141" t="s">
+        <v>91</v>
+      </c>
+      <c r="C24" s="141">
         <v>3</v>
       </c>
-      <c r="E24" s="162">
+      <c r="E24" s="160">
         <v>620.08570194143249</v>
       </c>
-      <c r="G24" s="163">
+      <c r="G24" s="161">
         <v>620.08570194143249</v>
       </c>
       <c r="I24" s="193">
@@ -4828,17 +4851,17 @@
       </c>
       <c r="J24" s="194"/>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B25" s="143" t="s">
-        <v>96</v>
-      </c>
-      <c r="C25" s="143">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B25" s="141" t="s">
+        <v>91</v>
+      </c>
+      <c r="C25" s="141">
         <v>4</v>
       </c>
-      <c r="E25" s="162">
+      <c r="E25" s="160">
         <v>620.08570194143249</v>
       </c>
-      <c r="G25" s="163">
+      <c r="G25" s="161">
         <v>620.08570194143249</v>
       </c>
       <c r="I25" s="193">
@@ -4847,17 +4870,17 @@
       </c>
       <c r="J25" s="194"/>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B26" s="143" t="s">
-        <v>96</v>
-      </c>
-      <c r="C26" s="143">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B26" s="141" t="s">
+        <v>91</v>
+      </c>
+      <c r="C26" s="141">
         <v>5</v>
       </c>
-      <c r="E26" s="162">
+      <c r="E26" s="160">
         <v>620.08570194143249</v>
       </c>
-      <c r="G26" s="163">
+      <c r="G26" s="161">
         <v>620.08570194143249</v>
       </c>
       <c r="I26" s="193">
@@ -4866,17 +4889,17 @@
       </c>
       <c r="J26" s="194"/>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B27" s="143" t="s">
-        <v>96</v>
-      </c>
-      <c r="C27" s="143">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B27" s="141" t="s">
+        <v>91</v>
+      </c>
+      <c r="C27" s="141">
         <v>6</v>
       </c>
-      <c r="E27" s="162">
+      <c r="E27" s="160">
         <v>310.04285097071624</v>
       </c>
-      <c r="G27" s="163">
+      <c r="G27" s="161">
         <v>310.04285097071624</v>
       </c>
       <c r="I27" s="193">
@@ -4885,17 +4908,17 @@
       </c>
       <c r="J27" s="194"/>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B28" s="143" t="s">
-        <v>96</v>
-      </c>
-      <c r="C28" s="143">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B28" s="141" t="s">
+        <v>91</v>
+      </c>
+      <c r="C28" s="141">
         <v>7</v>
       </c>
-      <c r="E28" s="162">
+      <c r="E28" s="160">
         <v>310.04285097071624</v>
       </c>
-      <c r="G28" s="163">
+      <c r="G28" s="161">
         <v>310.04285097071624</v>
       </c>
       <c r="I28" s="193">
@@ -4904,17 +4927,17 @@
       </c>
       <c r="J28" s="194"/>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B29" s="143" t="s">
-        <v>96</v>
-      </c>
-      <c r="C29" s="143">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B29" s="141" t="s">
+        <v>91</v>
+      </c>
+      <c r="C29" s="141">
         <v>8</v>
       </c>
-      <c r="E29" s="162">
+      <c r="E29" s="160">
         <v>310.04285097071624</v>
       </c>
-      <c r="G29" s="163">
+      <c r="G29" s="161">
         <v>310.04285097071624</v>
       </c>
       <c r="I29" s="193">
@@ -4923,12 +4946,12 @@
       </c>
       <c r="J29" s="194"/>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="E30" s="152">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="E30" s="150">
         <f>SUM(E22:E29)</f>
         <v>4133.9046796095499</v>
       </c>
-      <c r="G30" s="149">
+      <c r="G30" s="147">
         <f>SUM(G22:G29)</f>
         <v>4133.9046796095499</v>
       </c>
@@ -4938,27 +4961,27 @@
       </c>
       <c r="J30" s="194"/>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="E31" s="152"/>
-      <c r="G31" s="149"/>
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="E31" s="150"/>
+      <c r="G31" s="147"/>
       <c r="I31" s="193">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J31" s="194"/>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="E32" s="150"/>
-      <c r="G32" s="151"/>
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="E32" s="148"/>
+      <c r="G32" s="149"/>
       <c r="I32" s="193"/>
       <c r="J32" s="194"/>
     </row>
-    <row r="33" spans="5:10" x14ac:dyDescent="0.3">
-      <c r="E33" s="152">
+    <row r="33" spans="5:10" x14ac:dyDescent="0.25">
+      <c r="E33" s="150">
         <f>E30+E21</f>
         <v>351243.74189499998</v>
       </c>
-      <c r="G33" s="149">
+      <c r="G33" s="147">
         <f>G21+G30</f>
         <v>351243.74189499998</v>
       </c>
@@ -4970,21 +4993,6 @@
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="I17:J17"/>
     <mergeCell ref="I31:J31"/>
     <mergeCell ref="I32:J32"/>
     <mergeCell ref="I33:J33"/>
@@ -5001,6 +5009,21 @@
     <mergeCell ref="I22:J22"/>
     <mergeCell ref="I23:J23"/>
     <mergeCell ref="I24:J24"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="I17:J17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="portrait" r:id="rId1"/>

--- a/SALTA 1167/Noviembre/SALTA1167-Noviembre.xlsx
+++ b/SALTA 1167/Noviembre/SALTA1167-Noviembre.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\SALTA 1167\Noviembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\SALTA 1167\Noviembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B31B0D55-F426-4736-A94A-0C4199256F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{197C58EC-F926-4C3E-9CFF-89AFA5FC75FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -1387,83 +1387,83 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1842,21 +1842,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M101"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.5703125" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" customWidth="1"/>
+    <col min="1" max="1" width="37.5546875" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
+    <col min="5" max="5" width="14.6640625" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.28515625" customWidth="1"/>
+    <col min="12" max="12" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="14"/>
       <c r="B1" s="53" t="s">
         <v>78</v>
@@ -1865,7 +1865,7 @@
       <c r="D1" s="53"/>
       <c r="E1" s="54"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="15"/>
       <c r="B2" s="55" t="s">
         <v>14</v>
@@ -1874,16 +1874,16 @@
       <c r="D2" s="55"/>
       <c r="E2" s="56"/>
     </row>
-    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="15"/>
-      <c r="B3" s="169" t="s">
+      <c r="B3" s="167" t="s">
         <v>81</v>
       </c>
-      <c r="C3" s="169"/>
-      <c r="D3" s="169"/>
-      <c r="E3" s="170"/>
-    </row>
-    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C3" s="167"/>
+      <c r="D3" s="167"/>
+      <c r="E3" s="168"/>
+    </row>
+    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="18" t="s">
         <v>0</v>
       </c>
@@ -1894,7 +1894,7 @@
       <c r="D4" s="19"/>
       <c r="E4" s="20"/>
     </row>
-    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="15" t="s">
         <v>79</v>
       </c>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="E5" s="17"/>
     </row>
-    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="18" t="s">
         <v>26</v>
       </c>
@@ -1918,57 +1918,57 @@
       </c>
       <c r="E6" s="20"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="172" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="170" t="s">
         <v>122</v>
       </c>
-      <c r="C8" s="172"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="172"/>
-      <c r="C9" s="172"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="172"/>
-      <c r="C10" s="172"/>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="171" t="s">
+      <c r="C8" s="170"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B9" s="170"/>
+      <c r="C9" s="170"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="170"/>
+      <c r="C10" s="170"/>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="169" t="s">
         <v>108</v>
       </c>
-      <c r="B13" s="171"/>
-      <c r="C13" s="171"/>
-      <c r="D13" s="171"/>
-      <c r="E13" s="171"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="171"/>
-      <c r="B14" s="171"/>
-      <c r="C14" s="171"/>
-      <c r="D14" s="171"/>
-      <c r="E14" s="171"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="171"/>
-      <c r="B15" s="171"/>
-      <c r="C15" s="171"/>
-      <c r="D15" s="171"/>
-      <c r="E15" s="171"/>
-    </row>
-    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="171"/>
-      <c r="B16" s="171"/>
-      <c r="C16" s="171"/>
-      <c r="D16" s="171"/>
-      <c r="E16" s="171"/>
-    </row>
-    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="169"/>
+      <c r="C13" s="169"/>
+      <c r="D13" s="169"/>
+      <c r="E13" s="169"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="169"/>
+      <c r="B14" s="169"/>
+      <c r="C14" s="169"/>
+      <c r="D14" s="169"/>
+      <c r="E14" s="169"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="169"/>
+      <c r="B15" s="169"/>
+      <c r="C15" s="169"/>
+      <c r="D15" s="169"/>
+      <c r="E15" s="169"/>
+    </row>
+    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="169"/>
+      <c r="B16" s="169"/>
+      <c r="C16" s="169"/>
+      <c r="D16" s="169"/>
+      <c r="E16" s="169"/>
+    </row>
+    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="10" t="s">
         <v>111</v>
       </c>
@@ -1977,7 +1977,7 @@
       <c r="D20" s="8"/>
       <c r="E20" s="13"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="26" t="s">
         <v>82</v>
       </c>
@@ -1986,7 +1986,7 @@
       <c r="D21" s="121"/>
       <c r="E21" s="106"/>
     </row>
-    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="165" t="s">
         <v>126</v>
       </c>
@@ -2000,7 +2000,7 @@
       </c>
       <c r="H22" s="95"/>
     </row>
-    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="165" t="s">
         <v>127</v>
       </c>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="H23" s="95"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="22" t="s">
         <v>9</v>
       </c>
@@ -2026,7 +2026,7 @@
         <v>862572.36</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="26" t="s">
         <v>18</v>
       </c>
@@ -2035,11 +2035,11 @@
       <c r="D25" s="124"/>
       <c r="E25" s="136"/>
     </row>
-    <row r="26" spans="1:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="173" t="s">
+    <row r="26" spans="1:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="171" t="s">
         <v>80</v>
       </c>
-      <c r="B26" s="174"/>
+      <c r="B26" s="172"/>
       <c r="C26" s="42"/>
       <c r="D26" s="164">
         <v>66146</v>
@@ -2048,7 +2048,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="22" t="s">
         <v>1</v>
       </c>
@@ -2060,7 +2060,7 @@
         <v>66146</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="26" t="s">
         <v>10</v>
       </c>
@@ -2069,7 +2069,7 @@
       <c r="D28" s="125"/>
       <c r="E28" s="111"/>
     </row>
-    <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
         <v>70</v>
       </c>
@@ -2080,7 +2080,7 @@
       </c>
       <c r="E29" s="115"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
         <v>69</v>
       </c>
@@ -2093,7 +2093,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
         <v>69</v>
       </c>
@@ -2106,11 +2106,11 @@
         <v>131</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="173" t="s">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32" s="171" t="s">
         <v>71</v>
       </c>
-      <c r="B32" s="174"/>
+      <c r="B32" s="172"/>
       <c r="C32" s="5"/>
       <c r="D32" s="116">
         <v>242436.28</v>
@@ -2119,7 +2119,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="118" t="s">
         <v>83</v>
       </c>
@@ -2132,7 +2132,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="22" t="s">
         <v>2</v>
       </c>
@@ -2144,14 +2144,14 @@
         <v>589930.27</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="26"/>
       <c r="B35" s="22"/>
       <c r="C35" s="22"/>
       <c r="D35" s="123"/>
       <c r="E35" s="112"/>
     </row>
-    <row r="36" spans="1:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="165" t="s">
         <v>137</v>
       </c>
@@ -2164,7 +2164,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="165" t="s">
         <v>138</v>
       </c>
@@ -2177,7 +2177,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="165" t="s">
         <v>139</v>
       </c>
@@ -2190,7 +2190,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="133" t="s">
         <v>140</v>
       </c>
@@ -2203,7 +2203,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="165" t="s">
         <v>132</v>
       </c>
@@ -2216,7 +2216,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="165" t="s">
         <v>129</v>
       </c>
@@ -2229,7 +2229,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="22" t="s">
         <v>6</v>
       </c>
@@ -2241,7 +2241,7 @@
         <v>1134802</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="26" t="s">
         <v>11</v>
       </c>
@@ -2250,7 +2250,7 @@
       <c r="D43" s="121"/>
       <c r="E43" s="106"/>
     </row>
-    <row r="44" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="165" t="s">
         <v>29</v>
       </c>
@@ -2261,14 +2261,14 @@
       </c>
       <c r="E44" s="140"/>
     </row>
-    <row r="45" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="133"/>
       <c r="B45" s="134"/>
       <c r="C45" s="40"/>
       <c r="D45" s="151"/>
       <c r="E45" s="140"/>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="22" t="s">
         <v>9</v>
       </c>
@@ -2280,7 +2280,7 @@
         <v>140000</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="26" t="s">
         <v>8</v>
       </c>
@@ -2289,7 +2289,7 @@
       <c r="D47" s="120"/>
       <c r="E47" s="107"/>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
         <v>28</v>
       </c>
@@ -2298,7 +2298,7 @@
       <c r="D48" s="116"/>
       <c r="E48" s="113"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
         <v>134</v>
       </c>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="E49" s="30"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="39" t="s">
         <v>9</v>
       </c>
@@ -2322,14 +2322,14 @@
         <v>35000.199999999997</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="5"/>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
       <c r="D51" s="77"/>
       <c r="E51" s="83"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="23" t="s">
         <v>107</v>
       </c>
@@ -2338,13 +2338,13 @@
       <c r="D52" s="84"/>
       <c r="E52" s="139"/>
     </row>
-    <row r="53" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="1"/>
       <c r="D53" s="85"/>
       <c r="E53" s="86"/>
       <c r="F53" s="32"/>
     </row>
-    <row r="54" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="3" t="s">
         <v>103</v>
       </c>
@@ -2358,16 +2358,16 @@
       <c r="F54" s="105"/>
       <c r="G54" s="32"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="D55" s="85"/>
       <c r="E55" s="85"/>
     </row>
-    <row r="56" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D56" s="85"/>
       <c r="E56" s="85"/>
       <c r="H56" s="127"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" s="10" t="s">
         <v>104</v>
       </c>
@@ -2376,29 +2376,29 @@
       <c r="D57" s="89"/>
       <c r="E57" s="90"/>
     </row>
-    <row r="58" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="79"/>
       <c r="B58" s="114"/>
       <c r="C58" s="5"/>
       <c r="D58" s="80"/>
       <c r="E58" s="78"/>
     </row>
-    <row r="59" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="165"/>
       <c r="B59" s="166"/>
       <c r="C59" s="5"/>
       <c r="D59" s="80"/>
       <c r="E59" s="78"/>
     </row>
-    <row r="60" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="79"/>
       <c r="B61" s="81"/>
       <c r="C61" s="5"/>
       <c r="D61" s="80"/>
       <c r="E61" s="78"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="37"/>
       <c r="B62" s="36"/>
       <c r="C62" s="36"/>
@@ -2408,9 +2408,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="65" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="64" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="65" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="23" t="s">
         <v>106</v>
       </c>
@@ -2419,8 +2419,8 @@
       <c r="D65" s="24"/>
       <c r="E65" s="76"/>
     </row>
-    <row r="66" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="67" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="67" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" s="3" t="s">
         <v>105</v>
       </c>
@@ -2432,8 +2432,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="69" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="69" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="74" t="s">
         <v>112</v>
       </c>
@@ -2442,7 +2442,7 @@
         <v>2828450.83</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="74" t="s">
         <v>113</v>
       </c>
@@ -2451,7 +2451,7 @@
         <v>2828450.83</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="74" t="s">
         <v>114</v>
       </c>
@@ -2460,7 +2460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" s="74" t="s">
         <v>115</v>
       </c>
@@ -2469,12 +2469,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:5" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" s="29" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A74"/>
       <c r="B74" s="31"/>
       <c r="C74" s="28"/>
     </row>
-    <row r="75" spans="1:5" s="29" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" s="29" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A75" s="97" t="s">
         <v>116</v>
       </c>
@@ -2484,7 +2484,7 @@
       <c r="C75" s="28"/>
       <c r="D75" s="35"/>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="42" t="s">
         <v>109</v>
       </c>
@@ -2493,7 +2493,7 @@
         <v>-2828450.83</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" s="42" t="s">
         <v>27</v>
       </c>
@@ -2502,7 +2502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="42" t="s">
         <v>118</v>
       </c>
@@ -2511,7 +2511,7 @@
         <v>2038799.4999999998</v>
       </c>
     </row>
-    <row r="79" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A79" s="42" t="s">
         <v>135</v>
       </c>
@@ -2520,13 +2520,13 @@
         <v>294965.15000000002</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" s="104" t="s">
         <v>25</v>
       </c>
       <c r="B80" s="128"/>
     </row>
-    <row r="81" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A81" s="100" t="s">
         <v>120</v>
       </c>
@@ -2535,13 +2535,13 @@
         <v>115565.9499999996</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" s="98"/>
       <c r="B82" s="98"/>
       <c r="D82" s="32"/>
       <c r="E82" s="31"/>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="97" t="s">
         <v>117</v>
       </c>
@@ -2551,7 +2551,7 @@
       <c r="D83" s="31"/>
       <c r="E83" s="32"/>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" s="42" t="s">
         <v>110</v>
       </c>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="D84" s="32"/>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" s="42" t="s">
         <v>27</v>
       </c>
@@ -2571,7 +2571,7 @@
       </c>
       <c r="D85" s="32"/>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="42" t="s">
         <v>119</v>
       </c>
@@ -2579,13 +2579,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" s="104" t="s">
         <v>25</v>
       </c>
       <c r="B87" s="128"/>
     </row>
-    <row r="88" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A88" s="100" t="s">
         <v>121</v>
       </c>
@@ -2594,28 +2594,28 @@
         <v>2000000</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" s="98"/>
       <c r="B89" s="98"/>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" s="98"/>
       <c r="B90" s="98"/>
     </row>
-    <row r="91" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A92" s="168" t="s">
+    <row r="91" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A92" s="174" t="s">
         <v>19</v>
       </c>
-      <c r="B92" s="168"/>
-      <c r="C92" s="168"/>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A93" s="168"/>
-      <c r="B93" s="168"/>
-      <c r="C93" s="168"/>
-    </row>
-    <row r="94" spans="1:5" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B92" s="174"/>
+      <c r="C92" s="174"/>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A93" s="174"/>
+      <c r="B93" s="174"/>
+      <c r="C93" s="174"/>
+    </row>
+    <row r="94" spans="1:5" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="92"/>
       <c r="B94" s="27"/>
       <c r="C94" s="27">
@@ -2623,13 +2623,13 @@
       </c>
       <c r="E94" s="105"/>
     </row>
-    <row r="95" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="92"/>
       <c r="B95" s="94"/>
       <c r="C95" s="91"/>
       <c r="D95" s="105"/>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" s="33" t="s">
         <v>6</v>
       </c>
@@ -2639,39 +2639,44 @@
       </c>
       <c r="C96" s="34"/>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
       <c r="M97" s="7"/>
     </row>
-    <row r="98" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="167"/>
-      <c r="B98" s="167"/>
-      <c r="C98" s="167"/>
-      <c r="D98" s="167"/>
-      <c r="E98" s="167"/>
-    </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A99" s="167"/>
-      <c r="B99" s="167"/>
-      <c r="C99" s="167"/>
-      <c r="D99" s="167"/>
-      <c r="E99" s="167"/>
-    </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A100" s="167"/>
-      <c r="B100" s="167"/>
-      <c r="C100" s="167"/>
-      <c r="D100" s="167"/>
-      <c r="E100" s="167"/>
-    </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A101" s="167"/>
-      <c r="B101" s="167"/>
-      <c r="C101" s="167"/>
-      <c r="D101" s="167"/>
-      <c r="E101" s="167"/>
+    <row r="98" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="173"/>
+      <c r="B98" s="173"/>
+      <c r="C98" s="173"/>
+      <c r="D98" s="173"/>
+      <c r="E98" s="173"/>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A99" s="173"/>
+      <c r="B99" s="173"/>
+      <c r="C99" s="173"/>
+      <c r="D99" s="173"/>
+      <c r="E99" s="173"/>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A100" s="173"/>
+      <c r="B100" s="173"/>
+      <c r="C100" s="173"/>
+      <c r="D100" s="173"/>
+      <c r="E100" s="173"/>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A101" s="173"/>
+      <c r="B101" s="173"/>
+      <c r="C101" s="173"/>
+      <c r="D101" s="173"/>
+      <c r="E101" s="173"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A98:E101"/>
+    <mergeCell ref="A92:C93"/>
+    <mergeCell ref="A59:B59"/>
     <mergeCell ref="A38:B38"/>
     <mergeCell ref="A40:B40"/>
     <mergeCell ref="A37:B37"/>
@@ -2683,11 +2688,6 @@
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="A32:B32"/>
     <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A98:E101"/>
-    <mergeCell ref="A92:C93"/>
-    <mergeCell ref="A59:B59"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2698,45 +2698,45 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Q42"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="4.28515625" customWidth="1"/>
-    <col min="3" max="3" width="18.5703125" customWidth="1"/>
+    <col min="1" max="2" width="4.33203125" customWidth="1"/>
+    <col min="3" max="3" width="18.5546875" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="8.42578125" customWidth="1"/>
-    <col min="6" max="6" width="14.140625" customWidth="1"/>
-    <col min="7" max="7" width="12.28515625" customWidth="1"/>
-    <col min="8" max="8" width="10.5703125" customWidth="1"/>
-    <col min="9" max="9" width="9.5703125" customWidth="1"/>
-    <col min="10" max="10" width="12.28515625" customWidth="1"/>
-    <col min="11" max="11" width="12.42578125" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" customWidth="1"/>
+    <col min="5" max="5" width="8.44140625" customWidth="1"/>
+    <col min="6" max="6" width="14.109375" customWidth="1"/>
+    <col min="7" max="7" width="12.33203125" customWidth="1"/>
+    <col min="8" max="8" width="10.5546875" customWidth="1"/>
+    <col min="9" max="9" width="9.5546875" customWidth="1"/>
+    <col min="10" max="10" width="12.33203125" customWidth="1"/>
+    <col min="11" max="11" width="12.44140625" customWidth="1"/>
+    <col min="12" max="12" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.6640625" customWidth="1"/>
     <col min="14" max="14" width="12" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" customWidth="1"/>
-    <col min="16" max="16" width="0.140625" customWidth="1"/>
+    <col min="15" max="15" width="14.33203125" customWidth="1"/>
+    <col min="16" max="16" width="0.109375" customWidth="1"/>
     <col min="17" max="17" width="12" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="152"/>
       <c r="D1" s="152"/>
-      <c r="E1" s="178"/>
-      <c r="F1" s="178"/>
-      <c r="G1" s="178"/>
-      <c r="H1" s="178"/>
-      <c r="I1" s="178"/>
-      <c r="J1" s="178"/>
-      <c r="K1" s="178"/>
-      <c r="L1" s="178"/>
-      <c r="M1" s="178"/>
+      <c r="E1" s="175"/>
+      <c r="F1" s="175"/>
+      <c r="G1" s="175"/>
+      <c r="H1" s="175"/>
+      <c r="I1" s="175"/>
+      <c r="J1" s="175"/>
+      <c r="K1" s="175"/>
+      <c r="L1" s="175"/>
+      <c r="M1" s="175"/>
       <c r="N1" s="6"/>
       <c r="O1" s="6"/>
     </row>
-    <row r="2" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="152"/>
@@ -2762,7 +2762,7 @@
       <c r="O2" s="43"/>
       <c r="P2" s="21"/>
     </row>
-    <row r="3" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="152"/>
@@ -2780,163 +2780,163 @@
       <c r="O3" s="43"/>
       <c r="P3" s="21"/>
     </row>
-    <row r="4" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="188" t="s">
+    <row r="4" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="187" t="s">
         <v>100</v>
       </c>
-      <c r="B4" s="189"/>
-      <c r="C4" s="189"/>
-      <c r="D4" s="189"/>
-      <c r="E4" s="189"/>
-      <c r="F4" s="189"/>
-      <c r="G4" s="189"/>
-      <c r="H4" s="189"/>
-      <c r="I4" s="189"/>
-      <c r="J4" s="189"/>
-      <c r="K4" s="189"/>
-      <c r="L4" s="189"/>
-      <c r="M4" s="189"/>
-      <c r="N4" s="189"/>
-      <c r="O4" s="189"/>
+      <c r="B4" s="188"/>
+      <c r="C4" s="188"/>
+      <c r="D4" s="188"/>
+      <c r="E4" s="188"/>
+      <c r="F4" s="188"/>
+      <c r="G4" s="188"/>
+      <c r="H4" s="188"/>
+      <c r="I4" s="188"/>
+      <c r="J4" s="188"/>
+      <c r="K4" s="188"/>
+      <c r="L4" s="188"/>
+      <c r="M4" s="188"/>
+      <c r="N4" s="188"/>
+      <c r="O4" s="188"/>
       <c r="P4" s="21"/>
     </row>
-    <row r="5" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="189"/>
-      <c r="B5" s="189"/>
-      <c r="C5" s="189"/>
-      <c r="D5" s="189"/>
-      <c r="E5" s="189"/>
-      <c r="F5" s="189"/>
-      <c r="G5" s="189"/>
-      <c r="H5" s="189"/>
-      <c r="I5" s="189"/>
-      <c r="J5" s="189"/>
-      <c r="K5" s="189"/>
-      <c r="L5" s="189"/>
-      <c r="M5" s="189"/>
-      <c r="N5" s="189"/>
-      <c r="O5" s="189"/>
+    <row r="5" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="188"/>
+      <c r="B5" s="188"/>
+      <c r="C5" s="188"/>
+      <c r="D5" s="188"/>
+      <c r="E5" s="188"/>
+      <c r="F5" s="188"/>
+      <c r="G5" s="188"/>
+      <c r="H5" s="188"/>
+      <c r="I5" s="188"/>
+      <c r="J5" s="188"/>
+      <c r="K5" s="188"/>
+      <c r="L5" s="188"/>
+      <c r="M5" s="188"/>
+      <c r="N5" s="188"/>
+      <c r="O5" s="188"/>
       <c r="P5" s="21"/>
     </row>
-    <row r="6" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="189"/>
-      <c r="B6" s="189"/>
-      <c r="C6" s="189"/>
-      <c r="D6" s="189"/>
-      <c r="E6" s="189"/>
-      <c r="F6" s="189"/>
-      <c r="G6" s="189"/>
-      <c r="H6" s="189"/>
-      <c r="I6" s="189"/>
-      <c r="J6" s="189"/>
-      <c r="K6" s="189"/>
-      <c r="L6" s="189"/>
-      <c r="M6" s="189"/>
-      <c r="N6" s="189"/>
-      <c r="O6" s="189"/>
+    <row r="6" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="188"/>
+      <c r="B6" s="188"/>
+      <c r="C6" s="188"/>
+      <c r="D6" s="188"/>
+      <c r="E6" s="188"/>
+      <c r="F6" s="188"/>
+      <c r="G6" s="188"/>
+      <c r="H6" s="188"/>
+      <c r="I6" s="188"/>
+      <c r="J6" s="188"/>
+      <c r="K6" s="188"/>
+      <c r="L6" s="188"/>
+      <c r="M6" s="188"/>
+      <c r="N6" s="188"/>
+      <c r="O6" s="188"/>
       <c r="P6" s="21"/>
     </row>
-    <row r="7" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="189"/>
-      <c r="B7" s="189"/>
-      <c r="C7" s="189"/>
-      <c r="D7" s="189"/>
-      <c r="E7" s="189"/>
-      <c r="F7" s="189"/>
-      <c r="G7" s="189"/>
-      <c r="H7" s="189"/>
-      <c r="I7" s="189"/>
-      <c r="J7" s="189"/>
-      <c r="K7" s="189"/>
-      <c r="L7" s="189"/>
-      <c r="M7" s="189"/>
-      <c r="N7" s="189"/>
-      <c r="O7" s="189"/>
+    <row r="7" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="188"/>
+      <c r="B7" s="188"/>
+      <c r="C7" s="188"/>
+      <c r="D7" s="188"/>
+      <c r="E7" s="188"/>
+      <c r="F7" s="188"/>
+      <c r="G7" s="188"/>
+      <c r="H7" s="188"/>
+      <c r="I7" s="188"/>
+      <c r="J7" s="188"/>
+      <c r="K7" s="188"/>
+      <c r="L7" s="188"/>
+      <c r="M7" s="188"/>
+      <c r="N7" s="188"/>
+      <c r="O7" s="188"/>
       <c r="P7" s="21"/>
     </row>
-    <row r="8" spans="1:16" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="190"/>
-      <c r="B8" s="190"/>
-      <c r="C8" s="190"/>
-      <c r="D8" s="190"/>
-      <c r="E8" s="190"/>
-      <c r="F8" s="190"/>
-      <c r="G8" s="190"/>
-      <c r="H8" s="190"/>
-      <c r="I8" s="190"/>
-      <c r="J8" s="190"/>
-      <c r="K8" s="190"/>
-      <c r="L8" s="190"/>
-      <c r="M8" s="190"/>
-      <c r="N8" s="190"/>
-      <c r="O8" s="190"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" s="175" t="s">
+    <row r="8" spans="1:16" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="189"/>
+      <c r="B8" s="189"/>
+      <c r="C8" s="189"/>
+      <c r="D8" s="189"/>
+      <c r="E8" s="189"/>
+      <c r="F8" s="189"/>
+      <c r="G8" s="189"/>
+      <c r="H8" s="189"/>
+      <c r="I8" s="189"/>
+      <c r="J8" s="189"/>
+      <c r="K8" s="189"/>
+      <c r="L8" s="189"/>
+      <c r="M8" s="189"/>
+      <c r="N8" s="189"/>
+      <c r="O8" s="189"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A9" s="180" t="s">
         <v>3</v>
       </c>
       <c r="B9" s="129"/>
-      <c r="C9" s="175" t="s">
+      <c r="C9" s="180" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="175" t="s">
+      <c r="D9" s="180" t="s">
         <v>13</v>
       </c>
-      <c r="E9" s="175" t="s">
+      <c r="E9" s="180" t="s">
         <v>7</v>
       </c>
-      <c r="F9" s="179" t="s">
+      <c r="F9" s="176" t="s">
         <v>24</v>
       </c>
-      <c r="G9" s="175" t="s">
+      <c r="G9" s="180" t="s">
         <v>5</v>
       </c>
-      <c r="H9" s="183" t="s">
+      <c r="H9" s="182" t="s">
         <v>17</v>
       </c>
-      <c r="I9" s="179" t="s">
+      <c r="I9" s="176" t="s">
         <v>23</v>
       </c>
-      <c r="J9" s="179" t="s">
+      <c r="J9" s="176" t="s">
         <v>84</v>
       </c>
-      <c r="K9" s="179" t="s">
+      <c r="K9" s="176" t="s">
         <v>101</v>
       </c>
-      <c r="L9" s="186" t="s">
+      <c r="L9" s="185" t="s">
         <v>102</v>
       </c>
       <c r="M9" s="47" t="s">
         <v>21</v>
       </c>
-      <c r="N9" s="181" t="s">
+      <c r="N9" s="178" t="s">
         <v>12</v>
       </c>
-      <c r="O9" s="191" t="s">
+      <c r="O9" s="190" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="177"/>
+    <row r="10" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="181"/>
       <c r="B10" s="130"/>
-      <c r="C10" s="177"/>
-      <c r="D10" s="176"/>
-      <c r="E10" s="177"/>
-      <c r="F10" s="180"/>
-      <c r="G10" s="177"/>
-      <c r="H10" s="184"/>
-      <c r="I10" s="180"/>
-      <c r="J10" s="185"/>
-      <c r="K10" s="180"/>
-      <c r="L10" s="187"/>
+      <c r="C10" s="181"/>
+      <c r="D10" s="192"/>
+      <c r="E10" s="181"/>
+      <c r="F10" s="177"/>
+      <c r="G10" s="181"/>
+      <c r="H10" s="183"/>
+      <c r="I10" s="177"/>
+      <c r="J10" s="184"/>
+      <c r="K10" s="177"/>
+      <c r="L10" s="186"/>
       <c r="M10" s="45" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 15/12</v>
       </c>
-      <c r="N10" s="182"/>
-      <c r="O10" s="192"/>
-    </row>
-    <row r="11" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N10" s="179"/>
+      <c r="O10" s="191"/>
+    </row>
+    <row r="11" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="48">
         <v>1</v>
       </c>
@@ -2993,7 +2993,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="48">
         <v>2</v>
       </c>
@@ -3051,7 +3051,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="48">
         <v>3</v>
       </c>
@@ -3111,7 +3111,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="48">
         <v>4</v>
       </c>
@@ -3171,7 +3171,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="48">
         <v>5</v>
       </c>
@@ -3231,7 +3231,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="48">
         <v>6</v>
       </c>
@@ -3291,7 +3291,7 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="48">
         <v>7</v>
       </c>
@@ -3351,7 +3351,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="48">
         <v>8</v>
       </c>
@@ -3411,7 +3411,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="48">
         <v>9</v>
       </c>
@@ -3471,7 +3471,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="48">
         <v>10</v>
       </c>
@@ -3531,7 +3531,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="48">
         <v>11</v>
       </c>
@@ -3592,7 +3592,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="48">
         <v>12</v>
       </c>
@@ -3652,7 +3652,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="48">
         <v>13</v>
       </c>
@@ -3712,7 +3712,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="48">
         <v>14</v>
       </c>
@@ -3770,7 +3770,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="48">
         <v>15</v>
       </c>
@@ -3828,7 +3828,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="48">
         <v>16</v>
       </c>
@@ -3888,7 +3888,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="48">
         <v>17</v>
       </c>
@@ -3946,7 +3946,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="28" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="48">
         <v>18</v>
       </c>
@@ -4004,7 +4004,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" s="48">
         <v>19</v>
       </c>
@@ -4059,7 +4059,7 @@
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" s="65">
         <v>20</v>
       </c>
@@ -4110,7 +4110,7 @@
       </c>
       <c r="P30" s="32"/>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" s="65">
         <v>21</v>
       </c>
@@ -4164,7 +4164,7 @@
       </c>
       <c r="P31" s="32"/>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32" s="66">
         <v>22</v>
       </c>
@@ -4216,7 +4216,7 @@
       </c>
       <c r="P32" s="32"/>
     </row>
-    <row r="33" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="48">
         <v>23</v>
       </c>
@@ -4270,7 +4270,7 @@
       </c>
       <c r="P33" s="32"/>
     </row>
-    <row r="34" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="70"/>
       <c r="B34" s="70"/>
       <c r="C34" s="71"/>
@@ -4320,94 +4320,99 @@
         <v>2016928.9000000001</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C35" s="38"/>
       <c r="D35" s="38"/>
     </row>
-    <row r="36" spans="1:16" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="1:16" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C37" s="167" t="str">
+    <row r="36" spans="1:16" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="37" spans="1:16" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C37" s="173" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. PORFAVOR RESPETAR LOS CENTAVOS AL ABONAR.</v>
       </c>
-      <c r="D37" s="167"/>
-      <c r="E37" s="167"/>
-      <c r="F37" s="167"/>
-      <c r="G37" s="167"/>
-      <c r="H37" s="167"/>
-      <c r="I37" s="167"/>
-      <c r="J37" s="167"/>
-      <c r="K37" s="167"/>
-      <c r="L37" s="167"/>
-      <c r="M37" s="167"/>
-    </row>
-    <row r="38" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C38" s="167"/>
-      <c r="D38" s="167"/>
-      <c r="E38" s="167"/>
-      <c r="F38" s="167"/>
-      <c r="G38" s="167"/>
-      <c r="H38" s="167"/>
-      <c r="I38" s="167"/>
-      <c r="J38" s="167"/>
-      <c r="K38" s="167"/>
-      <c r="L38" s="167"/>
-      <c r="M38" s="167"/>
-    </row>
-    <row r="39" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C39" s="167"/>
-      <c r="D39" s="167"/>
-      <c r="E39" s="167"/>
-      <c r="F39" s="167"/>
-      <c r="G39" s="167"/>
-      <c r="H39" s="167"/>
-      <c r="I39" s="167"/>
-      <c r="J39" s="167"/>
-      <c r="K39" s="167"/>
-      <c r="L39" s="167"/>
-      <c r="M39" s="167"/>
-    </row>
-    <row r="40" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C40" s="167"/>
-      <c r="D40" s="167"/>
-      <c r="E40" s="167"/>
-      <c r="F40" s="167"/>
-      <c r="G40" s="167"/>
-      <c r="H40" s="167"/>
-      <c r="I40" s="167"/>
-      <c r="J40" s="167"/>
-      <c r="K40" s="167"/>
-      <c r="L40" s="167"/>
-      <c r="M40" s="167"/>
-    </row>
-    <row r="41" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C41" s="167"/>
-      <c r="D41" s="167"/>
-      <c r="E41" s="167"/>
-      <c r="F41" s="167"/>
-      <c r="G41" s="167"/>
-      <c r="H41" s="167"/>
-      <c r="I41" s="167"/>
-      <c r="J41" s="167"/>
-      <c r="K41" s="167"/>
-      <c r="L41" s="167"/>
-      <c r="M41" s="167"/>
-    </row>
-    <row r="42" spans="1:16" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C42" s="167"/>
-      <c r="D42" s="167"/>
-      <c r="E42" s="167"/>
-      <c r="F42" s="167"/>
-      <c r="G42" s="167"/>
-      <c r="H42" s="167"/>
-      <c r="I42" s="167"/>
-      <c r="J42" s="167"/>
-      <c r="K42" s="167"/>
-      <c r="L42" s="167"/>
-      <c r="M42" s="167"/>
+      <c r="D37" s="173"/>
+      <c r="E37" s="173"/>
+      <c r="F37" s="173"/>
+      <c r="G37" s="173"/>
+      <c r="H37" s="173"/>
+      <c r="I37" s="173"/>
+      <c r="J37" s="173"/>
+      <c r="K37" s="173"/>
+      <c r="L37" s="173"/>
+      <c r="M37" s="173"/>
+    </row>
+    <row r="38" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C38" s="173"/>
+      <c r="D38" s="173"/>
+      <c r="E38" s="173"/>
+      <c r="F38" s="173"/>
+      <c r="G38" s="173"/>
+      <c r="H38" s="173"/>
+      <c r="I38" s="173"/>
+      <c r="J38" s="173"/>
+      <c r="K38" s="173"/>
+      <c r="L38" s="173"/>
+      <c r="M38" s="173"/>
+    </row>
+    <row r="39" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C39" s="173"/>
+      <c r="D39" s="173"/>
+      <c r="E39" s="173"/>
+      <c r="F39" s="173"/>
+      <c r="G39" s="173"/>
+      <c r="H39" s="173"/>
+      <c r="I39" s="173"/>
+      <c r="J39" s="173"/>
+      <c r="K39" s="173"/>
+      <c r="L39" s="173"/>
+      <c r="M39" s="173"/>
+    </row>
+    <row r="40" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C40" s="173"/>
+      <c r="D40" s="173"/>
+      <c r="E40" s="173"/>
+      <c r="F40" s="173"/>
+      <c r="G40" s="173"/>
+      <c r="H40" s="173"/>
+      <c r="I40" s="173"/>
+      <c r="J40" s="173"/>
+      <c r="K40" s="173"/>
+      <c r="L40" s="173"/>
+      <c r="M40" s="173"/>
+    </row>
+    <row r="41" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C41" s="173"/>
+      <c r="D41" s="173"/>
+      <c r="E41" s="173"/>
+      <c r="F41" s="173"/>
+      <c r="G41" s="173"/>
+      <c r="H41" s="173"/>
+      <c r="I41" s="173"/>
+      <c r="J41" s="173"/>
+      <c r="K41" s="173"/>
+      <c r="L41" s="173"/>
+      <c r="M41" s="173"/>
+    </row>
+    <row r="42" spans="1:16" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C42" s="173"/>
+      <c r="D42" s="173"/>
+      <c r="E42" s="173"/>
+      <c r="F42" s="173"/>
+      <c r="G42" s="173"/>
+      <c r="H42" s="173"/>
+      <c r="I42" s="173"/>
+      <c r="J42" s="173"/>
+      <c r="K42" s="173"/>
+      <c r="L42" s="173"/>
+      <c r="M42" s="173"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="C37:M42"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="E9:E10"/>
     <mergeCell ref="E1:M1"/>
     <mergeCell ref="I9:I10"/>
     <mergeCell ref="F9:F10"/>
@@ -4419,11 +4424,6 @@
     <mergeCell ref="L9:L10"/>
     <mergeCell ref="A4:O8"/>
     <mergeCell ref="O9:O10"/>
-    <mergeCell ref="C37:M42"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="E9:E10"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
@@ -4433,17 +4433,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D7123E2-E76E-40B2-9631-974509386176}">
   <dimension ref="B3:J33"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="4" customWidth="1"/>
-    <col min="5" max="5" width="21.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.5703125" customWidth="1"/>
-    <col min="7" max="7" width="24.42578125" customWidth="1"/>
+    <col min="5" max="5" width="21.6640625" customWidth="1"/>
+    <col min="6" max="6" width="4.5546875" customWidth="1"/>
+    <col min="7" max="7" width="24.44140625" customWidth="1"/>
     <col min="8" max="8" width="5" customWidth="1"/>
-    <col min="10" max="10" width="19.5703125" customWidth="1"/>
+    <col min="10" max="10" width="19.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="141" t="s">
         <v>85</v>
       </c>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="J3" s="196"/>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B4" s="141"/>
       <c r="C4" s="141"/>
       <c r="E4" s="141"/>
@@ -4469,7 +4469,7 @@
       <c r="I4" s="195"/>
       <c r="J4" s="196"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B5" s="141">
         <v>1</v>
       </c>
@@ -4489,7 +4489,7 @@
       </c>
       <c r="J5" s="194"/>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B6" s="141">
         <v>1</v>
       </c>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="J6" s="194"/>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B7" s="141">
         <v>1</v>
       </c>
@@ -4529,7 +4529,7 @@
       </c>
       <c r="J7" s="194"/>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B8" s="141">
         <v>2</v>
       </c>
@@ -4549,7 +4549,7 @@
       </c>
       <c r="J8" s="194"/>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B9" s="142">
         <v>2</v>
       </c>
@@ -4569,7 +4569,7 @@
       </c>
       <c r="J9" s="194"/>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B10" s="142">
         <v>2</v>
       </c>
@@ -4589,7 +4589,7 @@
       </c>
       <c r="J10" s="194"/>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B11" s="142">
         <v>2</v>
       </c>
@@ -4609,7 +4609,7 @@
       </c>
       <c r="J11" s="194"/>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B12" s="142">
         <v>3</v>
       </c>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="J12" s="194"/>
     </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B13" s="141">
         <v>3</v>
       </c>
@@ -4649,7 +4649,7 @@
       </c>
       <c r="J13" s="194"/>
     </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B14" s="142">
         <v>3</v>
       </c>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="J14" s="194"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B15" s="142">
         <v>3</v>
       </c>
@@ -4689,7 +4689,7 @@
       </c>
       <c r="J15" s="194"/>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B16" s="141">
         <v>4</v>
       </c>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="J16" s="194"/>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B17" s="142">
         <v>4</v>
       </c>
@@ -4729,7 +4729,7 @@
       </c>
       <c r="J17" s="194"/>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B18" s="141">
         <v>4</v>
       </c>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="J18" s="194"/>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B19" s="142">
         <v>4</v>
       </c>
@@ -4769,7 +4769,7 @@
       </c>
       <c r="J19" s="194"/>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B20" s="141"/>
       <c r="C20" s="141"/>
       <c r="E20" s="141"/>
@@ -4777,7 +4777,7 @@
       <c r="I20" s="193"/>
       <c r="J20" s="194"/>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B21" s="141"/>
       <c r="C21" s="141"/>
       <c r="E21" s="150">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="J21" s="194"/>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B22" s="141" t="s">
         <v>91</v>
       </c>
@@ -4813,7 +4813,7 @@
       </c>
       <c r="J22" s="194"/>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B23" s="141" t="s">
         <v>91</v>
       </c>
@@ -4832,7 +4832,7 @@
       </c>
       <c r="J23" s="194"/>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B24" s="141" t="s">
         <v>91</v>
       </c>
@@ -4851,7 +4851,7 @@
       </c>
       <c r="J24" s="194"/>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B25" s="141" t="s">
         <v>91</v>
       </c>
@@ -4870,7 +4870,7 @@
       </c>
       <c r="J25" s="194"/>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B26" s="141" t="s">
         <v>91</v>
       </c>
@@ -4889,7 +4889,7 @@
       </c>
       <c r="J26" s="194"/>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B27" s="141" t="s">
         <v>91</v>
       </c>
@@ -4908,7 +4908,7 @@
       </c>
       <c r="J27" s="194"/>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B28" s="141" t="s">
         <v>91</v>
       </c>
@@ -4927,7 +4927,7 @@
       </c>
       <c r="J28" s="194"/>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B29" s="141" t="s">
         <v>91</v>
       </c>
@@ -4946,7 +4946,7 @@
       </c>
       <c r="J29" s="194"/>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.3">
       <c r="E30" s="150">
         <f>SUM(E22:E29)</f>
         <v>4133.9046796095499</v>
@@ -4961,7 +4961,7 @@
       </c>
       <c r="J30" s="194"/>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.3">
       <c r="E31" s="150"/>
       <c r="G31" s="147"/>
       <c r="I31" s="193">
@@ -4970,13 +4970,13 @@
       </c>
       <c r="J31" s="194"/>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.3">
       <c r="E32" s="148"/>
       <c r="G32" s="149"/>
       <c r="I32" s="193"/>
       <c r="J32" s="194"/>
     </row>
-    <row r="33" spans="5:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="5:10" x14ac:dyDescent="0.3">
       <c r="E33" s="150">
         <f>E30+E21</f>
         <v>351243.74189499998</v>
@@ -4993,6 +4993,21 @@
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="I17:J17"/>
     <mergeCell ref="I31:J31"/>
     <mergeCell ref="I32:J32"/>
     <mergeCell ref="I33:J33"/>
@@ -5009,21 +5024,6 @@
     <mergeCell ref="I22:J22"/>
     <mergeCell ref="I23:J23"/>
     <mergeCell ref="I24:J24"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="I17:J17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="portrait" r:id="rId1"/>
